--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022264</v>
+        <v>126022260</v>
       </c>
       <c r="B7" t="n">
         <v>78968</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431780</v>
+        <v>431805</v>
       </c>
       <c r="R7" t="n">
-        <v>6793497</v>
+        <v>6793440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022260</v>
+        <v>126022264</v>
       </c>
       <c r="B8" t="n">
         <v>78968</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431805</v>
+        <v>431780</v>
       </c>
       <c r="R8" t="n">
-        <v>6793440</v>
+        <v>6793497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022257</v>
+        <v>126022254</v>
       </c>
       <c r="B11" t="n">
         <v>78968</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431770</v>
+        <v>431618</v>
       </c>
       <c r="R11" t="n">
-        <v>6793441</v>
+        <v>6793484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022254</v>
+        <v>126022257</v>
       </c>
       <c r="B12" t="n">
         <v>78968</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431618</v>
+        <v>431770</v>
       </c>
       <c r="R12" t="n">
-        <v>6793484</v>
+        <v>6793441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022267</v>
+        <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431663</v>
+        <v>431785</v>
       </c>
       <c r="R14" t="n">
-        <v>6793516</v>
+        <v>6793548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022232</v>
+        <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>79557</v>
+        <v>78635</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431615</v>
+        <v>431663</v>
       </c>
       <c r="R15" t="n">
-        <v>6793508</v>
+        <v>6793516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022246</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431785</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793548</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022251</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022241</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022243</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022253</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022256</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022260</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022264</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022240</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126022236</v>
       </c>
       <c r="B10" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126022254</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126022257</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126022238</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022246</v>
+        <v>126022232</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>79561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431785</v>
+        <v>431615</v>
       </c>
       <c r="R14" t="n">
-        <v>6793548</v>
+        <v>6793508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022267</v>
+        <v>126022246</v>
       </c>
       <c r="B15" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431663</v>
+        <v>431785</v>
       </c>
       <c r="R15" t="n">
-        <v>6793516</v>
+        <v>6793548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022232</v>
+        <v>126022267</v>
       </c>
       <c r="B16" t="n">
-        <v>79557</v>
+        <v>78639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431615</v>
+        <v>431663</v>
       </c>
       <c r="R16" t="n">
-        <v>6793508</v>
+        <v>6793516</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R17" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B18" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R18" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>126022247</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022255</v>
+        <v>126022237</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431623</v>
+        <v>431839</v>
       </c>
       <c r="R20" t="n">
-        <v>6793485</v>
+        <v>6793457</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022237</v>
+        <v>126022262</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431839</v>
+        <v>431808</v>
       </c>
       <c r="R21" t="n">
-        <v>6793457</v>
+        <v>6793454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022262</v>
+        <v>126022255</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431808</v>
+        <v>431623</v>
       </c>
       <c r="R22" t="n">
-        <v>6793454</v>
+        <v>6793485</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
         <v>126022245</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126022250</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126022242</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126022248</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126022263</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>126022252</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>126022239</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R14" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R15" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78639</v>
+        <v>79561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R17" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R18" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022237</v>
+        <v>126022255</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431839</v>
+        <v>431623</v>
       </c>
       <c r="R20" t="n">
-        <v>6793457</v>
+        <v>6793485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022262</v>
+        <v>126022237</v>
       </c>
       <c r="B21" t="n">
         <v>78972</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431808</v>
+        <v>431839</v>
       </c>
       <c r="R21" t="n">
-        <v>6793454</v>
+        <v>6793457</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022255</v>
+        <v>126022262</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431623</v>
+        <v>431808</v>
       </c>
       <c r="R22" t="n">
-        <v>6793485</v>
+        <v>6793454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R14" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022267</v>
+        <v>126022246</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431663</v>
+        <v>431785</v>
       </c>
       <c r="R15" t="n">
-        <v>6793516</v>
+        <v>6793548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3389,6 +3389,8346 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126159713</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>431676</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6793755</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126159766</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>431687</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6793778</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126161051</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>431757</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6793912</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126161265</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>431735</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6794019</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126161615</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>431758</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6794063</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126161538</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>431778</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6794048</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126162525</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>431861</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6794056</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126162787</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>431921</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6794053</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126166842</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>432245</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6794369</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126165139</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>431949</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6794232</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126166251</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126156950</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>431647</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6793602</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126159534</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>431657</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6793728</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126162274</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>431815</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6794067</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126161498</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>431776</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6794017</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126162811</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>431942</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6794029</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126164975</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>431934</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6794246</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126165020</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>431934</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6794246</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126165872</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126165832</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126167392</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>431653</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6793960</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126166682</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>432272</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6794337</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126161213</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>431756</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6793994</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126160760</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>431740</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6793833</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126162332</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>431839</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6794073</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126166244</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126157375</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>431639</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6793601</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126160189</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>431763</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6793789</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126162045</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>431758</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6794063</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126162207</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>431783</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6794074</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126166337</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126167237</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>432161</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6794303</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126166910</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>432177</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6794345</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126162778</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>431921</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6794053</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126162541</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>431861</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6794056</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126165216</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>431949</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6794232</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126165950</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126160807</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>431738</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6793845</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126160381</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>431734</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6793794</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126159369</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>431635</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6793754</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126162164</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>431783</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6794074</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126164027</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>431844</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6794158</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126165342</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>431949</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6794232</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126166809</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>432273</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6794365</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126166708</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>432272</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6794337</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126162912</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>431943</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6794014</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126163869</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>431844</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6794158</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126161304</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>431735</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6794019</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126166104</v>
+      </c>
+      <c r="B78" t="n">
+        <v>75067</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126157808</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>431582</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6793582</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126159852</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>431733</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6793772</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126166662</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>432272</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6794337</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126158231</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>431597</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6793646</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126162596</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>431888</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6794051</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126165131</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>431949</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6794232</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126161478</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>431764</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6794018</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126161557</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>431758</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6794063</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126166691</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>432272</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6794337</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126157967</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>431581</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6793601</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126161074</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>431755</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6793917</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126163857</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>431844</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6794158</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126165579</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>432011</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6794169</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126161036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>431757</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6793912</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126162862</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>431942</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6794029</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126158198</v>
+      </c>
+      <c r="B94" t="n">
+        <v>75067</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>431575</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6793614</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126165247</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>431949</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6794232</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126160693</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>431740</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6793833</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126161159</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>431724</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6793934</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126161358</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>431735</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6794019</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126162110</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>431776</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6794066</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126160792</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>431740</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6793833</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126160826</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>431763</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6793869</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126162464</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>431861</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6794056</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126159604</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>431657</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6793728</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126163938</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>431844</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6794158</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126160391</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>431718</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6793795</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126160368</v>
+      </c>
+      <c r="B106" t="n">
+        <v>75067</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>431734</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6793794</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126160965</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>431763</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6793869</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126162132</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>431783</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6794074</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126164968</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>431934</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6794246</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126166906</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91252</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>432177</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6794345</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126167341</v>
+      </c>
+      <c r="B111" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>431682</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6794066</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126161563</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>431758</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6794063</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126160295</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>431734</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6793794</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126162496</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>431861</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6794056</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022267</v>
+        <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431663</v>
+        <v>431785</v>
       </c>
       <c r="R14" t="n">
-        <v>6793516</v>
+        <v>6793548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R15" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R17" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R18" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126162787</v>
+        <v>126166251</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431921</v>
+        <v>432011</v>
       </c>
       <c r="R37" t="n">
-        <v>6794053</v>
+        <v>6794169</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126166842</v>
+        <v>126162787</v>
       </c>
       <c r="B38" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4178,39 +4178,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432245</v>
+        <v>431921</v>
       </c>
       <c r="R38" t="n">
-        <v>6794369</v>
+        <v>6794053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126165139</v>
+        <v>126166842</v>
       </c>
       <c r="B39" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,34 +4275,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431949</v>
+        <v>432245</v>
       </c>
       <c r="R39" t="n">
-        <v>6794232</v>
+        <v>6794369</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126166251</v>
+        <v>126165139</v>
       </c>
       <c r="B40" t="n">
         <v>79590</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432011</v>
+        <v>431949</v>
       </c>
       <c r="R40" t="n">
-        <v>6794169</v>
+        <v>6794232</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126162274</v>
+        <v>126167392</v>
       </c>
       <c r="B43" t="n">
         <v>78972</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431815</v>
+        <v>431653</v>
       </c>
       <c r="R43" t="n">
-        <v>6794067</v>
+        <v>6793960</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4728,6 +4728,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4754,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126161498</v>
+        <v>126166682</v>
       </c>
       <c r="B44" t="n">
-        <v>57648</v>
+        <v>78731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,39 +4770,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431776</v>
+        <v>432272</v>
       </c>
       <c r="R44" t="n">
-        <v>6794017</v>
+        <v>6794337</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126162811</v>
+        <v>126162274</v>
       </c>
       <c r="B45" t="n">
         <v>78972</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431942</v>
+        <v>431815</v>
       </c>
       <c r="R45" t="n">
-        <v>6794029</v>
+        <v>6794067</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126164975</v>
+        <v>126161498</v>
       </c>
       <c r="B46" t="n">
-        <v>79561</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4964,34 +4964,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431934</v>
+        <v>431776</v>
       </c>
       <c r="R46" t="n">
-        <v>6794246</v>
+        <v>6794017</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5050,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126165020</v>
+        <v>126162811</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5061,39 +5066,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431934</v>
+        <v>431942</v>
       </c>
       <c r="R47" t="n">
-        <v>6794246</v>
+        <v>6794029</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126165872</v>
+        <v>126164975</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432011</v>
+        <v>431934</v>
       </c>
       <c r="R48" t="n">
-        <v>6794169</v>
+        <v>6794246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,45 +5249,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126165832</v>
+        <v>126165020</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>432011</v>
+        <v>431934</v>
       </c>
       <c r="R49" t="n">
-        <v>6794169</v>
+        <v>6794246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126167392</v>
+        <v>126165872</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431653</v>
+        <v>432011</v>
       </c>
       <c r="R50" t="n">
-        <v>6793960</v>
+        <v>6794169</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5417,11 +5422,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5448,32 +5448,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126166682</v>
+        <v>126165832</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432272</v>
+        <v>432011</v>
       </c>
       <c r="R51" t="n">
-        <v>6794337</v>
+        <v>6794169</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126161213</v>
+        <v>126166244</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,34 +5556,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431756</v>
+        <v>432011</v>
       </c>
       <c r="R52" t="n">
-        <v>6793994</v>
+        <v>6794169</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126160760</v>
+        <v>126162332</v>
       </c>
       <c r="B53" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431740</v>
+        <v>431839</v>
       </c>
       <c r="R53" t="n">
-        <v>6793833</v>
+        <v>6794073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5739,7 +5739,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B54" t="n">
         <v>78972</v>
@@ -5770,14 +5770,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R54" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126166244</v>
+        <v>126160760</v>
       </c>
       <c r="B55" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,34 +5847,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>432011</v>
+        <v>431740</v>
       </c>
       <c r="R55" t="n">
-        <v>6794169</v>
+        <v>6793833</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5933,7 +5933,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126157375</v>
+        <v>126157004</v>
       </c>
       <c r="B56" t="n">
         <v>78972</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6132,50 +6132,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126162045</v>
+        <v>126166337</v>
       </c>
       <c r="B58" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431758</v>
+        <v>432011</v>
       </c>
       <c r="R58" t="n">
-        <v>6794063</v>
+        <v>6794169</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6331,45 +6326,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126166337</v>
+        <v>126162045</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>58020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432011</v>
+        <v>431758</v>
       </c>
       <c r="R60" t="n">
-        <v>6794169</v>
+        <v>6794063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126162778</v>
+        <v>126165216</v>
       </c>
       <c r="B63" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,39 +6638,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431921</v>
+        <v>431949</v>
       </c>
       <c r="R63" t="n">
-        <v>6794053</v>
+        <v>6794232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6729,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126162541</v>
+        <v>126165950</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>57648</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,34 +6735,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431861</v>
+        <v>432011</v>
       </c>
       <c r="R64" t="n">
-        <v>6794056</v>
+        <v>6794169</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126165216</v>
+        <v>126162778</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>57648</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,34 +6837,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431949</v>
+        <v>431921</v>
       </c>
       <c r="R65" t="n">
-        <v>6794232</v>
+        <v>6794053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6923,10 +6928,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126165950</v>
+        <v>126162541</v>
       </c>
       <c r="B66" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,39 +6939,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432011</v>
+        <v>431861</v>
       </c>
       <c r="R66" t="n">
-        <v>6794169</v>
+        <v>6794056</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126162912</v>
+        <v>126161304</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>79561</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7817,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431943</v>
+        <v>431735</v>
       </c>
       <c r="R75" t="n">
-        <v>6794014</v>
+        <v>6794019</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,12 +7871,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7908,10 +7903,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126163869</v>
+        <v>126166104</v>
       </c>
       <c r="B76" t="n">
-        <v>79561</v>
+        <v>75067</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7919,21 +7914,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431844</v>
+        <v>432011</v>
       </c>
       <c r="R76" t="n">
-        <v>6794158</v>
+        <v>6794169</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8005,45 +8000,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126161304</v>
+        <v>126157808</v>
       </c>
       <c r="B77" t="n">
-        <v>79561</v>
+        <v>58020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431735</v>
+        <v>431582</v>
       </c>
       <c r="R77" t="n">
-        <v>6794019</v>
+        <v>6793582</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8070,12 +8070,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126166104</v>
+        <v>126162912</v>
       </c>
       <c r="B78" t="n">
-        <v>75067</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8113,34 +8113,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432011</v>
+        <v>431943</v>
       </c>
       <c r="R78" t="n">
-        <v>6794169</v>
+        <v>6794014</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8199,50 +8204,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126157808</v>
+        <v>126163869</v>
       </c>
       <c r="B79" t="n">
-        <v>58020</v>
+        <v>79561</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431582</v>
+        <v>431844</v>
       </c>
       <c r="R79" t="n">
-        <v>6793582</v>
+        <v>6794158</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126166662</v>
+        <v>126162596</v>
       </c>
       <c r="B81" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,21 +8409,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432272</v>
+        <v>431888</v>
       </c>
       <c r="R81" t="n">
-        <v>6794337</v>
+        <v>6794051</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126158231</v>
+        <v>126166662</v>
       </c>
       <c r="B82" t="n">
-        <v>57651</v>
+        <v>79561</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,39 +8506,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431597</v>
+        <v>432272</v>
       </c>
       <c r="R82" t="n">
-        <v>6793646</v>
+        <v>6794337</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8597,10 +8592,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126162596</v>
+        <v>126158231</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8608,34 +8603,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431888</v>
+        <v>431597</v>
       </c>
       <c r="R83" t="n">
-        <v>6794051</v>
+        <v>6793646</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126161478</v>
+        <v>126166691</v>
       </c>
       <c r="B85" t="n">
         <v>79590</v>
@@ -8822,14 +8822,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431764</v>
+        <v>432272</v>
       </c>
       <c r="R85" t="n">
-        <v>6794018</v>
+        <v>6794337</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8985,7 +8985,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126166691</v>
+        <v>126161478</v>
       </c>
       <c r="B87" t="n">
         <v>79590</v>
@@ -9016,14 +9016,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432272</v>
+        <v>431764</v>
       </c>
       <c r="R87" t="n">
-        <v>6794337</v>
+        <v>6794018</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126157967</v>
+        <v>126163857</v>
       </c>
       <c r="B88" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9093,34 +9093,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431581</v>
+        <v>431844</v>
       </c>
       <c r="R88" t="n">
-        <v>6793601</v>
+        <v>6794158</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9179,10 +9184,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9190,21 +9195,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9214,10 +9219,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R89" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9244,12 +9249,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9276,10 +9281,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126163857</v>
+        <v>126161074</v>
       </c>
       <c r="B90" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9287,39 +9292,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431844</v>
+        <v>431755</v>
       </c>
       <c r="R90" t="n">
-        <v>6794158</v>
+        <v>6793917</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11532,10 +11532,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126160295</v>
+        <v>126162496</v>
       </c>
       <c r="B113" t="n">
-        <v>57648</v>
+        <v>79590</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11543,39 +11543,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431734</v>
+        <v>431861</v>
       </c>
       <c r="R113" t="n">
-        <v>6793794</v>
+        <v>6794056</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11634,10 +11629,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126162496</v>
+        <v>126160295</v>
       </c>
       <c r="B114" t="n">
-        <v>79590</v>
+        <v>57648</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11645,34 +11640,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431861</v>
+        <v>431734</v>
       </c>
       <c r="R114" t="n">
-        <v>6794056</v>
+        <v>6793794</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,6 +11728,7278 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126167440</v>
+      </c>
+      <c r="B115" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>431667</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6793982</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126190532</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>431671</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6793831</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126162009</v>
+      </c>
+      <c r="B117" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>431754</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6794068</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126188368</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>431698</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6793851</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126189457</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79004</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>185</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>431586</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6793587</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>126190428</v>
+      </c>
+      <c r="B120" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>431652</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6793771</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126163646</v>
+      </c>
+      <c r="B121" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>431898</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6794103</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>126174681</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>431802</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6794020</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>126174973</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>432045</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6794330</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>126161529</v>
+      </c>
+      <c r="B124" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>431705</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6794050</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>126175046</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>432130</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6794314</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>126174513</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>431721</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6793745</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126174710</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>431847</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6794063</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126190566</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>431683</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6793850</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>126166304</v>
+      </c>
+      <c r="B129" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>432104</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6794293</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>126190620</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>432093</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6794181</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>126174983</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>432144</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6794303</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>126165849</v>
+      </c>
+      <c r="B132" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>432071</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6794181</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Hona? ev med kycklingar</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>126165489</v>
+      </c>
+      <c r="B133" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>432050</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6794210</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning, fjolårets, på stubbe</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>126162531</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>431906</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6794099</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>126174545</v>
+      </c>
+      <c r="B135" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>431721</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6793766</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>126189221</v>
+      </c>
+      <c r="B136" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>431686</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6793927</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>126188380</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>431700</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6793865</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Massor</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>126167010</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>432026</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6794333</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>126165527</v>
+      </c>
+      <c r="B139" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>432037</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6794186</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>126162062</v>
+      </c>
+      <c r="B140" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>431788</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6794108</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>126189975</v>
+      </c>
+      <c r="B141" t="n">
+        <v>92714</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>431647</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6794014</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126166597</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>432054</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6794331</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>126190225</v>
+      </c>
+      <c r="B143" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>431908</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6794091</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>126190276</v>
+      </c>
+      <c r="B144" t="n">
+        <v>56227</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Baruersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>431609</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6793764</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>126174674</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>431802</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6794020</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>126188869</v>
+      </c>
+      <c r="B146" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>431661</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6793741</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>126188441</v>
+      </c>
+      <c r="B147" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>431692</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6793928</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>126188589</v>
+      </c>
+      <c r="B148" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>431672</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6794047</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>126174633</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>431765</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6793901</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>126174664</v>
+      </c>
+      <c r="B150" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>431803</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6793998</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>126161782</v>
+      </c>
+      <c r="B151" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>431721</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6794089</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>126189837</v>
+      </c>
+      <c r="B152" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>431661</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6793926</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>126190311</v>
+      </c>
+      <c r="B153" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>431597</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6793607</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>126175021</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>432130</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6794314</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>126174690</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>431789</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6794033</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>126165721</v>
+      </c>
+      <c r="B156" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>432067</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6794181</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Barr</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>126185018</v>
+      </c>
+      <c r="B157" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>431898</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6794103</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>126165414</v>
+      </c>
+      <c r="B158" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>432012</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6794220</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>126188626</v>
+      </c>
+      <c r="B159" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>431672</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6794047</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Hästmyror i stubben</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>126190467</v>
+      </c>
+      <c r="B160" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>431637</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6793824</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>126174574</v>
+      </c>
+      <c r="B161" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>431765</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6793901</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>126174924</v>
+      </c>
+      <c r="B162" t="n">
+        <v>79004</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>185</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>431893</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6794043</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>126188337</v>
+      </c>
+      <c r="B163" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>431609</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6793762</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>126189054</v>
+      </c>
+      <c r="B164" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>431660</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6793737</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>126174961</v>
+      </c>
+      <c r="B165" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>432073</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6794217</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>126174659</v>
+      </c>
+      <c r="B166" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>431731</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6793834</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>126165393</v>
+      </c>
+      <c r="B167" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>432012</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6794220</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>126162636</v>
+      </c>
+      <c r="B168" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>431906</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6794099</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>126166368</v>
+      </c>
+      <c r="B169" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>432093</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6794312</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>126165703</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92522</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>432067</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6794181</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>126165571</v>
+      </c>
+      <c r="B171" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>432034</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6794182</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>126174682</v>
+      </c>
+      <c r="B172" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>431789</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6794033</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>126192573</v>
+      </c>
+      <c r="B173" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>431790</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6794069</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>126189897</v>
+      </c>
+      <c r="B174" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>431648</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6793779</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>126174557</v>
+      </c>
+      <c r="B175" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>431730</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6793838</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>126174530</v>
+      </c>
+      <c r="B176" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>431675</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6793721</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>126162572</v>
+      </c>
+      <c r="B177" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>431906</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6794099</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>126188293</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Bauersberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>431642</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6794010</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>126167044</v>
+      </c>
+      <c r="B179" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Baursberg, Baursberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>432002</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6794336</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022251</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022241</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022243</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022253</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022256</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022260</v>
+        <v>126022264</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431805</v>
+        <v>431780</v>
       </c>
       <c r="R7" t="n">
-        <v>6793440</v>
+        <v>6793497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022264</v>
+        <v>126022240</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431780</v>
+        <v>431829</v>
       </c>
       <c r="R8" t="n">
-        <v>6793497</v>
+        <v>6793466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126022240</v>
+        <v>126022260</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431829</v>
+        <v>431805</v>
       </c>
       <c r="R9" t="n">
-        <v>6793466</v>
+        <v>6793440</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>126022236</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126022254</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126022257</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126022238</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>79562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R15" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022232</v>
+        <v>126022267</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>78640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431615</v>
+        <v>431663</v>
       </c>
       <c r="R16" t="n">
-        <v>6793508</v>
+        <v>6793516</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R17" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R18" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>126022247</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126022255</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126022237</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126022262</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126022245</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126022250</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126022242</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126022248</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126022263</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>126022252</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>126022239</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126159713</v>
+        <v>126165882</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,37 +3402,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431676</v>
+        <v>432011</v>
       </c>
       <c r="R30" t="n">
-        <v>6793755</v>
+        <v>6794169</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126159766</v>
+        <v>126161615</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,14 +3519,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431687</v>
+        <v>431758</v>
       </c>
       <c r="R31" t="n">
-        <v>6793778</v>
+        <v>6794063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126161051</v>
+        <v>126165139</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,34 +3596,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431757</v>
+        <v>431949</v>
       </c>
       <c r="R32" t="n">
-        <v>6793912</v>
+        <v>6794232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3685,7 +3685,7 @@
         <v>126161265</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126161615</v>
+        <v>126159713</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3810,17 +3810,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431758</v>
+        <v>431676</v>
       </c>
       <c r="R34" t="n">
-        <v>6794063</v>
+        <v>6793755</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126161538</v>
+        <v>126159766</v>
       </c>
       <c r="B35" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,34 +3887,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431778</v>
+        <v>431687</v>
       </c>
       <c r="R35" t="n">
-        <v>6794048</v>
+        <v>6793778</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126162525</v>
+        <v>126161051</v>
       </c>
       <c r="B36" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3984,34 +3984,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431861</v>
+        <v>431757</v>
       </c>
       <c r="R36" t="n">
-        <v>6794056</v>
+        <v>6793912</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126166251</v>
+        <v>126162787</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432011</v>
+        <v>431921</v>
       </c>
       <c r="R37" t="n">
-        <v>6794169</v>
+        <v>6794053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126162787</v>
+        <v>126166842</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4178,34 +4178,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431921</v>
+        <v>432245</v>
       </c>
       <c r="R38" t="n">
-        <v>6794053</v>
+        <v>6794369</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126166842</v>
+        <v>126161538</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>78732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4275,39 +4280,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432245</v>
+        <v>431778</v>
       </c>
       <c r="R39" t="n">
-        <v>6794369</v>
+        <v>6794048</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126165139</v>
+        <v>126162525</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>79562</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R40" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,45 +4463,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126156950</v>
+        <v>126165832</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431647</v>
+        <v>432011</v>
       </c>
       <c r="R41" t="n">
-        <v>6793602</v>
+        <v>6794169</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126159534</v>
+        <v>126164975</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4571,34 +4571,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431657</v>
+        <v>431934</v>
       </c>
       <c r="R42" t="n">
-        <v>6793728</v>
+        <v>6794246</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126167392</v>
+        <v>126165872</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431653</v>
+        <v>432011</v>
       </c>
       <c r="R43" t="n">
-        <v>6793960</v>
+        <v>6794169</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4728,11 +4728,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4762,7 +4757,7 @@
         <v>126166682</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,10 +4851,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126162274</v>
+        <v>126167392</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4891,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431815</v>
+        <v>431653</v>
       </c>
       <c r="R45" t="n">
-        <v>6794067</v>
+        <v>6793960</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4927,6 +4922,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126161498</v>
+        <v>126162274</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4964,39 +4964,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431776</v>
+        <v>431815</v>
       </c>
       <c r="R46" t="n">
-        <v>6794017</v>
+        <v>6794067</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5058,7 +5053,7 @@
         <v>126162811</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5152,10 +5147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126164975</v>
+        <v>126156950</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,34 +5158,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431934</v>
+        <v>431647</v>
       </c>
       <c r="R48" t="n">
-        <v>6794246</v>
+        <v>6793602</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,10 +5244,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126165020</v>
+        <v>126159534</v>
       </c>
       <c r="B49" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,39 +5255,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431934</v>
+        <v>431657</v>
       </c>
       <c r="R49" t="n">
-        <v>6794246</v>
+        <v>6793728</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5341,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126165872</v>
+        <v>126161498</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>57649</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,34 +5352,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432011</v>
+        <v>431776</v>
       </c>
       <c r="R50" t="n">
-        <v>6794169</v>
+        <v>6794017</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,45 +5443,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126165832</v>
+        <v>126165020</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432011</v>
+        <v>431934</v>
       </c>
       <c r="R51" t="n">
-        <v>6794169</v>
+        <v>6794246</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126166244</v>
+        <v>126161213</v>
       </c>
       <c r="B52" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,34 +5556,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432011</v>
+        <v>431756</v>
       </c>
       <c r="R52" t="n">
-        <v>6794169</v>
+        <v>6793994</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5645,7 +5645,7 @@
         <v>126162332</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126161213</v>
+        <v>126160760</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431756</v>
+        <v>431740</v>
       </c>
       <c r="R54" t="n">
-        <v>6793994</v>
+        <v>6793833</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126160760</v>
+        <v>126166244</v>
       </c>
       <c r="B55" t="n">
-        <v>79590</v>
+        <v>79562</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,34 +5847,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431740</v>
+        <v>432011</v>
       </c>
       <c r="R55" t="n">
-        <v>6793833</v>
+        <v>6794169</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5933,10 +5933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126157004</v>
+        <v>126160189</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431639</v>
+        <v>431763</v>
       </c>
       <c r="R56" t="n">
-        <v>6793601</v>
+        <v>6793789</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6004,11 +6004,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6035,10 +6030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126160189</v>
+        <v>126166521</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6066,14 +6061,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431763</v>
+        <v>432011</v>
       </c>
       <c r="R57" t="n">
-        <v>6793789</v>
+        <v>6794169</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6132,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126166337</v>
+        <v>126157375</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6163,14 +6158,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432011</v>
+        <v>431639</v>
       </c>
       <c r="R58" t="n">
-        <v>6794169</v>
+        <v>6793601</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6203,6 +6198,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6232,7 +6232,7 @@
         <v>126162207</v>
       </c>
       <c r="B59" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>126162045</v>
       </c>
       <c r="B60" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126167237</v>
+        <v>126162778</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6439,34 +6439,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432161</v>
+        <v>431921</v>
       </c>
       <c r="R61" t="n">
-        <v>6794303</v>
+        <v>6794053</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6499,11 +6504,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126166910</v>
+        <v>126165950</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,34 +6541,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432177</v>
+        <v>432011</v>
       </c>
       <c r="R62" t="n">
-        <v>6794345</v>
+        <v>6794169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126165216</v>
+        <v>126162541</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6662,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R63" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126165950</v>
+        <v>126165216</v>
       </c>
       <c r="B64" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,39 +6740,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432011</v>
+        <v>431949</v>
       </c>
       <c r="R64" t="n">
-        <v>6794169</v>
+        <v>6794232</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126162778</v>
+        <v>126166910</v>
       </c>
       <c r="B65" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,39 +6837,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431921</v>
+        <v>432177</v>
       </c>
       <c r="R65" t="n">
-        <v>6794053</v>
+        <v>6794345</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6928,10 +6923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126162541</v>
+        <v>126167107</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6963,10 +6958,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431861</v>
+        <v>432161</v>
       </c>
       <c r="R66" t="n">
-        <v>6794056</v>
+        <v>6794303</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6999,6 +6994,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126160807</v>
+        <v>126166809</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,14 +7056,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431738</v>
+        <v>432273</v>
       </c>
       <c r="R67" t="n">
-        <v>6793845</v>
+        <v>6794365</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126160381</v>
+        <v>126164027</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7133,34 +7133,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431734</v>
+        <v>431844</v>
       </c>
       <c r="R68" t="n">
-        <v>6793794</v>
+        <v>6794158</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126159369</v>
+        <v>126160807</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431635</v>
+        <v>431738</v>
       </c>
       <c r="R69" t="n">
-        <v>6793754</v>
+        <v>6793845</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7316,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126162164</v>
+        <v>126160381</v>
       </c>
       <c r="B70" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7327,34 +7327,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431783</v>
+        <v>431734</v>
       </c>
       <c r="R70" t="n">
-        <v>6794074</v>
+        <v>6793794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7413,10 +7413,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126164027</v>
+        <v>126159369</v>
       </c>
       <c r="B71" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7424,34 +7424,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431844</v>
+        <v>431635</v>
       </c>
       <c r="R71" t="n">
-        <v>6794158</v>
+        <v>6793754</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7513,7 +7513,7 @@
         <v>126165342</v>
       </c>
       <c r="B72" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126166809</v>
+        <v>126162164</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7618,21 +7618,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432273</v>
+        <v>431783</v>
       </c>
       <c r="R73" t="n">
-        <v>6794365</v>
+        <v>6794074</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7707,7 +7707,7 @@
         <v>126166708</v>
       </c>
       <c r="B74" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126161304</v>
+        <v>126159852</v>
       </c>
       <c r="B75" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431735</v>
+        <v>431733</v>
       </c>
       <c r="R75" t="n">
-        <v>6794019</v>
+        <v>6793772</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7871,12 +7871,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7906,7 +7906,7 @@
         <v>126166104</v>
       </c>
       <c r="B76" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8000,27 +8000,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126157808</v>
+        <v>126162912</v>
       </c>
       <c r="B77" t="n">
-        <v>58020</v>
+        <v>57652</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8031,19 +8031,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431582</v>
+        <v>431943</v>
       </c>
       <c r="R77" t="n">
-        <v>6793582</v>
+        <v>6794014</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8102,27 +8102,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126162912</v>
+        <v>126157808</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>58021</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8133,19 +8133,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431943</v>
+        <v>431582</v>
       </c>
       <c r="R78" t="n">
-        <v>6794014</v>
+        <v>6793582</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8204,10 +8204,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126163869</v>
+        <v>126161304</v>
       </c>
       <c r="B79" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8235,14 +8235,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431844</v>
+        <v>431735</v>
       </c>
       <c r="R79" t="n">
-        <v>6794158</v>
+        <v>6794019</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126159852</v>
+        <v>126163869</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,34 +8312,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431733</v>
+        <v>431844</v>
       </c>
       <c r="R80" t="n">
-        <v>6793772</v>
+        <v>6794158</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8401,7 +8401,7 @@
         <v>126162596</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126166662</v>
+        <v>126158231</v>
       </c>
       <c r="B82" t="n">
-        <v>79561</v>
+        <v>57652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,34 +8506,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432272</v>
+        <v>431597</v>
       </c>
       <c r="R82" t="n">
-        <v>6794337</v>
+        <v>6793646</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8592,10 +8597,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126158231</v>
+        <v>126166662</v>
       </c>
       <c r="B83" t="n">
-        <v>57651</v>
+        <v>79562</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8603,39 +8608,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431597</v>
+        <v>432272</v>
       </c>
       <c r="R83" t="n">
-        <v>6793646</v>
+        <v>6794337</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8694,10 +8694,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126165131</v>
+        <v>126166691</v>
       </c>
       <c r="B84" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8705,21 +8705,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431949</v>
+        <v>432272</v>
       </c>
       <c r="R84" t="n">
-        <v>6794232</v>
+        <v>6794337</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126166691</v>
+        <v>126161478</v>
       </c>
       <c r="B85" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8822,14 +8822,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432272</v>
+        <v>431764</v>
       </c>
       <c r="R85" t="n">
-        <v>6794337</v>
+        <v>6794018</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8891,7 +8891,7 @@
         <v>126161557</v>
       </c>
       <c r="B86" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8985,10 +8985,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126161478</v>
+        <v>126165131</v>
       </c>
       <c r="B87" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8996,34 +8996,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431764</v>
+        <v>431949</v>
       </c>
       <c r="R87" t="n">
-        <v>6794018</v>
+        <v>6794232</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9085,7 +9085,7 @@
         <v>126163857</v>
       </c>
       <c r="B88" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9184,10 +9184,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126157967</v>
+        <v>126161074</v>
       </c>
       <c r="B89" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9195,21 +9195,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431581</v>
+        <v>431755</v>
       </c>
       <c r="R89" t="n">
-        <v>6793601</v>
+        <v>6793917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9281,10 +9281,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9292,21 +9292,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R90" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9381,7 +9381,7 @@
         <v>126165579</v>
       </c>
       <c r="B91" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9572,10 +9572,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126162862</v>
+        <v>126158198</v>
       </c>
       <c r="B93" t="n">
-        <v>79561</v>
+        <v>75068</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9583,34 +9583,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431942</v>
+        <v>431575</v>
       </c>
       <c r="R93" t="n">
-        <v>6794029</v>
+        <v>6793614</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9669,10 +9669,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126158198</v>
+        <v>126165247</v>
       </c>
       <c r="B94" t="n">
-        <v>75067</v>
+        <v>57649</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9680,34 +9680,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431575</v>
+        <v>431949</v>
       </c>
       <c r="R94" t="n">
-        <v>6793614</v>
+        <v>6794232</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,10 +9771,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126165247</v>
+        <v>126160693</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9797,19 +9802,19 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431949</v>
+        <v>431740</v>
       </c>
       <c r="R95" t="n">
-        <v>6794232</v>
+        <v>6793833</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9836,12 +9841,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9868,10 +9873,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126160693</v>
+        <v>126162862</v>
       </c>
       <c r="B96" t="n">
-        <v>57648</v>
+        <v>79562</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9879,39 +9884,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431740</v>
+        <v>431942</v>
       </c>
       <c r="R96" t="n">
-        <v>6793833</v>
+        <v>6794029</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9938,12 +9938,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9973,7 +9973,7 @@
         <v>126161159</v>
       </c>
       <c r="B97" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>126161358</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>126162110</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>126160792</v>
       </c>
       <c r="B100" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>126160826</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126162464</v>
+        <v>126163938</v>
       </c>
       <c r="B102" t="n">
-        <v>57648</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,39 +10466,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431861</v>
+        <v>431844</v>
       </c>
       <c r="R102" t="n">
-        <v>6794056</v>
+        <v>6794158</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10557,10 +10552,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126159604</v>
+        <v>126162464</v>
       </c>
       <c r="B103" t="n">
-        <v>79561</v>
+        <v>57649</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10568,34 +10563,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431657</v>
+        <v>431861</v>
       </c>
       <c r="R103" t="n">
-        <v>6793728</v>
+        <v>6794056</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10654,10 +10654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126163938</v>
+        <v>126159604</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10665,34 +10665,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431844</v>
+        <v>431657</v>
       </c>
       <c r="R104" t="n">
-        <v>6794158</v>
+        <v>6793728</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126160391</v>
+        <v>126162132</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10782,14 +10782,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431718</v>
+        <v>431783</v>
       </c>
       <c r="R105" t="n">
-        <v>6793795</v>
+        <v>6794074</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126160368</v>
+        <v>126160965</v>
       </c>
       <c r="B106" t="n">
-        <v>75067</v>
+        <v>79591</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10859,21 +10859,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431734</v>
+        <v>431763</v>
       </c>
       <c r="R106" t="n">
-        <v>6793794</v>
+        <v>6793869</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10945,10 +10945,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126160965</v>
+        <v>126160391</v>
       </c>
       <c r="B107" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10956,21 +10956,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431763</v>
+        <v>431718</v>
       </c>
       <c r="R107" t="n">
-        <v>6793869</v>
+        <v>6793795</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11042,10 +11042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126162132</v>
+        <v>126164968</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11053,21 +11053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431783</v>
+        <v>431934</v>
       </c>
       <c r="R108" t="n">
-        <v>6794074</v>
+        <v>6794246</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11139,10 +11139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126164968</v>
+        <v>126160368</v>
       </c>
       <c r="B109" t="n">
-        <v>79590</v>
+        <v>75068</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11150,34 +11150,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431934</v>
+        <v>431734</v>
       </c>
       <c r="R109" t="n">
-        <v>6794246</v>
+        <v>6793794</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11239,7 +11239,7 @@
         <v>126166906</v>
       </c>
       <c r="B110" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>126167341</v>
       </c>
       <c r="B111" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>126161563</v>
       </c>
       <c r="B112" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>126162496</v>
       </c>
       <c r="B113" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>126160295</v>
       </c>
       <c r="B114" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11731,57 +11731,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126167440</v>
+        <v>126190532</v>
       </c>
       <c r="B115" t="n">
-        <v>97217</v>
+        <v>57649</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431667</v>
+        <v>431671</v>
       </c>
       <c r="R115" t="n">
-        <v>6793982</v>
+        <v>6793831</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11813,7 +11809,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11823,12 +11819,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11837,7 +11828,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -11849,60 +11839,64 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126190532</v>
+        <v>126167440</v>
       </c>
       <c r="B116" t="n">
-        <v>57648</v>
+        <v>97219</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431671</v>
+        <v>431667</v>
       </c>
       <c r="R116" t="n">
-        <v>6793831</v>
+        <v>6793982</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11934,7 +11928,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -11944,7 +11938,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11953,6 +11952,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -11964,17 +11964,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126162009</v>
+        <v>126189457</v>
       </c>
       <c r="B117" t="n">
-        <v>78730</v>
+        <v>79005</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12005,14 +12005,14 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431754</v>
+        <v>431586</v>
       </c>
       <c r="R117" t="n">
-        <v>6794068</v>
+        <v>6793587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12085,7 +12085,7 @@
         <v>126188368</v>
       </c>
       <c r="B118" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12198,10 +12198,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126189457</v>
+        <v>126162009</v>
       </c>
       <c r="B119" t="n">
-        <v>79004</v>
+        <v>78731</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12209,21 +12209,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12232,14 +12232,14 @@
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431586</v>
+        <v>431754</v>
       </c>
       <c r="R119" t="n">
-        <v>6793587</v>
+        <v>6794068</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12312,7 +12312,7 @@
         <v>126190428</v>
       </c>
       <c r="B120" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12542,41 +12542,43 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126174681</v>
+        <v>126174973</v>
       </c>
       <c r="B122" t="n">
-        <v>79561</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -12584,10 +12586,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431802</v>
+        <v>432045</v>
       </c>
       <c r="R122" t="n">
-        <v>6794020</v>
+        <v>6794330</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12647,54 +12649,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126174973</v>
+        <v>126161529</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>432045</v>
+        <v>431705</v>
       </c>
       <c r="R123" t="n">
-        <v>6794330</v>
+        <v>6794050</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12724,40 +12717,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126161529</v>
+        <v>126174681</v>
       </c>
       <c r="B124" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12765,34 +12767,41 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431705</v>
+        <v>431802</v>
       </c>
       <c r="R124" t="n">
-        <v>6794050</v>
+        <v>6794020</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12822,49 +12831,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126175046</v>
+        <v>126174513</v>
       </c>
       <c r="B125" t="n">
-        <v>79561</v>
+        <v>79591</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12872,21 +12872,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>432130</v>
+        <v>431721</v>
       </c>
       <c r="R125" t="n">
-        <v>6794314</v>
+        <v>6793745</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12966,10 +12966,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126174513</v>
+        <v>126174710</v>
       </c>
       <c r="B126" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431721</v>
+        <v>431847</v>
       </c>
       <c r="R126" t="n">
-        <v>6793745</v>
+        <v>6794063</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13071,10 +13071,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126174710</v>
+        <v>126190566</v>
       </c>
       <c r="B127" t="n">
-        <v>79590</v>
+        <v>57649</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13082,41 +13082,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431847</v>
+        <v>431683</v>
       </c>
       <c r="R127" t="n">
-        <v>6794063</v>
+        <v>6793850</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13146,40 +13147,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126190566</v>
+        <v>126175046</v>
       </c>
       <c r="B128" t="n">
-        <v>57648</v>
+        <v>79562</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13187,42 +13197,41 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431683</v>
+        <v>432130</v>
       </c>
       <c r="R128" t="n">
-        <v>6793850</v>
+        <v>6794314</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13252,39 +13261,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13401,7 +13401,7 @@
         <v>126190620</v>
       </c>
       <c r="B130" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13513,52 +13513,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126174983</v>
+        <v>126165489</v>
       </c>
       <c r="B131" t="n">
-        <v>79590</v>
+        <v>56844</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>432144</v>
+        <v>432050</v>
       </c>
       <c r="R131" t="n">
-        <v>6794303</v>
+        <v>6794210</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13588,30 +13589,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning, fjolårets, på stubbe</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13621,7 +13636,7 @@
         <v>126165849</v>
       </c>
       <c r="B132" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13738,53 +13753,52 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126165489</v>
+        <v>126174983</v>
       </c>
       <c r="B133" t="n">
-        <v>56843</v>
+        <v>79591</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>432050</v>
+        <v>432144</v>
       </c>
       <c r="R133" t="n">
-        <v>6794210</v>
+        <v>6794303</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13814,44 +13828,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning, fjolårets, på stubbe</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
         <v>126162531</v>
       </c>
       <c r="B134" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13965,52 +13965,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126174545</v>
+        <v>126189221</v>
       </c>
       <c r="B135" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431721</v>
+        <v>431686</v>
       </c>
       <c r="R135" t="n">
-        <v>6793766</v>
+        <v>6793927</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14040,9 +14038,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14058,62 +14066,64 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126189221</v>
+        <v>126174545</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431686</v>
+        <v>431721</v>
       </c>
       <c r="R136" t="n">
-        <v>6793927</v>
+        <v>6793766</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14143,19 +14153,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14171,22 +14171,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126188380</v>
+        <v>126167010</v>
       </c>
       <c r="B137" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14212,19 +14212,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431700</v>
+        <v>432026</v>
       </c>
       <c r="R137" t="n">
-        <v>6793865</v>
+        <v>6794333</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14256,7 +14253,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14266,12 +14263,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Massor</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14280,7 +14272,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14299,10 +14290,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126167010</v>
+        <v>126188380</v>
       </c>
       <c r="B138" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14328,16 +14319,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>432026</v>
+        <v>431700</v>
       </c>
       <c r="R138" t="n">
-        <v>6794333</v>
+        <v>6793865</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14369,7 +14363,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14379,7 +14373,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14388,6 +14387,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14406,10 +14406,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126165527</v>
+        <v>126162062</v>
       </c>
       <c r="B139" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14417,37 +14417,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>432037</v>
+        <v>431788</v>
       </c>
       <c r="R139" t="n">
-        <v>6794186</v>
+        <v>6794108</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14479,7 +14476,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14489,7 +14486,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14498,7 +14495,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14517,10 +14513,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126162062</v>
+        <v>126165527</v>
       </c>
       <c r="B140" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14528,34 +14524,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431788</v>
+        <v>432037</v>
       </c>
       <c r="R140" t="n">
-        <v>6794108</v>
+        <v>6794186</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14587,7 +14586,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14597,7 +14596,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14606,6 +14605,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>126189975</v>
       </c>
       <c r="B141" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14848,27 +14848,27 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126190225</v>
+        <v>126190276</v>
       </c>
       <c r="B143" t="n">
-        <v>56843</v>
+        <v>56228</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -14876,11 +14876,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
@@ -14891,14 +14887,14 @@
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431908</v>
+        <v>431609</v>
       </c>
       <c r="R143" t="n">
-        <v>6794091</v>
+        <v>6793764</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14930,7 +14926,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -14940,7 +14936,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14960,34 +14956,34 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126190276</v>
+        <v>126190225</v>
       </c>
       <c r="B144" t="n">
-        <v>56227</v>
+        <v>56844</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -14995,7 +14991,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
@@ -15006,14 +15006,14 @@
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431609</v>
+        <v>431908</v>
       </c>
       <c r="R144" t="n">
-        <v>6793764</v>
+        <v>6794091</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15075,17 +15075,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126174674</v>
+        <v>126188589</v>
       </c>
       <c r="B145" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15093,41 +15093,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431802</v>
+        <v>431672</v>
       </c>
       <c r="R145" t="n">
-        <v>6794020</v>
+        <v>6794047</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15157,9 +15153,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15175,22 +15186,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126188869</v>
+        <v>126188441</v>
       </c>
       <c r="B146" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15198,21 +15209,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15225,10 +15236,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431661</v>
+        <v>431692</v>
       </c>
       <c r="R146" t="n">
-        <v>6793741</v>
+        <v>6793928</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15260,7 +15271,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15270,7 +15281,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15298,10 +15309,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126188441</v>
+        <v>126188869</v>
       </c>
       <c r="B147" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15309,21 +15320,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15336,10 +15347,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431692</v>
+        <v>431661</v>
       </c>
       <c r="R147" t="n">
-        <v>6793928</v>
+        <v>6793741</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15371,7 +15382,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15381,7 +15392,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15409,10 +15420,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126188589</v>
+        <v>126174674</v>
       </c>
       <c r="B148" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15420,37 +15431,41 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431672</v>
+        <v>431802</v>
       </c>
       <c r="R148" t="n">
-        <v>6794047</v>
+        <v>6794020</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,24 +15495,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15513,60 +15513,69 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126174633</v>
+        <v>126190311</v>
       </c>
       <c r="B149" t="n">
-        <v>79561</v>
+        <v>97219</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431765</v>
+        <v>431597</v>
       </c>
       <c r="R149" t="n">
-        <v>6793901</v>
+        <v>6793607</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15596,9 +15605,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15614,12 +15633,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -15629,7 +15648,7 @@
         <v>126174664</v>
       </c>
       <c r="B150" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15731,10 +15750,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126161782</v>
+        <v>126174633</v>
       </c>
       <c r="B151" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15742,21 +15761,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15765,14 +15784,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431721</v>
+        <v>431765</v>
       </c>
       <c r="R151" t="n">
-        <v>6794089</v>
+        <v>6793901</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15802,19 +15821,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15830,22 +15839,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126189837</v>
+        <v>126161782</v>
       </c>
       <c r="B152" t="n">
-        <v>57651</v>
+        <v>78732</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15853,46 +15862,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>431661</v>
+        <v>431721</v>
       </c>
       <c r="R152" t="n">
-        <v>6793926</v>
+        <v>6794089</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -15934,12 +15934,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15948,6 +15943,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15959,53 +15955,53 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126190311</v>
+        <v>126189837</v>
       </c>
       <c r="B153" t="n">
-        <v>97217</v>
+        <v>57652</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16013,10 +16009,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431597</v>
+        <v>431661</v>
       </c>
       <c r="R153" t="n">
-        <v>6793607</v>
+        <v>6793926</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16048,7 +16044,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16058,7 +16054,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16067,7 +16068,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16079,17 +16079,17 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126175021</v>
+        <v>126185018</v>
       </c>
       <c r="B154" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16097,28 +16097,24 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
@@ -16128,10 +16124,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>432130</v>
+        <v>431898</v>
       </c>
       <c r="R154" t="n">
-        <v>6794314</v>
+        <v>6794103</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16161,9 +16157,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16179,22 +16185,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126174690</v>
+        <v>126175021</v>
       </c>
       <c r="B155" t="n">
-        <v>79561</v>
+        <v>79591</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16202,21 +16208,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -16233,10 +16239,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431789</v>
+        <v>432130</v>
       </c>
       <c r="R155" t="n">
-        <v>6794033</v>
+        <v>6794314</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16296,32 +16302,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126165721</v>
+        <v>126188626</v>
       </c>
       <c r="B156" t="n">
-        <v>56843</v>
+        <v>57649</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16329,20 +16335,20 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>432067</v>
+        <v>431672</v>
       </c>
       <c r="R156" t="n">
-        <v>6794181</v>
+        <v>6794047</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16374,7 +16380,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16384,12 +16390,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hästmyror i stubben</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16416,48 +16422,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126185018</v>
+        <v>126165721</v>
       </c>
       <c r="B157" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>431898</v>
+        <v>432067</v>
       </c>
       <c r="R157" t="n">
-        <v>6794103</v>
+        <v>6794181</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,7 +16500,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16499,7 +16510,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16508,7 +16524,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16530,7 +16545,7 @@
         <v>126165414</v>
       </c>
       <c r="B158" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16647,10 +16662,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126188626</v>
+        <v>126174690</v>
       </c>
       <c r="B159" t="n">
-        <v>57648</v>
+        <v>79562</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16658,42 +16673,41 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>431672</v>
+        <v>431789</v>
       </c>
       <c r="R159" t="n">
-        <v>6794047</v>
+        <v>6794033</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16723,44 +16737,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Hästmyror i stubben</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16770,7 +16770,7 @@
         <v>126190467</v>
       </c>
       <c r="B160" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16878,10 +16878,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126174574</v>
+        <v>126174924</v>
       </c>
       <c r="B161" t="n">
-        <v>79590</v>
+        <v>79005</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16889,21 +16889,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -16920,10 +16920,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>431765</v>
+        <v>431893</v>
       </c>
       <c r="R161" t="n">
-        <v>6793901</v>
+        <v>6794043</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16956,6 +16956,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16983,10 +16988,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126174924</v>
+        <v>126174574</v>
       </c>
       <c r="B162" t="n">
-        <v>79004</v>
+        <v>79591</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16994,21 +16999,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -17025,10 +17030,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>431893</v>
+        <v>431765</v>
       </c>
       <c r="R162" t="n">
-        <v>6794043</v>
+        <v>6793901</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17061,11 +17066,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17093,57 +17093,48 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126188337</v>
+        <v>126189054</v>
       </c>
       <c r="B163" t="n">
-        <v>98256</v>
+        <v>79591</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>431609</v>
+        <v>431660</v>
       </c>
       <c r="R163" t="n">
-        <v>6793762</v>
+        <v>6793737</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17175,7 +17166,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17185,7 +17176,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17206,55 +17197,64 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126189054</v>
+        <v>126188337</v>
       </c>
       <c r="B164" t="n">
-        <v>79590</v>
+        <v>98258</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>431660</v>
+        <v>431609</v>
       </c>
       <c r="R164" t="n">
-        <v>6793737</v>
+        <v>6793762</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17327,7 +17327,7 @@
         <v>126174961</v>
       </c>
       <c r="B165" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17429,54 +17429,53 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126174659</v>
+        <v>126165393</v>
       </c>
       <c r="B166" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431731</v>
+        <v>432012</v>
       </c>
       <c r="R166" t="n">
-        <v>6793834</v>
+        <v>6794220</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17506,57 +17505,66 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126165393</v>
+        <v>126162636</v>
       </c>
       <c r="B167" t="n">
-        <v>57648</v>
+        <v>58021</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -17567,11 +17575,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -17579,10 +17583,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>432012</v>
+        <v>431906</v>
       </c>
       <c r="R167" t="n">
-        <v>6794220</v>
+        <v>6794099</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17614,7 +17618,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17624,7 +17628,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17651,10 +17660,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126162636</v>
+        <v>126174659</v>
       </c>
       <c r="B168" t="n">
-        <v>58020</v>
+        <v>8447</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17662,38 +17671,43 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431906</v>
+        <v>431731</v>
       </c>
       <c r="R168" t="n">
-        <v>6794099</v>
+        <v>6793834</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17723,44 +17737,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -17770,7 +17770,7 @@
         <v>126166368</v>
       </c>
       <c r="B169" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17882,56 +17882,52 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126165703</v>
+        <v>126174682</v>
       </c>
       <c r="B170" t="n">
-        <v>92522</v>
+        <v>79591</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>432067</v>
+        <v>431789</v>
       </c>
       <c r="R170" t="n">
-        <v>6794181</v>
+        <v>6794033</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17961,24 +17957,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17994,57 +17975,68 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126165571</v>
+        <v>126165703</v>
       </c>
       <c r="B171" t="n">
-        <v>78731</v>
+        <v>92524</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>432034</v>
+        <v>432067</v>
       </c>
       <c r="R171" t="n">
-        <v>6794182</v>
+        <v>6794181</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18076,7 +18068,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18086,7 +18078,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18095,6 +18092,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18106,17 +18104,17 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126174682</v>
+        <v>126165571</v>
       </c>
       <c r="B172" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18124,41 +18122,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>431789</v>
+        <v>432034</v>
       </c>
       <c r="R172" t="n">
-        <v>6794033</v>
+        <v>6794182</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18188,30 +18179,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
@@ -18221,7 +18221,7 @@
         <v>126192573</v>
       </c>
       <c r="B173" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>126189897</v>
       </c>
       <c r="B174" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18453,52 +18453,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126174557</v>
+        <v>126188293</v>
       </c>
       <c r="B175" t="n">
-        <v>79590</v>
+        <v>5176</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>431730</v>
+        <v>431642</v>
       </c>
       <c r="R175" t="n">
-        <v>6793838</v>
+        <v>6794010</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,9 +18526,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18546,22 +18554,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126174530</v>
+        <v>126162572</v>
       </c>
       <c r="B176" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18569,41 +18577,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>431675</v>
+        <v>431906</v>
       </c>
       <c r="R176" t="n">
-        <v>6793721</v>
+        <v>6794099</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18633,9 +18637,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18651,22 +18670,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126162572</v>
+        <v>126174530</v>
       </c>
       <c r="B177" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18674,37 +18693,41 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431906</v>
+        <v>431675</v>
       </c>
       <c r="R177" t="n">
-        <v>6794099</v>
+        <v>6793721</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,24 +18757,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18767,62 +18775,64 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126188293</v>
+        <v>126174557</v>
       </c>
       <c r="B178" t="n">
-        <v>5176</v>
+        <v>79591</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>431642</v>
+        <v>431730</v>
       </c>
       <c r="R178" t="n">
-        <v>6794010</v>
+        <v>6793838</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18852,19 +18862,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18880,12 +18880,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -18895,7 +18895,7 @@
         <v>126167044</v>
       </c>
       <c r="B179" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022264</v>
+        <v>126022260</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431780</v>
+        <v>431805</v>
       </c>
       <c r="R7" t="n">
-        <v>6793497</v>
+        <v>6793440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022240</v>
+        <v>126022264</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431829</v>
+        <v>431780</v>
       </c>
       <c r="R8" t="n">
-        <v>6793466</v>
+        <v>6793497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126022260</v>
+        <v>126022240</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431805</v>
+        <v>431829</v>
       </c>
       <c r="R9" t="n">
-        <v>6793440</v>
+        <v>6793466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R17" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B18" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R18" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4463,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126165832</v>
+        <v>126167392</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432011</v>
+        <v>431653</v>
       </c>
       <c r="R41" t="n">
-        <v>6794169</v>
+        <v>6793960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4534,6 +4534,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4560,10 +4565,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126164975</v>
+        <v>126162274</v>
       </c>
       <c r="B42" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4571,21 +4576,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431934</v>
+        <v>431815</v>
       </c>
       <c r="R42" t="n">
-        <v>6794246</v>
+        <v>6794067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,10 +4662,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126165872</v>
+        <v>126162811</v>
       </c>
       <c r="B43" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4668,21 +4673,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432011</v>
+        <v>431942</v>
       </c>
       <c r="R43" t="n">
-        <v>6794169</v>
+        <v>6794029</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4754,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126166682</v>
+        <v>126156950</v>
       </c>
       <c r="B44" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,34 +4770,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432272</v>
+        <v>431647</v>
       </c>
       <c r="R44" t="n">
-        <v>6794337</v>
+        <v>6793602</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4851,7 +4856,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126167392</v>
+        <v>126159534</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4882,14 +4887,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431653</v>
+        <v>431657</v>
       </c>
       <c r="R45" t="n">
-        <v>6793960</v>
+        <v>6793728</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4922,11 +4927,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126162274</v>
+        <v>126161498</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4964,34 +4964,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431815</v>
+        <v>431776</v>
       </c>
       <c r="R46" t="n">
-        <v>6794067</v>
+        <v>6794017</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5050,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126162811</v>
+        <v>126165020</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5061,34 +5066,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431942</v>
+        <v>431934</v>
       </c>
       <c r="R47" t="n">
-        <v>6794029</v>
+        <v>6794246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5147,45 +5157,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126156950</v>
+        <v>126165832</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431647</v>
+        <v>432011</v>
       </c>
       <c r="R48" t="n">
-        <v>6793602</v>
+        <v>6794169</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5244,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126159534</v>
+        <v>126164975</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5255,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431657</v>
+        <v>431934</v>
       </c>
       <c r="R49" t="n">
-        <v>6793728</v>
+        <v>6794246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5341,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126161498</v>
+        <v>126165872</v>
       </c>
       <c r="B50" t="n">
-        <v>57649</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5352,39 +5362,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431776</v>
+        <v>432011</v>
       </c>
       <c r="R50" t="n">
-        <v>6794017</v>
+        <v>6794169</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5443,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126165020</v>
+        <v>126166682</v>
       </c>
       <c r="B51" t="n">
-        <v>57649</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5454,39 +5459,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431934</v>
+        <v>432272</v>
       </c>
       <c r="R51" t="n">
-        <v>6794246</v>
+        <v>6794337</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126162596</v>
+        <v>126158231</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,34 +8409,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431888</v>
+        <v>431597</v>
       </c>
       <c r="R81" t="n">
-        <v>6794051</v>
+        <v>6793646</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8495,10 +8500,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126158231</v>
+        <v>126166662</v>
       </c>
       <c r="B82" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,39 +8511,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431597</v>
+        <v>432272</v>
       </c>
       <c r="R82" t="n">
-        <v>6793646</v>
+        <v>6794337</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126166662</v>
+        <v>126162596</v>
       </c>
       <c r="B83" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432272</v>
+        <v>431888</v>
       </c>
       <c r="R83" t="n">
-        <v>6794337</v>
+        <v>6794051</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126189457</v>
+        <v>126188368</v>
       </c>
       <c r="B117" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431586</v>
+        <v>431698</v>
       </c>
       <c r="R117" t="n">
-        <v>6793587</v>
+        <v>6793851</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12054,7 +12054,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12075,17 +12080,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126188368</v>
+        <v>126162009</v>
       </c>
       <c r="B118" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12093,21 +12098,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12116,14 +12121,14 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431698</v>
+        <v>431754</v>
       </c>
       <c r="R118" t="n">
-        <v>6793851</v>
+        <v>6794068</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12155,7 +12160,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12165,12 +12170,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Fullt på träden</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126162009</v>
+        <v>126190428</v>
       </c>
       <c r="B119" t="n">
-        <v>78731</v>
+        <v>57649</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12209,37 +12209,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431754</v>
+        <v>431652</v>
       </c>
       <c r="R119" t="n">
-        <v>6794068</v>
+        <v>6793771</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12271,7 +12276,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12281,7 +12286,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12290,7 +12295,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12302,17 +12306,17 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126190428</v>
+        <v>126189457</v>
       </c>
       <c r="B120" t="n">
-        <v>57649</v>
+        <v>79005</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12320,31 +12324,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12352,10 +12351,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431652</v>
+        <v>431586</v>
       </c>
       <c r="R120" t="n">
-        <v>6793771</v>
+        <v>6793587</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12387,7 +12386,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12397,7 +12396,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12406,6 +12405,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13291,45 +13291,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B129" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R129" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13361,7 +13369,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13371,7 +13379,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13398,53 +13406,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B130" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R130" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13513,53 +13513,52 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126165489</v>
+        <v>126174983</v>
       </c>
       <c r="B131" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>432050</v>
+        <v>432144</v>
       </c>
       <c r="R131" t="n">
-        <v>6794210</v>
+        <v>6794303</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13589,51 +13588,37 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning, fjolårets, på stubbe</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126165849</v>
+        <v>126165489</v>
       </c>
       <c r="B132" t="n">
         <v>56844</v>
@@ -13666,7 +13651,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13676,10 +13661,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>432071</v>
+        <v>432050</v>
       </c>
       <c r="R132" t="n">
-        <v>6794181</v>
+        <v>6794210</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13711,7 +13696,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13721,12 +13706,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Hona? ev med kycklingar</t>
+          <t>Blåbärsspillning, fjolårets, på stubbe</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13746,59 +13731,60 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126174983</v>
+        <v>126165849</v>
       </c>
       <c r="B133" t="n">
-        <v>79591</v>
+        <v>56844</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>432144</v>
+        <v>432071</v>
       </c>
       <c r="R133" t="n">
-        <v>6794303</v>
+        <v>6794181</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13828,30 +13814,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Hona? ev med kycklingar</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -17324,10 +17324,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126174961</v>
+        <v>126165393</v>
       </c>
       <c r="B165" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17335,41 +17335,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>432073</v>
+        <v>432012</v>
       </c>
       <c r="R165" t="n">
-        <v>6794217</v>
+        <v>6794220</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17399,57 +17400,66 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126165393</v>
+        <v>126162636</v>
       </c>
       <c r="B166" t="n">
-        <v>57649</v>
+        <v>58021</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -17460,11 +17470,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17472,10 +17478,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>432012</v>
+        <v>431906</v>
       </c>
       <c r="R166" t="n">
-        <v>6794220</v>
+        <v>6794099</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17507,7 +17513,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17517,7 +17523,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17544,49 +17555,52 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126162636</v>
+        <v>126174961</v>
       </c>
       <c r="B167" t="n">
-        <v>58021</v>
+        <v>79591</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>431906</v>
+        <v>432073</v>
       </c>
       <c r="R167" t="n">
-        <v>6794099</v>
+        <v>6794217</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17616,44 +17630,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022260</v>
+        <v>126022264</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431805</v>
+        <v>431780</v>
       </c>
       <c r="R7" t="n">
-        <v>6793440</v>
+        <v>6793497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022264</v>
+        <v>126022260</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431780</v>
+        <v>431805</v>
       </c>
       <c r="R8" t="n">
-        <v>6793497</v>
+        <v>6793440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R14" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B15" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R15" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78640</v>
+        <v>79562</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R17" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R18" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022255</v>
+        <v>126022245</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431623</v>
+        <v>431788</v>
       </c>
       <c r="R20" t="n">
-        <v>6793485</v>
+        <v>6793544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022237</v>
+        <v>126022255</v>
       </c>
       <c r="B21" t="n">
         <v>78973</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431839</v>
+        <v>431623</v>
       </c>
       <c r="R21" t="n">
-        <v>6793457</v>
+        <v>6793485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022262</v>
+        <v>126022237</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431808</v>
+        <v>431839</v>
       </c>
       <c r="R22" t="n">
-        <v>6793454</v>
+        <v>6793457</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126022245</v>
+        <v>126022262</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431788</v>
+        <v>431808</v>
       </c>
       <c r="R23" t="n">
-        <v>6793544</v>
+        <v>6793454</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022263</v>
+        <v>126022252</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431802</v>
+        <v>431643</v>
       </c>
       <c r="R27" t="n">
-        <v>6793457</v>
+        <v>6793545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022252</v>
+        <v>126022263</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431643</v>
+        <v>431802</v>
       </c>
       <c r="R28" t="n">
-        <v>6793545</v>
+        <v>6793457</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126165882</v>
+        <v>126166842</v>
       </c>
       <c r="B30" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,34 +3402,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432011</v>
+        <v>432245</v>
       </c>
       <c r="R30" t="n">
-        <v>6794169</v>
+        <v>6794369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161615</v>
+        <v>126161538</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431758</v>
+        <v>431778</v>
       </c>
       <c r="R31" t="n">
-        <v>6794063</v>
+        <v>6794048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126165139</v>
+        <v>126162525</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>79562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R32" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3682,7 +3687,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126161265</v>
+        <v>126165882</v>
       </c>
       <c r="B33" t="n">
         <v>79591</v>
@@ -3713,14 +3718,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431735</v>
+        <v>432011</v>
       </c>
       <c r="R33" t="n">
-        <v>6794019</v>
+        <v>6794169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3747,12 +3752,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3876,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126159766</v>
+        <v>126165139</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,34 +3892,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431687</v>
+        <v>431949</v>
       </c>
       <c r="R35" t="n">
-        <v>6793778</v>
+        <v>6794232</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126161051</v>
+        <v>126162787</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4004,14 +4009,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431757</v>
+        <v>431921</v>
       </c>
       <c r="R36" t="n">
-        <v>6793912</v>
+        <v>6794053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4038,12 +4043,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4070,7 +4075,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126162787</v>
+        <v>126159766</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4101,14 +4106,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431921</v>
+        <v>431687</v>
       </c>
       <c r="R37" t="n">
-        <v>6794053</v>
+        <v>6793778</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126166842</v>
+        <v>126161265</v>
       </c>
       <c r="B38" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4178,39 +4183,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432245</v>
+        <v>431735</v>
       </c>
       <c r="R38" t="n">
-        <v>6794369</v>
+        <v>6794019</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126161538</v>
+        <v>126161051</v>
       </c>
       <c r="B39" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431778</v>
+        <v>431757</v>
       </c>
       <c r="R39" t="n">
-        <v>6794048</v>
+        <v>6793912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126162525</v>
+        <v>126161615</v>
       </c>
       <c r="B40" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431861</v>
+        <v>431758</v>
       </c>
       <c r="R40" t="n">
-        <v>6794056</v>
+        <v>6794063</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126167392</v>
+        <v>126156950</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4494,14 +4494,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431653</v>
+        <v>431647</v>
       </c>
       <c r="R41" t="n">
-        <v>6793960</v>
+        <v>6793602</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4534,11 +4534,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4565,7 +4560,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126162274</v>
+        <v>126167392</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4600,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431815</v>
+        <v>431653</v>
       </c>
       <c r="R42" t="n">
-        <v>6794067</v>
+        <v>6793960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126162811</v>
+        <v>126162274</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431942</v>
+        <v>431815</v>
       </c>
       <c r="R43" t="n">
-        <v>6794029</v>
+        <v>6794067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126156950</v>
+        <v>126162811</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431647</v>
+        <v>431942</v>
       </c>
       <c r="R44" t="n">
-        <v>6793602</v>
+        <v>6794029</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126161213</v>
+        <v>126162332</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5576,14 +5576,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431756</v>
+        <v>431839</v>
       </c>
       <c r="R52" t="n">
-        <v>6793994</v>
+        <v>6794073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5673,14 +5673,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R53" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5933,45 +5933,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126160189</v>
+        <v>126162045</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>58021</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431763</v>
+        <v>431758</v>
       </c>
       <c r="R56" t="n">
-        <v>6793789</v>
+        <v>6794063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6030,7 +6035,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126166521</v>
+        <v>126166337</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6127,7 +6132,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126157375</v>
+        <v>126157004</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6202,7 +6207,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6229,10 +6234,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126162207</v>
+        <v>126160189</v>
       </c>
       <c r="B59" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6240,34 +6245,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431783</v>
+        <v>431763</v>
       </c>
       <c r="R59" t="n">
-        <v>6794074</v>
+        <v>6793789</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6326,50 +6331,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126162045</v>
+        <v>126162207</v>
       </c>
       <c r="B60" t="n">
-        <v>58021</v>
+        <v>79591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431758</v>
+        <v>431783</v>
       </c>
       <c r="R60" t="n">
-        <v>6794063</v>
+        <v>6794074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126162778</v>
+        <v>126162541</v>
       </c>
       <c r="B61" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6439,39 +6439,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431921</v>
+        <v>431861</v>
       </c>
       <c r="R61" t="n">
-        <v>6794053</v>
+        <v>6794056</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6525,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126165950</v>
+        <v>126165216</v>
       </c>
       <c r="B62" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6536,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432011</v>
+        <v>431949</v>
       </c>
       <c r="R62" t="n">
-        <v>6794169</v>
+        <v>6794232</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6632,7 +6622,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126162541</v>
+        <v>126167107</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6667,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431861</v>
+        <v>432161</v>
       </c>
       <c r="R63" t="n">
-        <v>6794056</v>
+        <v>6794303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6703,6 +6693,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6729,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126165216</v>
+        <v>126162778</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,34 +6735,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431949</v>
+        <v>431921</v>
       </c>
       <c r="R64" t="n">
-        <v>6794232</v>
+        <v>6794053</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126166910</v>
+        <v>126165950</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,34 +6837,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432177</v>
+        <v>432011</v>
       </c>
       <c r="R65" t="n">
-        <v>6794345</v>
+        <v>6794169</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6923,7 +6928,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126167107</v>
+        <v>126166910</v>
       </c>
       <c r="B66" t="n">
         <v>78973</v>
@@ -6958,10 +6963,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432161</v>
+        <v>432177</v>
       </c>
       <c r="R66" t="n">
-        <v>6794303</v>
+        <v>6794345</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6994,11 +6999,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7025,7 +7025,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126166809</v>
+        <v>126159369</v>
       </c>
       <c r="B67" t="n">
         <v>78973</v>
@@ -7056,14 +7056,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432273</v>
+        <v>431635</v>
       </c>
       <c r="R67" t="n">
-        <v>6794365</v>
+        <v>6793754</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126164027</v>
+        <v>126160807</v>
       </c>
       <c r="B68" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7133,34 +7133,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431844</v>
+        <v>431738</v>
       </c>
       <c r="R68" t="n">
-        <v>6794158</v>
+        <v>6793845</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7219,7 +7219,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126160807</v>
+        <v>126160381</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431738</v>
+        <v>431734</v>
       </c>
       <c r="R69" t="n">
-        <v>6793845</v>
+        <v>6793794</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7316,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126160381</v>
+        <v>126164027</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7327,34 +7327,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431734</v>
+        <v>431844</v>
       </c>
       <c r="R70" t="n">
-        <v>6793794</v>
+        <v>6794158</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126159369</v>
+        <v>126166809</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7444,14 +7444,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431635</v>
+        <v>432273</v>
       </c>
       <c r="R71" t="n">
-        <v>6793754</v>
+        <v>6794365</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7510,10 +7510,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126165342</v>
+        <v>126166708</v>
       </c>
       <c r="B72" t="n">
-        <v>79562</v>
+        <v>57649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7521,34 +7521,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431949</v>
+        <v>432272</v>
       </c>
       <c r="R72" t="n">
-        <v>6794232</v>
+        <v>6794337</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7607,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126162164</v>
+        <v>126165342</v>
       </c>
       <c r="B73" t="n">
         <v>79562</v>
@@ -7642,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431783</v>
+        <v>431949</v>
       </c>
       <c r="R73" t="n">
-        <v>6794074</v>
+        <v>6794232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7704,10 +7709,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126166708</v>
+        <v>126162164</v>
       </c>
       <c r="B74" t="n">
-        <v>57649</v>
+        <v>79562</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7715,39 +7720,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432272</v>
+        <v>431783</v>
       </c>
       <c r="R74" t="n">
-        <v>6794337</v>
+        <v>6794074</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8000,27 +8000,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126162912</v>
+        <v>126157808</v>
       </c>
       <c r="B77" t="n">
-        <v>57652</v>
+        <v>58021</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8031,19 +8031,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431943</v>
+        <v>431582</v>
       </c>
       <c r="R77" t="n">
-        <v>6794014</v>
+        <v>6793582</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8102,50 +8102,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126157808</v>
+        <v>126161304</v>
       </c>
       <c r="B78" t="n">
-        <v>58021</v>
+        <v>79562</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431582</v>
+        <v>431735</v>
       </c>
       <c r="R78" t="n">
-        <v>6793582</v>
+        <v>6794019</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8172,12 +8167,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8204,7 +8199,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126161304</v>
+        <v>126163869</v>
       </c>
       <c r="B79" t="n">
         <v>79562</v>
@@ -8235,14 +8230,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431735</v>
+        <v>431844</v>
       </c>
       <c r="R79" t="n">
-        <v>6794019</v>
+        <v>6794158</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8269,12 +8264,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8301,10 +8296,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126163869</v>
+        <v>126162912</v>
       </c>
       <c r="B80" t="n">
-        <v>79562</v>
+        <v>57652</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,34 +8307,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431844</v>
+        <v>431943</v>
       </c>
       <c r="R80" t="n">
-        <v>6794158</v>
+        <v>6794014</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126161478</v>
+        <v>126161557</v>
       </c>
       <c r="B85" t="n">
         <v>79591</v>
@@ -8822,14 +8822,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431764</v>
+        <v>431758</v>
       </c>
       <c r="R85" t="n">
-        <v>6794018</v>
+        <v>6794063</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126161557</v>
+        <v>126161478</v>
       </c>
       <c r="B86" t="n">
         <v>79591</v>
@@ -8919,14 +8919,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431758</v>
+        <v>431764</v>
       </c>
       <c r="R86" t="n">
-        <v>6794063</v>
+        <v>6794018</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126163857</v>
+        <v>126161074</v>
       </c>
       <c r="B88" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9093,39 +9093,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431844</v>
+        <v>431755</v>
       </c>
       <c r="R88" t="n">
-        <v>6794158</v>
+        <v>6793917</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9152,12 +9147,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9184,10 +9179,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9195,21 +9190,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9219,10 +9214,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R89" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9249,12 +9244,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9281,10 +9276,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126157967</v>
+        <v>126163857</v>
       </c>
       <c r="B90" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9292,34 +9287,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431581</v>
+        <v>431844</v>
       </c>
       <c r="R90" t="n">
-        <v>6793601</v>
+        <v>6794158</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126161159</v>
+        <v>126161358</v>
       </c>
       <c r="B97" t="n">
         <v>78973</v>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431724</v>
+        <v>431735</v>
       </c>
       <c r="R97" t="n">
-        <v>6793934</v>
+        <v>6794019</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10067,7 +10067,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126161358</v>
+        <v>126161159</v>
       </c>
       <c r="B98" t="n">
         <v>78973</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431735</v>
+        <v>431724</v>
       </c>
       <c r="R98" t="n">
-        <v>6794019</v>
+        <v>6793934</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126163938</v>
+        <v>126159604</v>
       </c>
       <c r="B102" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,34 +10466,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431844</v>
+        <v>431657</v>
       </c>
       <c r="R102" t="n">
-        <v>6794158</v>
+        <v>6793728</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126162464</v>
+        <v>126163938</v>
       </c>
       <c r="B103" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10563,39 +10563,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431861</v>
+        <v>431844</v>
       </c>
       <c r="R103" t="n">
-        <v>6794056</v>
+        <v>6794158</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10654,10 +10649,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126159604</v>
+        <v>126162464</v>
       </c>
       <c r="B104" t="n">
-        <v>79562</v>
+        <v>57649</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10665,34 +10660,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431657</v>
+        <v>431861</v>
       </c>
       <c r="R104" t="n">
-        <v>6793728</v>
+        <v>6794056</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126162132</v>
+        <v>126164968</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431783</v>
+        <v>431934</v>
       </c>
       <c r="R105" t="n">
-        <v>6794074</v>
+        <v>6794246</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126160965</v>
+        <v>126167341</v>
       </c>
       <c r="B106" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10859,34 +10859,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431763</v>
+        <v>431682</v>
       </c>
       <c r="R106" t="n">
-        <v>6793869</v>
+        <v>6794066</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10913,12 +10913,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10945,7 +10950,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126160391</v>
+        <v>126162132</v>
       </c>
       <c r="B107" t="n">
         <v>78973</v>
@@ -10976,14 +10981,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431718</v>
+        <v>431783</v>
       </c>
       <c r="R107" t="n">
-        <v>6793795</v>
+        <v>6794074</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11042,10 +11047,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126164968</v>
+        <v>126160368</v>
       </c>
       <c r="B108" t="n">
-        <v>79591</v>
+        <v>75068</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11053,34 +11058,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431934</v>
+        <v>431734</v>
       </c>
       <c r="R108" t="n">
-        <v>6794246</v>
+        <v>6793794</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11139,10 +11144,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126160368</v>
+        <v>126160965</v>
       </c>
       <c r="B109" t="n">
-        <v>75068</v>
+        <v>79591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11150,21 +11155,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11174,10 +11179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431734</v>
+        <v>431763</v>
       </c>
       <c r="R109" t="n">
-        <v>6793794</v>
+        <v>6793869</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11204,12 +11209,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11239,7 +11244,7 @@
         <v>126166906</v>
       </c>
       <c r="B110" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11333,7 +11338,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126167341</v>
+        <v>126160391</v>
       </c>
       <c r="B111" t="n">
         <v>78973</v>
@@ -11364,14 +11369,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431682</v>
+        <v>431718</v>
       </c>
       <c r="R111" t="n">
-        <v>6794066</v>
+        <v>6793795</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11404,11 +11409,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11731,53 +11731,57 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126190532</v>
+        <v>126167440</v>
       </c>
       <c r="B115" t="n">
-        <v>57649</v>
+        <v>97221</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431671</v>
+        <v>431667</v>
       </c>
       <c r="R115" t="n">
-        <v>6793831</v>
+        <v>6793982</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11809,7 +11813,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11819,7 +11823,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11828,6 +11837,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -11839,64 +11849,60 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126167440</v>
+        <v>126190532</v>
       </c>
       <c r="B116" t="n">
-        <v>97219</v>
+        <v>57649</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431667</v>
+        <v>431671</v>
       </c>
       <c r="R116" t="n">
-        <v>6793982</v>
+        <v>6793831</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11928,7 +11934,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -11938,12 +11944,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11952,7 +11953,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -11964,17 +11964,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126188368</v>
+        <v>126162009</v>
       </c>
       <c r="B117" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12005,14 +12005,14 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431698</v>
+        <v>431754</v>
       </c>
       <c r="R117" t="n">
-        <v>6793851</v>
+        <v>6794068</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12054,12 +12054,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Fullt på träden</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12080,17 +12075,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126162009</v>
+        <v>126188368</v>
       </c>
       <c r="B118" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12098,21 +12093,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12121,14 +12116,14 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431754</v>
+        <v>431698</v>
       </c>
       <c r="R118" t="n">
-        <v>6794068</v>
+        <v>6793851</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12160,7 +12155,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12170,7 +12165,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126190428</v>
+        <v>126189457</v>
       </c>
       <c r="B119" t="n">
-        <v>57649</v>
+        <v>79005</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12209,31 +12209,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12241,10 +12236,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431652</v>
+        <v>431586</v>
       </c>
       <c r="R119" t="n">
-        <v>6793771</v>
+        <v>6793587</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12276,7 +12271,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12286,7 +12281,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12295,6 +12290,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12306,17 +12302,17 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126189457</v>
+        <v>126190428</v>
       </c>
       <c r="B120" t="n">
-        <v>79005</v>
+        <v>57649</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12324,26 +12320,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12351,10 +12352,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431586</v>
+        <v>431652</v>
       </c>
       <c r="R120" t="n">
-        <v>6793587</v>
+        <v>6793771</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12386,7 +12387,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12396,7 +12397,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12405,7 +12406,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12861,7 +12861,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126174513</v>
+        <v>126174710</v>
       </c>
       <c r="B125" t="n">
         <v>79591</v>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431721</v>
+        <v>431847</v>
       </c>
       <c r="R125" t="n">
-        <v>6793745</v>
+        <v>6794063</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12966,7 +12966,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126174710</v>
+        <v>126174513</v>
       </c>
       <c r="B126" t="n">
         <v>79591</v>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431847</v>
+        <v>431721</v>
       </c>
       <c r="R126" t="n">
-        <v>6794063</v>
+        <v>6793745</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13291,53 +13291,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B129" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R129" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13369,7 +13361,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13379,7 +13371,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13406,45 +13398,53 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B130" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R130" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13858,45 +13858,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126162531</v>
+        <v>126189221</v>
       </c>
       <c r="B134" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431906</v>
+        <v>431686</v>
       </c>
       <c r="R134" t="n">
-        <v>6794099</v>
+        <v>6793927</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13928,7 +13933,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -13938,7 +13943,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13947,6 +13952,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -13965,50 +13971,52 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126189221</v>
+        <v>126174545</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431686</v>
+        <v>431721</v>
       </c>
       <c r="R135" t="n">
-        <v>6793927</v>
+        <v>6793766</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14038,19 +14046,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14066,22 +14064,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126174545</v>
+        <v>126162531</v>
       </c>
       <c r="B136" t="n">
-        <v>78732</v>
+        <v>57649</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14089,41 +14087,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431721</v>
+        <v>431906</v>
       </c>
       <c r="R136" t="n">
-        <v>6793766</v>
+        <v>6794099</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14153,37 +14144,46 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126167010</v>
+        <v>126188380</v>
       </c>
       <c r="B137" t="n">
         <v>78973</v>
@@ -14212,16 +14212,19 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>432026</v>
+        <v>431700</v>
       </c>
       <c r="R137" t="n">
-        <v>6794333</v>
+        <v>6793865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14253,7 +14256,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14263,7 +14266,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14272,6 +14280,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14290,7 +14299,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126188380</v>
+        <v>126167010</v>
       </c>
       <c r="B138" t="n">
         <v>78973</v>
@@ -14319,19 +14328,16 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431700</v>
+        <v>432026</v>
       </c>
       <c r="R138" t="n">
-        <v>6793865</v>
+        <v>6794333</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14363,7 +14369,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14373,12 +14379,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Massor</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14387,7 +14388,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14406,10 +14406,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126162062</v>
+        <v>126190276</v>
       </c>
       <c r="B139" t="n">
-        <v>78973</v>
+        <v>56228</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14417,34 +14417,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431788</v>
+        <v>431609</v>
       </c>
       <c r="R139" t="n">
-        <v>6794108</v>
+        <v>6793764</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14476,7 +14484,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14486,7 +14494,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14506,44 +14514,46 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126165527</v>
+        <v>126166597</v>
       </c>
       <c r="B140" t="n">
-        <v>78731</v>
+        <v>8447</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14551,10 +14561,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>432037</v>
+        <v>432054</v>
       </c>
       <c r="R140" t="n">
-        <v>6794186</v>
+        <v>6794331</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14586,7 +14596,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14596,7 +14606,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14617,17 +14627,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126189975</v>
+        <v>126162062</v>
       </c>
       <c r="B141" t="n">
-        <v>92716</v>
+        <v>78973</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14635,37 +14645,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431647</v>
+        <v>431788</v>
       </c>
       <c r="R141" t="n">
-        <v>6794014</v>
+        <v>6794108</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14697,7 +14704,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14707,7 +14714,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14716,7 +14723,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14728,46 +14734,44 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126166597</v>
+        <v>126165527</v>
       </c>
       <c r="B142" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -14775,10 +14779,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>432054</v>
+        <v>432037</v>
       </c>
       <c r="R142" t="n">
-        <v>6794331</v>
+        <v>6794186</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14810,7 +14814,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -14820,7 +14824,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14841,17 +14845,17 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126190276</v>
+        <v>126189975</v>
       </c>
       <c r="B143" t="n">
-        <v>56228</v>
+        <v>92718</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14859,42 +14863,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>206004</v>
+        <v>2079</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431609</v>
+        <v>431647</v>
       </c>
       <c r="R143" t="n">
-        <v>6793764</v>
+        <v>6794014</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14926,7 +14925,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -14936,7 +14935,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14945,6 +14944,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15082,10 +15082,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126188589</v>
+        <v>126174674</v>
       </c>
       <c r="B145" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15093,37 +15093,41 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431672</v>
+        <v>431802</v>
       </c>
       <c r="R145" t="n">
-        <v>6794047</v>
+        <v>6794020</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15153,24 +15157,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15186,19 +15175,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126188441</v>
+        <v>126188589</v>
       </c>
       <c r="B146" t="n">
         <v>78973</v>
@@ -15236,10 +15225,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431692</v>
+        <v>431672</v>
       </c>
       <c r="R146" t="n">
-        <v>6793928</v>
+        <v>6794047</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15271,7 +15260,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15281,7 +15270,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15309,10 +15303,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126188869</v>
+        <v>126188441</v>
       </c>
       <c r="B147" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15320,21 +15314,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15347,10 +15341,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431661</v>
+        <v>431692</v>
       </c>
       <c r="R147" t="n">
-        <v>6793741</v>
+        <v>6793928</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15382,7 +15376,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15392,7 +15386,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15420,10 +15414,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126174674</v>
+        <v>126188869</v>
       </c>
       <c r="B148" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15431,41 +15425,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431802</v>
+        <v>431661</v>
       </c>
       <c r="R148" t="n">
-        <v>6794020</v>
+        <v>6793741</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15495,9 +15485,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15513,58 +15513,58 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126190311</v>
+        <v>126189837</v>
       </c>
       <c r="B149" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -15572,10 +15572,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431597</v>
+        <v>431661</v>
       </c>
       <c r="R149" t="n">
-        <v>6793607</v>
+        <v>6793926</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15617,7 +15617,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15626,7 +15631,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15638,17 +15642,17 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126174664</v>
+        <v>126174633</v>
       </c>
       <c r="B150" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15656,31 +15660,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -15688,10 +15687,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>431803</v>
+        <v>431765</v>
       </c>
       <c r="R150" t="n">
-        <v>6793998</v>
+        <v>6793901</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15732,6 +15731,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15750,10 +15750,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126174633</v>
+        <v>126161782</v>
       </c>
       <c r="B151" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15761,21 +15761,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15784,14 +15784,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431765</v>
+        <v>431721</v>
       </c>
       <c r="R151" t="n">
-        <v>6793901</v>
+        <v>6794089</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15821,9 +15821,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15839,22 +15849,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126161782</v>
+        <v>126174664</v>
       </c>
       <c r="B152" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15862,37 +15872,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>431721</v>
+        <v>431803</v>
       </c>
       <c r="R152" t="n">
-        <v>6794089</v>
+        <v>6793998</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15922,86 +15937,75 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126189837</v>
+        <v>126190311</v>
       </c>
       <c r="B153" t="n">
-        <v>57652</v>
+        <v>97221</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16009,10 +16013,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431661</v>
+        <v>431597</v>
       </c>
       <c r="R153" t="n">
-        <v>6793926</v>
+        <v>6793607</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16044,7 +16048,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16054,12 +16058,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16068,6 +16067,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16988,7 +16988,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126174574</v>
+        <v>126189054</v>
       </c>
       <c r="B162" t="n">
         <v>79591</v>
@@ -17016,24 +17016,20 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>431765</v>
+        <v>431660</v>
       </c>
       <c r="R162" t="n">
-        <v>6793901</v>
+        <v>6793737</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17063,9 +17059,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17081,19 +17087,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126189054</v>
+        <v>126174574</v>
       </c>
       <c r="B163" t="n">
         <v>79591</v>
@@ -17121,20 +17127,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>431660</v>
+        <v>431765</v>
       </c>
       <c r="R163" t="n">
-        <v>6793737</v>
+        <v>6793901</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17164,19 +17174,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17192,12 +17192,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17207,7 +17207,7 @@
         <v>126188337</v>
       </c>
       <c r="B164" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17317,34 +17317,34 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126165393</v>
+        <v>126162636</v>
       </c>
       <c r="B165" t="n">
-        <v>57649</v>
+        <v>58021</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -17355,11 +17355,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -17367,10 +17363,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>432012</v>
+        <v>431906</v>
       </c>
       <c r="R165" t="n">
-        <v>6794220</v>
+        <v>6794099</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17402,7 +17398,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17412,7 +17408,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17439,10 +17440,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126162636</v>
+        <v>126174659</v>
       </c>
       <c r="B166" t="n">
-        <v>58021</v>
+        <v>8447</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17450,38 +17451,43 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431906</v>
+        <v>431731</v>
       </c>
       <c r="R166" t="n">
-        <v>6794099</v>
+        <v>6793834</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17511,44 +17517,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -17660,54 +17652,53 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126174659</v>
+        <v>126165393</v>
       </c>
       <c r="B168" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431731</v>
+        <v>432012</v>
       </c>
       <c r="R168" t="n">
-        <v>6793834</v>
+        <v>6794220</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17737,30 +17728,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
         <v>126165703</v>
       </c>
       <c r="B171" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18218,10 +18218,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126192573</v>
+        <v>126189897</v>
       </c>
       <c r="B173" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18229,26 +18229,35 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
@@ -18256,10 +18265,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>431790</v>
+        <v>431648</v>
       </c>
       <c r="R173" t="n">
-        <v>6794069</v>
+        <v>6793779</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18291,7 +18300,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18301,7 +18310,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18310,7 +18324,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18322,17 +18335,17 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126189897</v>
+        <v>126192573</v>
       </c>
       <c r="B174" t="n">
-        <v>57652</v>
+        <v>79591</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18340,35 +18353,26 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
@@ -18376,10 +18380,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>431648</v>
+        <v>431790</v>
       </c>
       <c r="R174" t="n">
-        <v>6793779</v>
+        <v>6794069</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18411,7 +18415,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18421,12 +18425,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Hack efter tretåig hackspett i tallåga.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18435,6 +18434,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -18446,57 +18446,59 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126188293</v>
+        <v>126174530</v>
       </c>
       <c r="B175" t="n">
-        <v>5176</v>
+        <v>79591</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>431642</v>
+        <v>431675</v>
       </c>
       <c r="R175" t="n">
-        <v>6794010</v>
+        <v>6793721</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18526,19 +18528,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18554,22 +18546,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126162572</v>
+        <v>126174557</v>
       </c>
       <c r="B176" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18577,37 +18569,41 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>431906</v>
+        <v>431730</v>
       </c>
       <c r="R176" t="n">
-        <v>6794099</v>
+        <v>6793838</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18637,24 +18633,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18670,22 +18651,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126174530</v>
+        <v>126162572</v>
       </c>
       <c r="B177" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18693,41 +18674,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431675</v>
+        <v>431906</v>
       </c>
       <c r="R177" t="n">
-        <v>6793721</v>
+        <v>6794099</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18757,9 +18734,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18775,22 +18767,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126174557</v>
+        <v>126167044</v>
       </c>
       <c r="B178" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18798,41 +18790,38 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>431730</v>
+        <v>432002</v>
       </c>
       <c r="R178" t="n">
-        <v>6793838</v>
+        <v>6794336</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18862,79 +18851,89 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126167044</v>
+        <v>126188293</v>
       </c>
       <c r="B179" t="n">
-        <v>57649</v>
+        <v>5176</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>432002</v>
+        <v>431642</v>
       </c>
       <c r="R179" t="n">
-        <v>6794336</v>
+        <v>6794010</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18966,7 +18965,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -18976,7 +18975,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18985,6 +18984,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -18996,7 +18996,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Eva Löfqvist, Jakob Bowers, Peter Turander, Håkan Thenander, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126022250</v>
+        <v>126022248</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431733</v>
+        <v>431735</v>
       </c>
       <c r="R24" t="n">
-        <v>6793581</v>
+        <v>6793582</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126022242</v>
+        <v>126022250</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431819</v>
+        <v>431733</v>
       </c>
       <c r="R25" t="n">
-        <v>6793477</v>
+        <v>6793581</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022248</v>
+        <v>126022242</v>
       </c>
       <c r="B26" t="n">
         <v>78973</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431735</v>
+        <v>431819</v>
       </c>
       <c r="R26" t="n">
-        <v>6793582</v>
+        <v>6793477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5933,50 +5933,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126162045</v>
+        <v>126166337</v>
       </c>
       <c r="B56" t="n">
-        <v>58021</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431758</v>
+        <v>432011</v>
       </c>
       <c r="R56" t="n">
-        <v>6794063</v>
+        <v>6794169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6035,7 +6030,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126166337</v>
+        <v>126157004</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6066,14 +6061,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432011</v>
+        <v>431639</v>
       </c>
       <c r="R57" t="n">
-        <v>6794169</v>
+        <v>6793601</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6106,6 +6101,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6132,7 +6132,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126157004</v>
+        <v>126160189</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431639</v>
+        <v>431763</v>
       </c>
       <c r="R58" t="n">
-        <v>6793601</v>
+        <v>6793789</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6203,11 +6203,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6234,10 +6229,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126160189</v>
+        <v>126162207</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,34 +6240,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431763</v>
+        <v>431783</v>
       </c>
       <c r="R59" t="n">
-        <v>6793789</v>
+        <v>6794074</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6331,45 +6326,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126162207</v>
+        <v>126162045</v>
       </c>
       <c r="B60" t="n">
-        <v>79591</v>
+        <v>58021</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431783</v>
+        <v>431758</v>
       </c>
       <c r="R60" t="n">
-        <v>6794074</v>
+        <v>6794063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126162541</v>
+        <v>126166910</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431861</v>
+        <v>432177</v>
       </c>
       <c r="R61" t="n">
-        <v>6794056</v>
+        <v>6794345</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126165216</v>
+        <v>126162541</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R62" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6622,7 +6622,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126167107</v>
+        <v>126167237</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 60 meter</t>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6724,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126162778</v>
+        <v>126165216</v>
       </c>
       <c r="B64" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,39 +6735,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431921</v>
+        <v>431949</v>
       </c>
       <c r="R64" t="n">
-        <v>6794053</v>
+        <v>6794232</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,7 +6821,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126165950</v>
+        <v>126162778</v>
       </c>
       <c r="B65" t="n">
         <v>57649</v>
@@ -6866,10 +6861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432011</v>
+        <v>431921</v>
       </c>
       <c r="R65" t="n">
-        <v>6794169</v>
+        <v>6794053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6928,10 +6923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126166910</v>
+        <v>126165950</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6939,34 +6934,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432177</v>
+        <v>432011</v>
       </c>
       <c r="R66" t="n">
-        <v>6794345</v>
+        <v>6794169</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126158231</v>
+        <v>126162596</v>
       </c>
       <c r="B81" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,39 +8409,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431597</v>
+        <v>431888</v>
       </c>
       <c r="R81" t="n">
-        <v>6793646</v>
+        <v>6794051</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8597,10 +8592,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126162596</v>
+        <v>126158231</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8608,34 +8603,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431888</v>
+        <v>431597</v>
       </c>
       <c r="R83" t="n">
-        <v>6794051</v>
+        <v>6793646</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R88" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126157967</v>
+        <v>126161074</v>
       </c>
       <c r="B89" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431581</v>
+        <v>431755</v>
       </c>
       <c r="R89" t="n">
-        <v>6793601</v>
+        <v>6793917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9244,12 +9244,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11971,10 +11971,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126162009</v>
+        <v>126189457</v>
       </c>
       <c r="B117" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12005,14 +12005,14 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431754</v>
+        <v>431586</v>
       </c>
       <c r="R117" t="n">
-        <v>6794068</v>
+        <v>6793587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12075,17 +12075,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126188368</v>
+        <v>126162009</v>
       </c>
       <c r="B118" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12093,21 +12093,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12116,14 +12116,14 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431698</v>
+        <v>431754</v>
       </c>
       <c r="R118" t="n">
-        <v>6793851</v>
+        <v>6794068</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12165,12 +12165,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Fullt på träden</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12191,17 +12186,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126189457</v>
+        <v>126188368</v>
       </c>
       <c r="B119" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12209,21 +12204,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12236,10 +12231,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431586</v>
+        <v>431698</v>
       </c>
       <c r="R119" t="n">
-        <v>6793587</v>
+        <v>6793851</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12271,7 +12266,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12281,7 +12276,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -13858,50 +13858,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126189221</v>
+        <v>126162531</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431686</v>
+        <v>431906</v>
       </c>
       <c r="R134" t="n">
-        <v>6793927</v>
+        <v>6794099</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13933,7 +13928,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -13943,7 +13938,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13952,7 +13947,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -13971,52 +13965,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126174545</v>
+        <v>126189221</v>
       </c>
       <c r="B135" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431721</v>
+        <v>431686</v>
       </c>
       <c r="R135" t="n">
-        <v>6793766</v>
+        <v>6793927</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14046,9 +14038,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14064,22 +14066,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126162531</v>
+        <v>126174545</v>
       </c>
       <c r="B136" t="n">
-        <v>57649</v>
+        <v>78732</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14087,34 +14089,41 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431906</v>
+        <v>431721</v>
       </c>
       <c r="R136" t="n">
-        <v>6794099</v>
+        <v>6793766</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14144,39 +14153,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126189837</v>
+        <v>126174664</v>
       </c>
       <c r="B149" t="n">
         <v>57652</v>
@@ -15553,29 +15553,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431661</v>
+        <v>431803</v>
       </c>
       <c r="R149" t="n">
-        <v>6793926</v>
+        <v>6793998</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15605,24 +15601,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15637,22 +15618,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126174633</v>
+        <v>126189837</v>
       </c>
       <c r="B150" t="n">
-        <v>79562</v>
+        <v>57652</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15660,37 +15641,46 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>431765</v>
+        <v>431661</v>
       </c>
       <c r="R150" t="n">
-        <v>6793901</v>
+        <v>6793926</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15720,40 +15710,54 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126161782</v>
+        <v>126174633</v>
       </c>
       <c r="B151" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15761,21 +15765,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15784,14 +15788,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431721</v>
+        <v>431765</v>
       </c>
       <c r="R151" t="n">
-        <v>6794089</v>
+        <v>6793901</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15821,19 +15825,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15849,22 +15843,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126174664</v>
+        <v>126161782</v>
       </c>
       <c r="B152" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15872,42 +15866,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>431803</v>
+        <v>431721</v>
       </c>
       <c r="R152" t="n">
-        <v>6793998</v>
+        <v>6794089</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15937,29 +15926,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16086,10 +16086,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126185018</v>
+        <v>126174690</v>
       </c>
       <c r="B154" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16097,24 +16097,28 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
@@ -16124,10 +16128,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431898</v>
+        <v>431789</v>
       </c>
       <c r="R154" t="n">
-        <v>6794103</v>
+        <v>6794033</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16157,19 +16161,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16185,22 +16179,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126175021</v>
+        <v>126185018</v>
       </c>
       <c r="B155" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16208,28 +16202,24 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
@@ -16239,10 +16229,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>432130</v>
+        <v>431898</v>
       </c>
       <c r="R155" t="n">
-        <v>6794314</v>
+        <v>6794103</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16272,9 +16262,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16290,22 +16290,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126188626</v>
+        <v>126175021</v>
       </c>
       <c r="B156" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16313,42 +16313,41 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>431672</v>
+        <v>432130</v>
       </c>
       <c r="R156" t="n">
-        <v>6794047</v>
+        <v>6794314</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16378,76 +16377,62 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Hästmyror i stubben</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126165721</v>
+        <v>126188626</v>
       </c>
       <c r="B157" t="n">
-        <v>56844</v>
+        <v>57649</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16455,20 +16440,20 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432067</v>
+        <v>431672</v>
       </c>
       <c r="R157" t="n">
-        <v>6794181</v>
+        <v>6794047</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16500,7 +16485,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16510,12 +16495,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hästmyror i stubben</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16542,7 +16527,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126165414</v>
+        <v>126165721</v>
       </c>
       <c r="B158" t="n">
         <v>56844</v>
@@ -16585,10 +16570,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432012</v>
+        <v>432067</v>
       </c>
       <c r="R158" t="n">
-        <v>6794220</v>
+        <v>6794181</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16620,7 +16605,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16630,12 +16615,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16655,59 +16640,60 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126174690</v>
+        <v>126165414</v>
       </c>
       <c r="B159" t="n">
-        <v>79562</v>
+        <v>56844</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>431789</v>
+        <v>432012</v>
       </c>
       <c r="R159" t="n">
-        <v>6794033</v>
+        <v>6794220</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16737,30 +16723,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16878,10 +16878,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126174924</v>
+        <v>126189054</v>
       </c>
       <c r="B161" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16889,41 +16889,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>431893</v>
+        <v>431660</v>
       </c>
       <c r="R161" t="n">
-        <v>6794043</v>
+        <v>6793737</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16953,14 +16949,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16976,19 +16977,19 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126189054</v>
+        <v>126174574</v>
       </c>
       <c r="B162" t="n">
         <v>79591</v>
@@ -17016,20 +17017,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>431660</v>
+        <v>431765</v>
       </c>
       <c r="R162" t="n">
-        <v>6793737</v>
+        <v>6793901</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17059,19 +17064,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17087,22 +17082,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126174574</v>
+        <v>126174924</v>
       </c>
       <c r="B163" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17110,21 +17105,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -17141,10 +17136,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>431765</v>
+        <v>431893</v>
       </c>
       <c r="R163" t="n">
-        <v>6793901</v>
+        <v>6794043</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17177,6 +17172,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18218,10 +18218,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126189897</v>
+        <v>126192573</v>
       </c>
       <c r="B173" t="n">
-        <v>57652</v>
+        <v>79591</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18229,35 +18229,26 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
@@ -18265,10 +18256,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>431648</v>
+        <v>431790</v>
       </c>
       <c r="R173" t="n">
-        <v>6793779</v>
+        <v>6794069</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18300,7 +18291,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18310,12 +18301,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Hack efter tretåig hackspett i tallåga.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18324,6 +18310,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18335,17 +18322,17 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126192573</v>
+        <v>126189897</v>
       </c>
       <c r="B174" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18353,26 +18340,35 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
@@ -18380,10 +18376,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>431790</v>
+        <v>431648</v>
       </c>
       <c r="R174" t="n">
-        <v>6794069</v>
+        <v>6793779</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18415,7 +18411,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18425,7 +18421,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18434,7 +18435,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022264</v>
+        <v>126022260</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431780</v>
+        <v>431805</v>
       </c>
       <c r="R7" t="n">
-        <v>6793497</v>
+        <v>6793440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022260</v>
+        <v>126022264</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431805</v>
+        <v>431780</v>
       </c>
       <c r="R8" t="n">
-        <v>6793440</v>
+        <v>6793497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B14" t="n">
-        <v>78640</v>
+        <v>79562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R14" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R15" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B16" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R16" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022245</v>
+        <v>126022255</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431788</v>
+        <v>431623</v>
       </c>
       <c r="R20" t="n">
-        <v>6793544</v>
+        <v>6793485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022255</v>
+        <v>126022237</v>
       </c>
       <c r="B21" t="n">
         <v>78973</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431623</v>
+        <v>431839</v>
       </c>
       <c r="R21" t="n">
-        <v>6793485</v>
+        <v>6793457</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022237</v>
+        <v>126022262</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431839</v>
+        <v>431808</v>
       </c>
       <c r="R22" t="n">
-        <v>6793457</v>
+        <v>6793454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126022262</v>
+        <v>126022245</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431808</v>
+        <v>431788</v>
       </c>
       <c r="R23" t="n">
-        <v>6793454</v>
+        <v>6793544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126022248</v>
+        <v>126022250</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431735</v>
+        <v>431733</v>
       </c>
       <c r="R24" t="n">
-        <v>6793582</v>
+        <v>6793581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126022250</v>
+        <v>126022242</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431733</v>
+        <v>431819</v>
       </c>
       <c r="R25" t="n">
-        <v>6793581</v>
+        <v>6793477</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022242</v>
+        <v>126022248</v>
       </c>
       <c r="B26" t="n">
         <v>78973</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431819</v>
+        <v>431735</v>
       </c>
       <c r="R26" t="n">
-        <v>6793477</v>
+        <v>6793582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022252</v>
+        <v>126022263</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431643</v>
+        <v>431802</v>
       </c>
       <c r="R27" t="n">
-        <v>6793545</v>
+        <v>6793457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022263</v>
+        <v>126022252</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431802</v>
+        <v>431643</v>
       </c>
       <c r="R28" t="n">
-        <v>6793457</v>
+        <v>6793545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161538</v>
+        <v>126165882</v>
       </c>
       <c r="B31" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431778</v>
+        <v>432011</v>
       </c>
       <c r="R31" t="n">
-        <v>6794048</v>
+        <v>6794169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126162525</v>
+        <v>126161615</v>
       </c>
       <c r="B32" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431861</v>
+        <v>431758</v>
       </c>
       <c r="R32" t="n">
-        <v>6794056</v>
+        <v>6794063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126165882</v>
+        <v>126165139</v>
       </c>
       <c r="B33" t="n">
         <v>79591</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432011</v>
+        <v>431949</v>
       </c>
       <c r="R33" t="n">
-        <v>6794169</v>
+        <v>6794232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126159713</v>
+        <v>126161265</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431676</v>
+        <v>431735</v>
       </c>
       <c r="R34" t="n">
-        <v>6793755</v>
+        <v>6794019</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126165139</v>
+        <v>126159713</v>
       </c>
       <c r="B35" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,37 +3892,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431949</v>
+        <v>431676</v>
       </c>
       <c r="R35" t="n">
-        <v>6794232</v>
+        <v>6793755</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126162787</v>
+        <v>126159766</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4009,14 +4009,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431921</v>
+        <v>431687</v>
       </c>
       <c r="R36" t="n">
-        <v>6794053</v>
+        <v>6793778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126159766</v>
+        <v>126161051</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431687</v>
+        <v>431757</v>
       </c>
       <c r="R37" t="n">
-        <v>6793778</v>
+        <v>6793912</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161265</v>
+        <v>126162787</v>
       </c>
       <c r="B38" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431735</v>
+        <v>431921</v>
       </c>
       <c r="R38" t="n">
-        <v>6794019</v>
+        <v>6794053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126161051</v>
+        <v>126161538</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431757</v>
+        <v>431778</v>
       </c>
       <c r="R39" t="n">
-        <v>6793912</v>
+        <v>6794048</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126161615</v>
+        <v>126162525</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431758</v>
+        <v>431861</v>
       </c>
       <c r="R40" t="n">
-        <v>6794063</v>
+        <v>6794056</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126156950</v>
+        <v>126167392</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4494,14 +4494,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431647</v>
+        <v>431653</v>
       </c>
       <c r="R41" t="n">
-        <v>6793602</v>
+        <v>6793960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4534,6 +4534,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4560,7 +4565,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126167392</v>
+        <v>126162274</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4595,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431653</v>
+        <v>431815</v>
       </c>
       <c r="R42" t="n">
-        <v>6793960</v>
+        <v>6794067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4631,11 +4636,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126162274</v>
+        <v>126162811</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431815</v>
+        <v>431942</v>
       </c>
       <c r="R43" t="n">
-        <v>6794067</v>
+        <v>6794029</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126162811</v>
+        <v>126156950</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431942</v>
+        <v>431647</v>
       </c>
       <c r="R44" t="n">
-        <v>6794029</v>
+        <v>6793602</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126159534</v>
+        <v>126161498</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,34 +4867,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431657</v>
+        <v>431776</v>
       </c>
       <c r="R45" t="n">
-        <v>6793728</v>
+        <v>6794017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4953,7 +4958,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126161498</v>
+        <v>126165020</v>
       </c>
       <c r="B46" t="n">
         <v>57649</v>
@@ -4984,19 +4989,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431776</v>
+        <v>431934</v>
       </c>
       <c r="R46" t="n">
-        <v>6794017</v>
+        <v>6794246</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,50 +5060,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126165020</v>
+        <v>126165832</v>
       </c>
       <c r="B47" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431934</v>
+        <v>432011</v>
       </c>
       <c r="R47" t="n">
-        <v>6794246</v>
+        <v>6794169</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,45 +5157,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126165832</v>
+        <v>126159534</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432011</v>
+        <v>431657</v>
       </c>
       <c r="R48" t="n">
-        <v>6794169</v>
+        <v>6793728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126165872</v>
+        <v>126166682</v>
       </c>
       <c r="B50" t="n">
         <v>78732</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432011</v>
+        <v>432272</v>
       </c>
       <c r="R50" t="n">
-        <v>6794169</v>
+        <v>6794337</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,7 +5448,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126166682</v>
+        <v>126165872</v>
       </c>
       <c r="B51" t="n">
         <v>78732</v>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432272</v>
+        <v>432011</v>
       </c>
       <c r="R51" t="n">
-        <v>6794337</v>
+        <v>6794169</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5576,14 +5576,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R52" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126161213</v>
+        <v>126162332</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5673,14 +5673,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431756</v>
+        <v>431839</v>
       </c>
       <c r="R53" t="n">
-        <v>6793994</v>
+        <v>6794073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5933,45 +5933,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126166337</v>
+        <v>126162045</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>58021</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432011</v>
+        <v>431758</v>
       </c>
       <c r="R56" t="n">
-        <v>6794169</v>
+        <v>6794063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6030,7 +6035,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126157004</v>
+        <v>126160189</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6065,10 +6070,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431639</v>
+        <v>431763</v>
       </c>
       <c r="R57" t="n">
-        <v>6793601</v>
+        <v>6793789</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6101,11 +6106,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6132,7 +6132,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126160189</v>
+        <v>126166521</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6163,14 +6163,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431763</v>
+        <v>432011</v>
       </c>
       <c r="R58" t="n">
-        <v>6793789</v>
+        <v>6794169</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126162207</v>
+        <v>126157375</v>
       </c>
       <c r="B59" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6240,34 +6240,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431783</v>
+        <v>431639</v>
       </c>
       <c r="R59" t="n">
-        <v>6794074</v>
+        <v>6793601</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6300,6 +6300,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6326,50 +6331,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126162045</v>
+        <v>126162207</v>
       </c>
       <c r="B60" t="n">
-        <v>58021</v>
+        <v>79591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431758</v>
+        <v>431783</v>
       </c>
       <c r="R60" t="n">
-        <v>6794063</v>
+        <v>6794074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126166910</v>
+        <v>126162541</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432177</v>
+        <v>431861</v>
       </c>
       <c r="R61" t="n">
-        <v>6794345</v>
+        <v>6794056</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126162541</v>
+        <v>126165216</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431861</v>
+        <v>431949</v>
       </c>
       <c r="R62" t="n">
-        <v>6794056</v>
+        <v>6794232</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6622,7 +6622,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126167237</v>
+        <v>126166910</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432161</v>
+        <v>432177</v>
       </c>
       <c r="R63" t="n">
-        <v>6794303</v>
+        <v>6794345</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6693,11 +6693,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6724,7 +6719,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126165216</v>
+        <v>126167107</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -6759,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431949</v>
+        <v>432161</v>
       </c>
       <c r="R64" t="n">
-        <v>6794232</v>
+        <v>6794303</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6795,6 +6790,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7025,7 +7025,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126159369</v>
+        <v>126166809</v>
       </c>
       <c r="B67" t="n">
         <v>78973</v>
@@ -7056,14 +7056,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431635</v>
+        <v>432273</v>
       </c>
       <c r="R67" t="n">
-        <v>6793754</v>
+        <v>6794365</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126160807</v>
+        <v>126164027</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7133,34 +7133,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431738</v>
+        <v>431844</v>
       </c>
       <c r="R68" t="n">
-        <v>6793845</v>
+        <v>6794158</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7219,7 +7219,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126160381</v>
+        <v>126160807</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431734</v>
+        <v>431738</v>
       </c>
       <c r="R69" t="n">
-        <v>6793794</v>
+        <v>6793845</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7316,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126164027</v>
+        <v>126160381</v>
       </c>
       <c r="B70" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7327,34 +7327,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431844</v>
+        <v>431734</v>
       </c>
       <c r="R70" t="n">
-        <v>6794158</v>
+        <v>6793794</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126166809</v>
+        <v>126159369</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7444,14 +7444,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432273</v>
+        <v>431635</v>
       </c>
       <c r="R71" t="n">
-        <v>6794365</v>
+        <v>6793754</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7510,10 +7510,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126166708</v>
+        <v>126165342</v>
       </c>
       <c r="B72" t="n">
-        <v>57649</v>
+        <v>79562</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7521,39 +7521,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432272</v>
+        <v>431949</v>
       </c>
       <c r="R72" t="n">
-        <v>6794337</v>
+        <v>6794232</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7607,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126165342</v>
+        <v>126162164</v>
       </c>
       <c r="B73" t="n">
         <v>79562</v>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431949</v>
+        <v>431783</v>
       </c>
       <c r="R73" t="n">
-        <v>6794232</v>
+        <v>6794074</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,10 +7704,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126162164</v>
+        <v>126166708</v>
       </c>
       <c r="B74" t="n">
-        <v>79562</v>
+        <v>57649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7720,34 +7715,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431783</v>
+        <v>432272</v>
       </c>
       <c r="R74" t="n">
-        <v>6794074</v>
+        <v>6794337</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126159852</v>
+        <v>126162912</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431733</v>
+        <v>431943</v>
       </c>
       <c r="R75" t="n">
-        <v>6793772</v>
+        <v>6794014</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7903,10 +7908,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126166104</v>
+        <v>126159852</v>
       </c>
       <c r="B76" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7914,34 +7919,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432011</v>
+        <v>431733</v>
       </c>
       <c r="R76" t="n">
-        <v>6794169</v>
+        <v>6793772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8000,50 +8005,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126157808</v>
+        <v>126166104</v>
       </c>
       <c r="B77" t="n">
-        <v>58021</v>
+        <v>75068</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431582</v>
+        <v>432011</v>
       </c>
       <c r="R77" t="n">
-        <v>6793582</v>
+        <v>6794169</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8102,45 +8102,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126161304</v>
+        <v>126157808</v>
       </c>
       <c r="B78" t="n">
-        <v>79562</v>
+        <v>58021</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431735</v>
+        <v>431582</v>
       </c>
       <c r="R78" t="n">
-        <v>6794019</v>
+        <v>6793582</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8167,12 +8172,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8199,7 +8204,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126163869</v>
+        <v>126161304</v>
       </c>
       <c r="B79" t="n">
         <v>79562</v>
@@ -8230,14 +8235,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431844</v>
+        <v>431735</v>
       </c>
       <c r="R79" t="n">
-        <v>6794158</v>
+        <v>6794019</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8264,12 +8269,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8296,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126162912</v>
+        <v>126163869</v>
       </c>
       <c r="B80" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8307,39 +8312,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431943</v>
+        <v>431844</v>
       </c>
       <c r="R80" t="n">
-        <v>6794014</v>
+        <v>6794158</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126166662</v>
+        <v>126158231</v>
       </c>
       <c r="B82" t="n">
-        <v>79562</v>
+        <v>57652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,34 +8506,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432272</v>
+        <v>431597</v>
       </c>
       <c r="R82" t="n">
-        <v>6794337</v>
+        <v>6793646</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8592,10 +8597,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126158231</v>
+        <v>126166662</v>
       </c>
       <c r="B83" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8603,39 +8608,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431597</v>
+        <v>432272</v>
       </c>
       <c r="R83" t="n">
-        <v>6793646</v>
+        <v>6794337</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8694,10 +8694,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126166691</v>
+        <v>126165131</v>
       </c>
       <c r="B84" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8705,21 +8705,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432272</v>
+        <v>431949</v>
       </c>
       <c r="R84" t="n">
-        <v>6794337</v>
+        <v>6794232</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126161557</v>
+        <v>126166691</v>
       </c>
       <c r="B85" t="n">
         <v>79591</v>
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431758</v>
+        <v>432272</v>
       </c>
       <c r="R85" t="n">
-        <v>6794063</v>
+        <v>6794337</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8985,10 +8985,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126165131</v>
+        <v>126161557</v>
       </c>
       <c r="B87" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8996,21 +8996,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431949</v>
+        <v>431758</v>
       </c>
       <c r="R87" t="n">
-        <v>6794232</v>
+        <v>6794063</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126157967</v>
+        <v>126161074</v>
       </c>
       <c r="B88" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431581</v>
+        <v>431755</v>
       </c>
       <c r="R88" t="n">
-        <v>6793601</v>
+        <v>6793917</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R89" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9244,12 +9244,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9970,7 +9970,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126161358</v>
+        <v>126161159</v>
       </c>
       <c r="B97" t="n">
         <v>78973</v>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431735</v>
+        <v>431724</v>
       </c>
       <c r="R97" t="n">
-        <v>6794019</v>
+        <v>6793934</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10067,7 +10067,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126161159</v>
+        <v>126161358</v>
       </c>
       <c r="B98" t="n">
         <v>78973</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431724</v>
+        <v>431735</v>
       </c>
       <c r="R98" t="n">
-        <v>6793934</v>
+        <v>6794019</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126159604</v>
+        <v>126163938</v>
       </c>
       <c r="B102" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,34 +10466,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431657</v>
+        <v>431844</v>
       </c>
       <c r="R102" t="n">
-        <v>6793728</v>
+        <v>6794158</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126163938</v>
+        <v>126162464</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10563,34 +10563,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431844</v>
+        <v>431861</v>
       </c>
       <c r="R103" t="n">
-        <v>6794158</v>
+        <v>6794056</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10649,10 +10654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126162464</v>
+        <v>126159604</v>
       </c>
       <c r="B104" t="n">
-        <v>57649</v>
+        <v>79562</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10660,39 +10665,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431861</v>
+        <v>431657</v>
       </c>
       <c r="R104" t="n">
-        <v>6794056</v>
+        <v>6793728</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126164968</v>
+        <v>126166906</v>
       </c>
       <c r="B105" t="n">
-        <v>79591</v>
+        <v>91258</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431934</v>
+        <v>432177</v>
       </c>
       <c r="R105" t="n">
-        <v>6794246</v>
+        <v>6794345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10848,7 +10848,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126167341</v>
+        <v>126162132</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431682</v>
+        <v>431783</v>
       </c>
       <c r="R106" t="n">
-        <v>6794066</v>
+        <v>6794074</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10919,11 +10919,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10950,10 +10945,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126162132</v>
+        <v>126160965</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10961,34 +10956,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431783</v>
+        <v>431763</v>
       </c>
       <c r="R107" t="n">
-        <v>6794074</v>
+        <v>6793869</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11015,12 +11010,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11047,10 +11042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126160368</v>
+        <v>126160391</v>
       </c>
       <c r="B108" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11058,21 +11053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11082,10 +11077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431734</v>
+        <v>431718</v>
       </c>
       <c r="R108" t="n">
-        <v>6793794</v>
+        <v>6793795</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11144,7 +11139,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126160965</v>
+        <v>126164968</v>
       </c>
       <c r="B109" t="n">
         <v>79591</v>
@@ -11175,14 +11170,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431763</v>
+        <v>431934</v>
       </c>
       <c r="R109" t="n">
-        <v>6793869</v>
+        <v>6794246</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11209,12 +11204,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11241,10 +11236,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126166906</v>
+        <v>126160368</v>
       </c>
       <c r="B110" t="n">
-        <v>91256</v>
+        <v>75068</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11252,34 +11247,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>432177</v>
+        <v>431734</v>
       </c>
       <c r="R110" t="n">
-        <v>6794345</v>
+        <v>6793794</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11338,7 +11333,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126160391</v>
+        <v>126167341</v>
       </c>
       <c r="B111" t="n">
         <v>78973</v>
@@ -11369,14 +11364,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431718</v>
+        <v>431682</v>
       </c>
       <c r="R111" t="n">
-        <v>6793795</v>
+        <v>6794066</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11409,6 +11404,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11731,57 +11731,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126167440</v>
+        <v>126190532</v>
       </c>
       <c r="B115" t="n">
-        <v>97221</v>
+        <v>57649</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431667</v>
+        <v>431671</v>
       </c>
       <c r="R115" t="n">
-        <v>6793982</v>
+        <v>6793831</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11813,7 +11809,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11823,12 +11819,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11837,7 +11828,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -11849,60 +11839,64 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126190532</v>
+        <v>126167440</v>
       </c>
       <c r="B116" t="n">
-        <v>57649</v>
+        <v>97223</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431671</v>
+        <v>431667</v>
       </c>
       <c r="R116" t="n">
-        <v>6793831</v>
+        <v>6793982</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11934,7 +11928,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -11944,7 +11938,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11953,6 +11952,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -11964,17 +11964,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126189457</v>
+        <v>126162009</v>
       </c>
       <c r="B117" t="n">
-        <v>79005</v>
+        <v>78731</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12005,14 +12005,14 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431586</v>
+        <v>431754</v>
       </c>
       <c r="R117" t="n">
-        <v>6793587</v>
+        <v>6794068</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12075,17 +12075,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126162009</v>
+        <v>126189457</v>
       </c>
       <c r="B118" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12093,21 +12093,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12116,14 +12116,14 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431754</v>
+        <v>431586</v>
       </c>
       <c r="R118" t="n">
-        <v>6794068</v>
+        <v>6793587</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126161529</v>
+        <v>126174681</v>
       </c>
       <c r="B123" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12660,34 +12660,41 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431705</v>
+        <v>431802</v>
       </c>
       <c r="R123" t="n">
-        <v>6794050</v>
+        <v>6794020</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12717,49 +12724,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126174681</v>
+        <v>126161529</v>
       </c>
       <c r="B124" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12767,41 +12765,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431802</v>
+        <v>431705</v>
       </c>
       <c r="R124" t="n">
-        <v>6794020</v>
+        <v>6794050</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12831,37 +12822,46 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126174710</v>
+        <v>126174513</v>
       </c>
       <c r="B125" t="n">
         <v>79591</v>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431847</v>
+        <v>431721</v>
       </c>
       <c r="R125" t="n">
-        <v>6794063</v>
+        <v>6793745</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12966,7 +12966,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126174513</v>
+        <v>126174710</v>
       </c>
       <c r="B126" t="n">
         <v>79591</v>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431721</v>
+        <v>431847</v>
       </c>
       <c r="R126" t="n">
-        <v>6793745</v>
+        <v>6794063</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13071,10 +13071,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126190566</v>
+        <v>126175046</v>
       </c>
       <c r="B127" t="n">
-        <v>57649</v>
+        <v>79562</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13082,42 +13082,41 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431683</v>
+        <v>432130</v>
       </c>
       <c r="R127" t="n">
-        <v>6793850</v>
+        <v>6794314</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13147,49 +13146,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126175046</v>
+        <v>126190566</v>
       </c>
       <c r="B128" t="n">
-        <v>79562</v>
+        <v>57649</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13197,41 +13187,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>432130</v>
+        <v>431683</v>
       </c>
       <c r="R128" t="n">
-        <v>6794314</v>
+        <v>6793850</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13261,75 +13252,92 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B129" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R129" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13361,7 +13369,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13371,7 +13379,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13398,53 +13406,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B130" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R130" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13858,45 +13858,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126162531</v>
+        <v>126189221</v>
       </c>
       <c r="B134" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431906</v>
+        <v>431686</v>
       </c>
       <c r="R134" t="n">
-        <v>6794099</v>
+        <v>6793927</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13928,7 +13933,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -13938,7 +13943,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13947,6 +13952,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -13965,50 +13971,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126189221</v>
+        <v>126162531</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431686</v>
+        <v>431906</v>
       </c>
       <c r="R135" t="n">
-        <v>6793927</v>
+        <v>6794099</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14040,7 +14041,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14050,7 +14051,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14059,7 +14060,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14183,7 +14183,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126188380</v>
+        <v>126167010</v>
       </c>
       <c r="B137" t="n">
         <v>78973</v>
@@ -14212,19 +14212,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431700</v>
+        <v>432026</v>
       </c>
       <c r="R137" t="n">
-        <v>6793865</v>
+        <v>6794333</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14256,7 +14253,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14266,12 +14263,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Massor</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14280,7 +14272,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14299,7 +14290,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126167010</v>
+        <v>126188380</v>
       </c>
       <c r="B138" t="n">
         <v>78973</v>
@@ -14328,16 +14319,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>432026</v>
+        <v>431700</v>
       </c>
       <c r="R138" t="n">
-        <v>6794333</v>
+        <v>6793865</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14369,7 +14363,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14379,7 +14373,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14388,6 +14387,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14406,10 +14406,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126190276</v>
+        <v>126162062</v>
       </c>
       <c r="B139" t="n">
-        <v>56228</v>
+        <v>78973</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14417,42 +14417,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431609</v>
+        <v>431788</v>
       </c>
       <c r="R139" t="n">
-        <v>6793764</v>
+        <v>6794108</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14484,7 +14476,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14494,7 +14486,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14514,46 +14506,44 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126166597</v>
+        <v>126165527</v>
       </c>
       <c r="B140" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14561,10 +14551,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>432054</v>
+        <v>432037</v>
       </c>
       <c r="R140" t="n">
-        <v>6794331</v>
+        <v>6794186</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14596,7 +14586,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14606,7 +14596,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14627,17 +14617,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126162062</v>
+        <v>126189975</v>
       </c>
       <c r="B141" t="n">
-        <v>78973</v>
+        <v>92720</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14645,34 +14635,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431788</v>
+        <v>431647</v>
       </c>
       <c r="R141" t="n">
-        <v>6794108</v>
+        <v>6794014</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14704,7 +14697,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14714,7 +14707,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14723,6 +14716,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14734,55 +14728,64 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126165527</v>
+        <v>126190225</v>
       </c>
       <c r="B142" t="n">
-        <v>78731</v>
+        <v>56844</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>432037</v>
+        <v>431908</v>
       </c>
       <c r="R142" t="n">
-        <v>6794186</v>
+        <v>6794091</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14814,7 +14817,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -14824,7 +14827,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14833,7 +14836,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14852,48 +14854,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126189975</v>
+        <v>126166597</v>
       </c>
       <c r="B143" t="n">
-        <v>92718</v>
+        <v>8447</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431647</v>
+        <v>432054</v>
       </c>
       <c r="R143" t="n">
-        <v>6794014</v>
+        <v>6794331</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14925,7 +14929,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -14935,7 +14939,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14956,34 +14960,34 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126190225</v>
+        <v>126190276</v>
       </c>
       <c r="B144" t="n">
-        <v>56844</v>
+        <v>56228</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -14991,11 +14995,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
@@ -15006,14 +15006,14 @@
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431908</v>
+        <v>431609</v>
       </c>
       <c r="R144" t="n">
-        <v>6794091</v>
+        <v>6793764</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15075,17 +15075,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126174674</v>
+        <v>126188589</v>
       </c>
       <c r="B145" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15093,41 +15093,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431802</v>
+        <v>431672</v>
       </c>
       <c r="R145" t="n">
-        <v>6794020</v>
+        <v>6794047</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15157,9 +15153,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15175,19 +15186,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126188589</v>
+        <v>126188441</v>
       </c>
       <c r="B146" t="n">
         <v>78973</v>
@@ -15225,10 +15236,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431672</v>
+        <v>431692</v>
       </c>
       <c r="R146" t="n">
-        <v>6794047</v>
+        <v>6793928</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15260,7 +15271,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15270,12 +15281,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15303,10 +15309,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126188441</v>
+        <v>126188869</v>
       </c>
       <c r="B147" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15314,21 +15320,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15341,10 +15347,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431692</v>
+        <v>431661</v>
       </c>
       <c r="R147" t="n">
-        <v>6793928</v>
+        <v>6793741</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15376,7 +15382,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15386,7 +15392,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15414,10 +15420,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126188869</v>
+        <v>126174674</v>
       </c>
       <c r="B148" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15425,37 +15431,41 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431661</v>
+        <v>431802</v>
       </c>
       <c r="R148" t="n">
-        <v>6793741</v>
+        <v>6794020</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15485,19 +15495,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15513,22 +15513,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126174664</v>
+        <v>126174633</v>
       </c>
       <c r="B149" t="n">
-        <v>57652</v>
+        <v>79562</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15536,31 +15536,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -15568,10 +15563,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431803</v>
+        <v>431765</v>
       </c>
       <c r="R149" t="n">
-        <v>6793998</v>
+        <v>6793901</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15612,6 +15607,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15630,10 +15626,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126189837</v>
+        <v>126161782</v>
       </c>
       <c r="B150" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15641,46 +15637,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>431661</v>
+        <v>431721</v>
       </c>
       <c r="R150" t="n">
-        <v>6793926</v>
+        <v>6794089</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15712,7 +15699,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15722,12 +15709,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15736,6 +15718,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15747,55 +15730,64 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126174633</v>
+        <v>126190311</v>
       </c>
       <c r="B151" t="n">
-        <v>79562</v>
+        <v>97223</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431765</v>
+        <v>431597</v>
       </c>
       <c r="R151" t="n">
-        <v>6793901</v>
+        <v>6793607</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15825,9 +15817,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15843,22 +15845,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126161782</v>
+        <v>126174664</v>
       </c>
       <c r="B152" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15866,37 +15868,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>431721</v>
+        <v>431803</v>
       </c>
       <c r="R152" t="n">
-        <v>6794089</v>
+        <v>6793998</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15926,86 +15933,75 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126190311</v>
+        <v>126189837</v>
       </c>
       <c r="B153" t="n">
-        <v>97221</v>
+        <v>57652</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16013,10 +16009,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431597</v>
+        <v>431661</v>
       </c>
       <c r="R153" t="n">
-        <v>6793607</v>
+        <v>6793926</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16048,7 +16044,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16058,7 +16054,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16067,7 +16068,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16079,17 +16079,17 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126174690</v>
+        <v>126185018</v>
       </c>
       <c r="B154" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16097,28 +16097,24 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
@@ -16128,10 +16124,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431789</v>
+        <v>431898</v>
       </c>
       <c r="R154" t="n">
-        <v>6794033</v>
+        <v>6794103</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16161,9 +16157,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16179,22 +16185,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126185018</v>
+        <v>126175021</v>
       </c>
       <c r="B155" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16202,24 +16208,28 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
@@ -16229,10 +16239,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431898</v>
+        <v>432130</v>
       </c>
       <c r="R155" t="n">
-        <v>6794103</v>
+        <v>6794314</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16262,19 +16272,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16290,22 +16290,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126175021</v>
+        <v>126188626</v>
       </c>
       <c r="B156" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16313,41 +16313,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>432130</v>
+        <v>431672</v>
       </c>
       <c r="R156" t="n">
-        <v>6794314</v>
+        <v>6794047</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16377,62 +16378,76 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Hästmyror i stubben</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126188626</v>
+        <v>126165721</v>
       </c>
       <c r="B157" t="n">
-        <v>57649</v>
+        <v>56844</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16440,20 +16455,20 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>431672</v>
+        <v>432067</v>
       </c>
       <c r="R157" t="n">
-        <v>6794047</v>
+        <v>6794181</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16485,7 +16500,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16495,12 +16510,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Hästmyror i stubben</t>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16527,7 +16542,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126165721</v>
+        <v>126165414</v>
       </c>
       <c r="B158" t="n">
         <v>56844</v>
@@ -16570,10 +16585,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432067</v>
+        <v>432012</v>
       </c>
       <c r="R158" t="n">
-        <v>6794181</v>
+        <v>6794220</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16605,7 +16620,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16615,12 +16630,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16640,60 +16655,59 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126165414</v>
+        <v>126174690</v>
       </c>
       <c r="B159" t="n">
-        <v>56844</v>
+        <v>79562</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>432012</v>
+        <v>431789</v>
       </c>
       <c r="R159" t="n">
-        <v>6794220</v>
+        <v>6794033</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16723,44 +16737,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16878,10 +16878,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126189054</v>
+        <v>126174924</v>
       </c>
       <c r="B161" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16889,37 +16889,41 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>431660</v>
+        <v>431893</v>
       </c>
       <c r="R161" t="n">
-        <v>6793737</v>
+        <v>6794043</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16949,19 +16953,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:57</t>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16977,12 +16976,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17094,10 +17093,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126174924</v>
+        <v>126189054</v>
       </c>
       <c r="B163" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17105,41 +17104,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>431893</v>
+        <v>431660</v>
       </c>
       <c r="R163" t="n">
-        <v>6794043</v>
+        <v>6793737</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17169,14 +17164,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17192,12 +17192,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17207,7 +17207,7 @@
         <v>126188337</v>
       </c>
       <c r="B164" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17440,43 +17440,41 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126174659</v>
+        <v>126174961</v>
       </c>
       <c r="B166" t="n">
-        <v>8447</v>
+        <v>79591</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17484,10 +17482,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431731</v>
+        <v>432073</v>
       </c>
       <c r="R166" t="n">
-        <v>6793834</v>
+        <v>6794217</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17547,10 +17545,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126174961</v>
+        <v>126165393</v>
       </c>
       <c r="B167" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17558,41 +17556,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>432073</v>
+        <v>432012</v>
       </c>
       <c r="R167" t="n">
-        <v>6794217</v>
+        <v>6794220</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17622,83 +17621,93 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126165393</v>
+        <v>126174659</v>
       </c>
       <c r="B168" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>432012</v>
+        <v>431731</v>
       </c>
       <c r="R168" t="n">
-        <v>6794220</v>
+        <v>6793834</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17728,39 +17737,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -17882,52 +17882,56 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126174682</v>
+        <v>126165703</v>
       </c>
       <c r="B170" t="n">
-        <v>79591</v>
+        <v>92528</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>431789</v>
+        <v>432067</v>
       </c>
       <c r="R170" t="n">
-        <v>6794033</v>
+        <v>6794181</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17957,9 +17961,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17975,68 +17994,64 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126165703</v>
+        <v>126174682</v>
       </c>
       <c r="B171" t="n">
-        <v>92526</v>
+        <v>79591</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>432067</v>
+        <v>431789</v>
       </c>
       <c r="R171" t="n">
-        <v>6794181</v>
+        <v>6794033</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18066,24 +18081,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18099,12 +18099,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18453,10 +18453,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126174530</v>
+        <v>126162572</v>
       </c>
       <c r="B175" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18464,41 +18464,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>431675</v>
+        <v>431906</v>
       </c>
       <c r="R175" t="n">
-        <v>6793721</v>
+        <v>6794099</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18528,9 +18524,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18546,19 +18557,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126174557</v>
+        <v>126174530</v>
       </c>
       <c r="B176" t="n">
         <v>79591</v>
@@ -18600,10 +18611,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>431730</v>
+        <v>431675</v>
       </c>
       <c r="R176" t="n">
-        <v>6793838</v>
+        <v>6793721</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18663,10 +18674,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126162572</v>
+        <v>126174557</v>
       </c>
       <c r="B177" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18674,37 +18685,41 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431906</v>
+        <v>431730</v>
       </c>
       <c r="R177" t="n">
-        <v>6794099</v>
+        <v>6793838</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18734,24 +18749,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18767,12 +18767,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022251</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022241</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022243</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022253</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022256</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022260</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022264</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022240</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126022236</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126022254</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126022257</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126022238</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R14" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022246</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431785</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793548</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126022247</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126022255</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126022237</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126022262</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126022245</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126022250</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126022242</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126022248</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022263</v>
+        <v>126022252</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431802</v>
+        <v>431643</v>
       </c>
       <c r="R27" t="n">
-        <v>6793457</v>
+        <v>6793545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022252</v>
+        <v>126022263</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431643</v>
+        <v>431802</v>
       </c>
       <c r="R28" t="n">
-        <v>6793545</v>
+        <v>6793457</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>126022239</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126166842</v>
+        <v>126161538</v>
       </c>
       <c r="B30" t="n">
-        <v>57649</v>
+        <v>78736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,39 +3402,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432245</v>
+        <v>431778</v>
       </c>
       <c r="R30" t="n">
-        <v>6794369</v>
+        <v>6794048</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161615</v>
+        <v>126162525</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431758</v>
+        <v>431861</v>
       </c>
       <c r="R31" t="n">
-        <v>6794063</v>
+        <v>6794056</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126165139</v>
+        <v>126161265</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3621,14 +3616,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431949</v>
+        <v>431735</v>
       </c>
       <c r="R32" t="n">
-        <v>6794232</v>
+        <v>6794019</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3655,12 +3650,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3687,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126161265</v>
+        <v>126166842</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>57653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,34 +3693,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431735</v>
+        <v>432245</v>
       </c>
       <c r="R33" t="n">
-        <v>6794019</v>
+        <v>6794369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126159713</v>
+        <v>126161615</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3815,17 +3815,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431676</v>
+        <v>431758</v>
       </c>
       <c r="R34" t="n">
-        <v>6793755</v>
+        <v>6794063</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126159766</v>
+        <v>126159713</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3916,13 +3916,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431687</v>
+        <v>431676</v>
       </c>
       <c r="R35" t="n">
-        <v>6793778</v>
+        <v>6793755</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126161051</v>
+        <v>126159766</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431757</v>
+        <v>431687</v>
       </c>
       <c r="R36" t="n">
-        <v>6793912</v>
+        <v>6793778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4075,10 +4075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126162787</v>
+        <v>126161051</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4106,14 +4106,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431921</v>
+        <v>431757</v>
       </c>
       <c r="R37" t="n">
-        <v>6794053</v>
+        <v>6793912</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161538</v>
+        <v>126162787</v>
       </c>
       <c r="B38" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431778</v>
+        <v>431921</v>
       </c>
       <c r="R38" t="n">
-        <v>6794048</v>
+        <v>6794053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126162525</v>
+        <v>126165139</v>
       </c>
       <c r="B39" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431861</v>
+        <v>431949</v>
       </c>
       <c r="R39" t="n">
-        <v>6794056</v>
+        <v>6794232</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126167392</v>
+        <v>126164975</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431653</v>
+        <v>431934</v>
       </c>
       <c r="R40" t="n">
-        <v>6793960</v>
+        <v>6794246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4437,11 +4437,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4468,10 +4463,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126162274</v>
+        <v>126166682</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,21 +4474,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431815</v>
+        <v>432272</v>
       </c>
       <c r="R41" t="n">
-        <v>6794067</v>
+        <v>6794337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126162811</v>
+        <v>126167392</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4600,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431942</v>
+        <v>431653</v>
       </c>
       <c r="R42" t="n">
-        <v>6794029</v>
+        <v>6793960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126156950</v>
+        <v>126162274</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4693,14 +4693,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431647</v>
+        <v>431815</v>
       </c>
       <c r="R43" t="n">
-        <v>6793602</v>
+        <v>6794067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126161498</v>
+        <v>126162811</v>
       </c>
       <c r="B44" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4770,39 +4770,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431776</v>
+        <v>431942</v>
       </c>
       <c r="R44" t="n">
-        <v>6794017</v>
+        <v>6794029</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4861,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126165020</v>
+        <v>126156950</v>
       </c>
       <c r="B45" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,39 +4867,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431934</v>
+        <v>431647</v>
       </c>
       <c r="R45" t="n">
-        <v>6794246</v>
+        <v>6793602</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4966,7 +4956,7 @@
         <v>126159534</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,10 +5050,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126164975</v>
+        <v>126161498</v>
       </c>
       <c r="B47" t="n">
-        <v>79562</v>
+        <v>57653</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,34 +5061,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431934</v>
+        <v>431776</v>
       </c>
       <c r="R47" t="n">
-        <v>6794246</v>
+        <v>6794017</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126166682</v>
+        <v>126165020</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>57653</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5163,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432272</v>
+        <v>431934</v>
       </c>
       <c r="R48" t="n">
-        <v>6794337</v>
+        <v>6794246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126161213</v>
+        <v>126160760</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431756</v>
+        <v>431740</v>
       </c>
       <c r="R49" t="n">
-        <v>6793994</v>
+        <v>6793833</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5382,14 +5382,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126160760</v>
+        <v>126162332</v>
       </c>
       <c r="B51" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,34 +5459,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431740</v>
+        <v>431839</v>
       </c>
       <c r="R51" t="n">
-        <v>6793833</v>
+        <v>6794073</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5545,50 +5545,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126162045</v>
+        <v>126162207</v>
       </c>
       <c r="B52" t="n">
-        <v>58021</v>
+        <v>79595</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431758</v>
+        <v>431783</v>
       </c>
       <c r="R52" t="n">
-        <v>6794063</v>
+        <v>6794074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5650,7 +5645,7 @@
         <v>126160189</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5747,7 +5742,7 @@
         <v>126157375</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5846,45 +5841,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126162207</v>
+        <v>126162045</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>58025</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431783</v>
+        <v>431758</v>
       </c>
       <c r="R55" t="n">
-        <v>6794074</v>
+        <v>6794063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126162541</v>
+        <v>126162778</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5954,34 +5954,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431861</v>
+        <v>431921</v>
       </c>
       <c r="R56" t="n">
-        <v>6794056</v>
+        <v>6794053</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126165216</v>
+        <v>126162541</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R57" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126166910</v>
+        <v>126165216</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432177</v>
+        <v>431949</v>
       </c>
       <c r="R58" t="n">
-        <v>6794345</v>
+        <v>6794232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6234,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126167107</v>
+        <v>126166910</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6269,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432161</v>
+        <v>432177</v>
       </c>
       <c r="R59" t="n">
-        <v>6794303</v>
+        <v>6794345</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6305,11 +6310,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6336,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126162778</v>
+        <v>126167107</v>
       </c>
       <c r="B60" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6347,39 +6347,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431921</v>
+        <v>432161</v>
       </c>
       <c r="R60" t="n">
-        <v>6794053</v>
+        <v>6794303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6412,6 +6407,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126166809</v>
+        <v>126166708</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432273</v>
+        <v>432272</v>
       </c>
       <c r="R61" t="n">
-        <v>6794365</v>
+        <v>6794337</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,10 +6540,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126164027</v>
+        <v>126166809</v>
       </c>
       <c r="B62" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,21 +6551,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6575,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431844</v>
+        <v>432273</v>
       </c>
       <c r="R62" t="n">
-        <v>6794158</v>
+        <v>6794365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6635,7 +6640,7 @@
         <v>126160807</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6732,7 +6737,7 @@
         <v>126160381</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6829,7 +6834,7 @@
         <v>126159369</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6923,10 +6928,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126166708</v>
+        <v>126164027</v>
       </c>
       <c r="B66" t="n">
-        <v>57649</v>
+        <v>79595</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,39 +6939,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432272</v>
+        <v>431844</v>
       </c>
       <c r="R66" t="n">
-        <v>6794337</v>
+        <v>6794158</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7028,7 +7028,7 @@
         <v>126165342</v>
       </c>
       <c r="B67" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>126162164</v>
       </c>
       <c r="B68" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>126159852</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>126162912</v>
       </c>
       <c r="B70" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7418,45 +7418,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126161304</v>
+        <v>126157808</v>
       </c>
       <c r="B71" t="n">
-        <v>79562</v>
+        <v>58025</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431735</v>
+        <v>431582</v>
       </c>
       <c r="R71" t="n">
-        <v>6794019</v>
+        <v>6793582</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7483,12 +7488,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7515,10 +7520,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126163869</v>
+        <v>126161304</v>
       </c>
       <c r="B72" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7546,14 +7551,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431844</v>
+        <v>431735</v>
       </c>
       <c r="R72" t="n">
-        <v>6794158</v>
+        <v>6794019</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7580,12 +7585,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7612,50 +7617,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126157808</v>
+        <v>126163869</v>
       </c>
       <c r="B73" t="n">
-        <v>58021</v>
+        <v>79566</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431582</v>
+        <v>431844</v>
       </c>
       <c r="R73" t="n">
-        <v>6793582</v>
+        <v>6794158</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
         <v>126162596</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>126158231</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>126166662</v>
       </c>
       <c r="B76" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>126166691</v>
       </c>
       <c r="B77" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>126161478</v>
       </c>
       <c r="B78" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>126161557</v>
       </c>
       <c r="B79" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>126165131</v>
       </c>
       <c r="B80" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>126161074</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>126157967</v>
       </c>
       <c r="B82" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>126163857</v>
       </c>
       <c r="B83" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126160693</v>
+        <v>126158198</v>
       </c>
       <c r="B85" t="n">
-        <v>57649</v>
+        <v>75072</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8802,39 +8802,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431740</v>
+        <v>431575</v>
       </c>
       <c r="R85" t="n">
-        <v>6793833</v>
+        <v>6793614</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8861,12 +8856,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8893,10 +8888,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126162862</v>
+        <v>126165247</v>
       </c>
       <c r="B86" t="n">
-        <v>79562</v>
+        <v>57653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8904,34 +8899,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431942</v>
+        <v>431949</v>
       </c>
       <c r="R86" t="n">
-        <v>6794029</v>
+        <v>6794232</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126158198</v>
+        <v>126160693</v>
       </c>
       <c r="B87" t="n">
-        <v>75068</v>
+        <v>57653</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9001,34 +9001,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431575</v>
+        <v>431740</v>
       </c>
       <c r="R87" t="n">
-        <v>6793614</v>
+        <v>6793833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9055,12 +9060,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9087,10 +9092,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126165247</v>
+        <v>126162862</v>
       </c>
       <c r="B88" t="n">
-        <v>57649</v>
+        <v>79566</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9098,39 +9103,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431949</v>
+        <v>431942</v>
       </c>
       <c r="R88" t="n">
-        <v>6794232</v>
+        <v>6794029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9192,7 +9192,7 @@
         <v>126161159</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>126161358</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>126162110</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>126160792</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>126160826</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>126163938</v>
       </c>
       <c r="B94" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>126162464</v>
       </c>
       <c r="B95" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>126159604</v>
       </c>
       <c r="B96" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126166906</v>
+        <v>126160965</v>
       </c>
       <c r="B97" t="n">
-        <v>91258</v>
+        <v>79595</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9981,34 +9981,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>432177</v>
+        <v>431763</v>
       </c>
       <c r="R97" t="n">
-        <v>6794345</v>
+        <v>6793869</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10035,12 +10035,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10067,10 +10067,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126162132</v>
+        <v>126164968</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10078,21 +10078,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431783</v>
+        <v>431934</v>
       </c>
       <c r="R98" t="n">
-        <v>6794074</v>
+        <v>6794246</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10164,10 +10164,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126160965</v>
+        <v>126162132</v>
       </c>
       <c r="B99" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10175,34 +10175,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431763</v>
+        <v>431783</v>
       </c>
       <c r="R99" t="n">
-        <v>6793869</v>
+        <v>6794074</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10264,7 +10264,7 @@
         <v>126160391</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10358,10 +10358,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126164968</v>
+        <v>126160368</v>
       </c>
       <c r="B101" t="n">
-        <v>79591</v>
+        <v>75072</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10369,34 +10369,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431934</v>
+        <v>431734</v>
       </c>
       <c r="R101" t="n">
-        <v>6794246</v>
+        <v>6793794</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126160368</v>
+        <v>126166906</v>
       </c>
       <c r="B102" t="n">
-        <v>75068</v>
+        <v>91262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,34 +10466,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431734</v>
+        <v>432177</v>
       </c>
       <c r="R102" t="n">
-        <v>6793794</v>
+        <v>6794345</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10555,7 +10555,7 @@
         <v>126167341</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>126161563</v>
       </c>
       <c r="B104" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126162496</v>
+        <v>126160295</v>
       </c>
       <c r="B105" t="n">
-        <v>79591</v>
+        <v>57653</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10762,34 +10762,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431861</v>
+        <v>431734</v>
       </c>
       <c r="R105" t="n">
-        <v>6794056</v>
+        <v>6793794</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10848,10 +10853,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126160295</v>
+        <v>126162496</v>
       </c>
       <c r="B106" t="n">
-        <v>57649</v>
+        <v>79595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10859,39 +10864,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431734</v>
+        <v>431861</v>
       </c>
       <c r="R106" t="n">
-        <v>6793794</v>
+        <v>6794056</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10950,57 +10950,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126167440</v>
+        <v>126190532</v>
       </c>
       <c r="B107" t="n">
-        <v>97223</v>
+        <v>57653</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431667</v>
+        <v>431671</v>
       </c>
       <c r="R107" t="n">
-        <v>6793982</v>
+        <v>6793831</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11032,7 +11028,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11042,12 +11038,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11056,7 +11047,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11068,60 +11058,64 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Eva Löfqvist, Peter Turander, Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126190532</v>
+        <v>126167440</v>
       </c>
       <c r="B108" t="n">
-        <v>57649</v>
+        <v>97227</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431671</v>
+        <v>431667</v>
       </c>
       <c r="R108" t="n">
-        <v>6793831</v>
+        <v>6793982</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11153,7 +11147,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11163,7 +11157,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11172,6 +11171,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Peter Turander, Eva Löfqvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
         <v>126189457</v>
       </c>
       <c r="B109" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>126188368</v>
       </c>
       <c r="B110" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>126162009</v>
       </c>
       <c r="B111" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>126190428</v>
       </c>
       <c r="B112" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126174681</v>
+        <v>126161529</v>
       </c>
       <c r="B115" t="n">
-        <v>79562</v>
+        <v>78736</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11879,41 +11879,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431802</v>
+        <v>431705</v>
       </c>
       <c r="R115" t="n">
-        <v>6794020</v>
+        <v>6794050</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11943,40 +11936,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126161529</v>
+        <v>126174681</v>
       </c>
       <c r="B116" t="n">
-        <v>78732</v>
+        <v>79566</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11984,34 +11986,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431705</v>
+        <v>431802</v>
       </c>
       <c r="R116" t="n">
-        <v>6794050</v>
+        <v>6794020</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12041,49 +12050,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126175046</v>
+        <v>126174513</v>
       </c>
       <c r="B117" t="n">
-        <v>79562</v>
+        <v>79595</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12091,21 +12091,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>432130</v>
+        <v>431721</v>
       </c>
       <c r="R117" t="n">
-        <v>6794314</v>
+        <v>6793745</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12185,10 +12185,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126190566</v>
+        <v>126174710</v>
       </c>
       <c r="B118" t="n">
-        <v>57649</v>
+        <v>79595</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12196,42 +12196,41 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431683</v>
+        <v>431847</v>
       </c>
       <c r="R118" t="n">
-        <v>6793850</v>
+        <v>6794063</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12261,49 +12260,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126174513</v>
+        <v>126190566</v>
       </c>
       <c r="B119" t="n">
-        <v>79591</v>
+        <v>57653</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12311,41 +12301,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431721</v>
+        <v>431683</v>
       </c>
       <c r="R119" t="n">
-        <v>6793745</v>
+        <v>6793850</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12375,40 +12366,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126174710</v>
+        <v>126175046</v>
       </c>
       <c r="B120" t="n">
-        <v>79591</v>
+        <v>79566</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12416,21 +12416,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431847</v>
+        <v>432130</v>
       </c>
       <c r="R120" t="n">
-        <v>6794063</v>
+        <v>6794314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12513,7 +12513,7 @@
         <v>126190620</v>
       </c>
       <c r="B121" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>126174983</v>
       </c>
       <c r="B123" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>126165489</v>
       </c>
       <c r="B124" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>126165849</v>
       </c>
       <c r="B125" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13077,10 +13077,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126162531</v>
+        <v>126174545</v>
       </c>
       <c r="B126" t="n">
-        <v>57649</v>
+        <v>78736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13088,34 +13088,41 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431906</v>
+        <v>431721</v>
       </c>
       <c r="R126" t="n">
-        <v>6794099</v>
+        <v>6793766</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13145,89 +13152,75 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126189221</v>
+        <v>126162531</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431686</v>
+        <v>431906</v>
       </c>
       <c r="R127" t="n">
-        <v>6793927</v>
+        <v>6794099</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13259,7 +13252,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13269,7 +13262,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13278,7 +13271,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13297,52 +13289,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126174545</v>
+        <v>126189221</v>
       </c>
       <c r="B128" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431721</v>
+        <v>431686</v>
       </c>
       <c r="R128" t="n">
-        <v>6793766</v>
+        <v>6793927</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13372,9 +13362,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13390,12 +13390,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
         <v>126167010</v>
       </c>
       <c r="B129" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>126188380</v>
       </c>
       <c r="B130" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13625,45 +13625,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126162062</v>
+        <v>126166597</v>
       </c>
       <c r="B131" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431788</v>
+        <v>432054</v>
       </c>
       <c r="R131" t="n">
-        <v>6794108</v>
+        <v>6794331</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13695,7 +13700,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13705,7 +13710,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13714,6 +13719,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13725,17 +13731,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126165527</v>
+        <v>126190276</v>
       </c>
       <c r="B132" t="n">
-        <v>78731</v>
+        <v>56232</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13743,37 +13749,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>206004</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>432037</v>
+        <v>431609</v>
       </c>
       <c r="R132" t="n">
-        <v>6794186</v>
+        <v>6793764</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13805,7 +13816,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13815,7 +13826,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13824,7 +13835,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13836,17 +13846,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126189975</v>
+        <v>126162062</v>
       </c>
       <c r="B133" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13854,37 +13864,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431647</v>
+        <v>431788</v>
       </c>
       <c r="R133" t="n">
-        <v>6794014</v>
+        <v>6794108</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13916,7 +13923,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13926,7 +13933,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13935,7 +13942,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13947,64 +13953,55 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126190225</v>
+        <v>126165527</v>
       </c>
       <c r="B134" t="n">
-        <v>56844</v>
+        <v>78735</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431908</v>
+        <v>432037</v>
       </c>
       <c r="R134" t="n">
-        <v>6794091</v>
+        <v>6794186</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14036,7 +14033,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14046,7 +14043,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14055,6 +14052,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14073,50 +14071,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126166597</v>
+        <v>126189975</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>92724</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>432054</v>
+        <v>431647</v>
       </c>
       <c r="R135" t="n">
-        <v>6794331</v>
+        <v>6794014</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14148,7 +14144,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14158,7 +14154,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14179,34 +14175,34 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126190276</v>
+        <v>126190225</v>
       </c>
       <c r="B136" t="n">
-        <v>56228</v>
+        <v>56848</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14214,7 +14210,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
@@ -14225,14 +14225,14 @@
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431609</v>
+        <v>431908</v>
       </c>
       <c r="R136" t="n">
-        <v>6793764</v>
+        <v>6794091</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
         <v>126188589</v>
       </c>
       <c r="B137" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>126188441</v>
       </c>
       <c r="B138" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>126188869</v>
       </c>
       <c r="B139" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>126174674</v>
       </c>
       <c r="B140" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14744,10 +14744,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126174633</v>
+        <v>126174664</v>
       </c>
       <c r="B141" t="n">
-        <v>79562</v>
+        <v>57656</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14755,26 +14755,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -14782,10 +14787,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431765</v>
+        <v>431803</v>
       </c>
       <c r="R141" t="n">
-        <v>6793901</v>
+        <v>6793998</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14826,7 +14831,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14845,10 +14849,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126161782</v>
+        <v>126189837</v>
       </c>
       <c r="B142" t="n">
-        <v>78732</v>
+        <v>57656</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14856,37 +14860,46 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431721</v>
+        <v>431661</v>
       </c>
       <c r="R142" t="n">
-        <v>6794089</v>
+        <v>6793926</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14918,7 +14931,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -14928,7 +14941,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14937,7 +14955,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14949,7 +14966,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14959,7 +14976,7 @@
         <v>126190311</v>
       </c>
       <c r="B143" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15076,10 +15093,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126174664</v>
+        <v>126174633</v>
       </c>
       <c r="B144" t="n">
-        <v>57652</v>
+        <v>79566</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15087,31 +15104,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15119,10 +15131,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431803</v>
+        <v>431765</v>
       </c>
       <c r="R144" t="n">
-        <v>6793998</v>
+        <v>6793901</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15163,6 +15175,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15181,10 +15194,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126189837</v>
+        <v>126161782</v>
       </c>
       <c r="B145" t="n">
-        <v>57652</v>
+        <v>78736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15192,46 +15205,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431661</v>
+        <v>431721</v>
       </c>
       <c r="R145" t="n">
-        <v>6793926</v>
+        <v>6794089</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15263,7 +15267,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15273,12 +15277,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15287,6 +15286,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15298,17 +15298,17 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126174690</v>
+        <v>126185018</v>
       </c>
       <c r="B146" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15316,28 +15316,24 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
@@ -15347,10 +15343,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431789</v>
+        <v>431898</v>
       </c>
       <c r="R146" t="n">
-        <v>6794033</v>
+        <v>6794103</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15380,9 +15376,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15398,22 +15404,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126185018</v>
+        <v>126175021</v>
       </c>
       <c r="B147" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15421,24 +15427,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -15448,10 +15458,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431898</v>
+        <v>432130</v>
       </c>
       <c r="R147" t="n">
-        <v>6794103</v>
+        <v>6794314</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15481,19 +15491,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,22 +15509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126175021</v>
+        <v>126188626</v>
       </c>
       <c r="B148" t="n">
-        <v>79591</v>
+        <v>57653</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15532,41 +15532,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>432130</v>
+        <v>431672</v>
       </c>
       <c r="R148" t="n">
-        <v>6794314</v>
+        <v>6794047</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15596,62 +15597,76 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Hästmyror i stubben</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126188626</v>
+        <v>126165721</v>
       </c>
       <c r="B149" t="n">
-        <v>57649</v>
+        <v>56848</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15659,20 +15674,20 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431672</v>
+        <v>432067</v>
       </c>
       <c r="R149" t="n">
-        <v>6794047</v>
+        <v>6794181</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15704,7 +15719,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15714,12 +15729,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Hästmyror i stubben</t>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15746,10 +15761,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126165721</v>
+        <v>126165414</v>
       </c>
       <c r="B150" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15789,10 +15804,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>432067</v>
+        <v>432012</v>
       </c>
       <c r="R150" t="n">
-        <v>6794181</v>
+        <v>6794220</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15824,7 +15839,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15834,12 +15849,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15859,60 +15874,59 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126165414</v>
+        <v>126174690</v>
       </c>
       <c r="B151" t="n">
-        <v>56844</v>
+        <v>79566</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>432012</v>
+        <v>431789</v>
       </c>
       <c r="R151" t="n">
-        <v>6794220</v>
+        <v>6794033</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15942,44 +15956,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
         <v>126190467</v>
       </c>
       <c r="B152" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16097,41 +16097,46 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126174924</v>
+        <v>126188337</v>
       </c>
       <c r="B153" t="n">
-        <v>79005</v>
+        <v>98266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16139,10 +16144,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431893</v>
+        <v>431609</v>
       </c>
       <c r="R153" t="n">
-        <v>6794043</v>
+        <v>6793762</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16172,14 +16177,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16195,12 +16205,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16210,7 +16220,7 @@
         <v>126174574</v>
       </c>
       <c r="B154" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16315,7 +16325,7 @@
         <v>126189054</v>
       </c>
       <c r="B155" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16423,46 +16433,41 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126188337</v>
+        <v>126174924</v>
       </c>
       <c r="B156" t="n">
-        <v>98262</v>
+        <v>79009</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16470,10 +16475,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>431609</v>
+        <v>431893</v>
       </c>
       <c r="R156" t="n">
-        <v>6793762</v>
+        <v>6794043</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16503,19 +16508,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:50</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16531,61 +16531,64 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126162636</v>
+        <v>126174961</v>
       </c>
       <c r="B157" t="n">
-        <v>58021</v>
+        <v>79595</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>431906</v>
+        <v>432073</v>
       </c>
       <c r="R157" t="n">
-        <v>6794099</v>
+        <v>6794217</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16615,54 +16618,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126174961</v>
+        <v>126165393</v>
       </c>
       <c r="B158" t="n">
-        <v>79591</v>
+        <v>57653</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16670,41 +16659,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432073</v>
+        <v>432012</v>
       </c>
       <c r="R158" t="n">
-        <v>6794217</v>
+        <v>6794220</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16734,57 +16724,66 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126165393</v>
+        <v>126162636</v>
       </c>
       <c r="B159" t="n">
-        <v>57649</v>
+        <v>58025</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -16795,11 +16794,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -16807,10 +16802,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>432012</v>
+        <v>431906</v>
       </c>
       <c r="R159" t="n">
-        <v>6794220</v>
+        <v>6794099</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16842,7 +16837,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16852,7 +16847,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16989,7 +16989,7 @@
         <v>126166368</v>
       </c>
       <c r="B161" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>126165703</v>
       </c>
       <c r="B162" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>126174682</v>
       </c>
       <c r="B163" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>126165571</v>
       </c>
       <c r="B164" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17437,10 +17437,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126192573</v>
+        <v>126189897</v>
       </c>
       <c r="B165" t="n">
-        <v>79591</v>
+        <v>57656</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17448,26 +17448,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -17475,10 +17484,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>431790</v>
+        <v>431648</v>
       </c>
       <c r="R165" t="n">
-        <v>6794069</v>
+        <v>6793779</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17510,7 +17519,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17520,7 +17529,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17529,7 +17543,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17541,17 +17554,17 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126189897</v>
+        <v>126192573</v>
       </c>
       <c r="B166" t="n">
-        <v>57652</v>
+        <v>79595</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17559,35 +17572,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17595,10 +17599,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431648</v>
+        <v>431790</v>
       </c>
       <c r="R166" t="n">
-        <v>6793779</v>
+        <v>6794069</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17630,7 +17634,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17640,12 +17644,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Hack efter tretåig hackspett i tallåga.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17654,6 +17653,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17665,57 +17665,55 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126188293</v>
+        <v>126162572</v>
       </c>
       <c r="B167" t="n">
-        <v>5176</v>
+        <v>78977</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>431642</v>
+        <v>431906</v>
       </c>
       <c r="R167" t="n">
-        <v>6794010</v>
+        <v>6794099</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17747,7 +17745,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17757,7 +17755,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17778,17 +17781,17 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jakob Bowers, Peter Turander, Håkan Thenander, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126162572</v>
+        <v>126167044</v>
       </c>
       <c r="B168" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17796,26 +17799,27 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17823,10 +17827,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431906</v>
+        <v>432002</v>
       </c>
       <c r="R168" t="n">
-        <v>6794099</v>
+        <v>6794336</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17858,7 +17862,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17868,12 +17872,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17882,7 +17881,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17894,7 +17892,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -17904,7 +17902,7 @@
         <v>126174530</v>
       </c>
       <c r="B169" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18009,7 +18007,7 @@
         <v>126174557</v>
       </c>
       <c r="B170" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18111,49 +18109,50 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126167044</v>
+        <v>126188293</v>
       </c>
       <c r="B171" t="n">
-        <v>57649</v>
+        <v>5176</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>432002</v>
+        <v>431642</v>
       </c>
       <c r="R171" t="n">
-        <v>6794336</v>
+        <v>6794010</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18185,7 +18184,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18195,7 +18194,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18204,6 +18203,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18215,7 +18215,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18225,7 +18225,7 @@
         <v>126165882</v>
       </c>
       <c r="B172" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>126165872</v>
       </c>
       <c r="B174" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>126166244</v>
       </c>
       <c r="B175" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>126166521</v>
       </c>
       <c r="B176" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>126165950</v>
       </c>
       <c r="B177" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>126166104</v>
       </c>
       <c r="B178" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>126163407</v>
       </c>
       <c r="B179" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>126163588</v>
       </c>
       <c r="B180" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>126165579</v>
       </c>
       <c r="B181" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022246</v>
+        <v>126022232</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431785</v>
+        <v>431615</v>
       </c>
       <c r="R14" t="n">
-        <v>6793548</v>
+        <v>6793508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022267</v>
+        <v>126022246</v>
       </c>
       <c r="B15" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431663</v>
+        <v>431785</v>
       </c>
       <c r="R15" t="n">
-        <v>6793516</v>
+        <v>6793548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022232</v>
+        <v>126022267</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>78644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431615</v>
+        <v>431663</v>
       </c>
       <c r="R16" t="n">
-        <v>6793508</v>
+        <v>6793516</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126161538</v>
+        <v>126166842</v>
       </c>
       <c r="B30" t="n">
-        <v>78736</v>
+        <v>57653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,34 +3402,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431778</v>
+        <v>432245</v>
       </c>
       <c r="R30" t="n">
-        <v>6794048</v>
+        <v>6794369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126162525</v>
+        <v>126161538</v>
       </c>
       <c r="B31" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431861</v>
+        <v>431778</v>
       </c>
       <c r="R31" t="n">
-        <v>6794056</v>
+        <v>6794048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126161265</v>
+        <v>126162525</v>
       </c>
       <c r="B32" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,34 +3601,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431735</v>
+        <v>431861</v>
       </c>
       <c r="R32" t="n">
-        <v>6794019</v>
+        <v>6794056</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3650,12 +3655,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3682,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126166842</v>
+        <v>126161615</v>
       </c>
       <c r="B33" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,39 +3698,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432245</v>
+        <v>431758</v>
       </c>
       <c r="R33" t="n">
-        <v>6794369</v>
+        <v>6794063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,7 +3784,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126161615</v>
+        <v>126159713</v>
       </c>
       <c r="B34" t="n">
         <v>78977</v>
@@ -3815,17 +3815,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431758</v>
+        <v>431676</v>
       </c>
       <c r="R34" t="n">
-        <v>6794063</v>
+        <v>6793755</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126159713</v>
+        <v>126159766</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3916,13 +3916,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431676</v>
+        <v>431687</v>
       </c>
       <c r="R35" t="n">
-        <v>6793755</v>
+        <v>6793778</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126159766</v>
+        <v>126161051</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431687</v>
+        <v>431757</v>
       </c>
       <c r="R36" t="n">
-        <v>6793778</v>
+        <v>6793912</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4075,7 +4075,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126161051</v>
+        <v>126162787</v>
       </c>
       <c r="B37" t="n">
         <v>78977</v>
@@ -4106,14 +4106,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431757</v>
+        <v>431921</v>
       </c>
       <c r="R37" t="n">
-        <v>6793912</v>
+        <v>6794053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126162787</v>
+        <v>126165139</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431921</v>
+        <v>431949</v>
       </c>
       <c r="R38" t="n">
-        <v>6794053</v>
+        <v>6794232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126165139</v>
+        <v>126161265</v>
       </c>
       <c r="B39" t="n">
         <v>79595</v>
@@ -4300,14 +4300,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431949</v>
+        <v>431735</v>
       </c>
       <c r="R39" t="n">
-        <v>6794232</v>
+        <v>6794019</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5545,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126162207</v>
+        <v>126160189</v>
       </c>
       <c r="B52" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,34 +5556,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431783</v>
+        <v>431763</v>
       </c>
       <c r="R52" t="n">
-        <v>6794074</v>
+        <v>6793789</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126160189</v>
+        <v>126157375</v>
       </c>
       <c r="B53" t="n">
         <v>78977</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431763</v>
+        <v>431639</v>
       </c>
       <c r="R53" t="n">
-        <v>6793789</v>
+        <v>6793601</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5713,6 +5713,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5739,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126157375</v>
+        <v>126162207</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,34 +5755,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431639</v>
+        <v>431783</v>
       </c>
       <c r="R54" t="n">
-        <v>6793601</v>
+        <v>6794074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5810,11 +5815,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126166708</v>
+        <v>126166809</v>
       </c>
       <c r="B61" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,39 +6449,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432272</v>
+        <v>432273</v>
       </c>
       <c r="R61" t="n">
-        <v>6794337</v>
+        <v>6794365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6540,7 +6535,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126166809</v>
+        <v>126160807</v>
       </c>
       <c r="B62" t="n">
         <v>78977</v>
@@ -6571,14 +6566,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432273</v>
+        <v>431738</v>
       </c>
       <c r="R62" t="n">
-        <v>6794365</v>
+        <v>6793845</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6605,12 +6600,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,7 +6632,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126160807</v>
+        <v>126160381</v>
       </c>
       <c r="B63" t="n">
         <v>78977</v>
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431738</v>
+        <v>431734</v>
       </c>
       <c r="R63" t="n">
-        <v>6793845</v>
+        <v>6793794</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6702,12 +6697,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6734,7 +6729,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126160381</v>
+        <v>126159369</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431734</v>
+        <v>431635</v>
       </c>
       <c r="R64" t="n">
-        <v>6793794</v>
+        <v>6793754</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6831,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126159369</v>
+        <v>126164027</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6842,34 +6837,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431635</v>
+        <v>431844</v>
       </c>
       <c r="R65" t="n">
-        <v>6793754</v>
+        <v>6794158</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6928,10 +6923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126164027</v>
+        <v>126166708</v>
       </c>
       <c r="B66" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6939,34 +6934,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431844</v>
+        <v>432272</v>
       </c>
       <c r="R66" t="n">
-        <v>6794158</v>
+        <v>6794337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7316,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126162912</v>
+        <v>126163869</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>79566</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7327,39 +7327,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431943</v>
+        <v>431844</v>
       </c>
       <c r="R70" t="n">
-        <v>6794014</v>
+        <v>6794158</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7520,10 +7515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126161304</v>
+        <v>126162912</v>
       </c>
       <c r="B72" t="n">
-        <v>79566</v>
+        <v>57656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7531,34 +7526,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431735</v>
+        <v>431943</v>
       </c>
       <c r="R72" t="n">
-        <v>6794019</v>
+        <v>6794014</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7617,7 +7617,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126163869</v>
+        <v>126161304</v>
       </c>
       <c r="B73" t="n">
         <v>79566</v>
@@ -7648,14 +7648,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431844</v>
+        <v>431735</v>
       </c>
       <c r="R73" t="n">
-        <v>6794158</v>
+        <v>6794019</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7714,10 +7714,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126162596</v>
+        <v>126166662</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7725,21 +7725,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431888</v>
+        <v>432272</v>
       </c>
       <c r="R74" t="n">
-        <v>6794051</v>
+        <v>6794337</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126158231</v>
+        <v>126162596</v>
       </c>
       <c r="B75" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7822,39 +7822,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431597</v>
+        <v>431888</v>
       </c>
       <c r="R75" t="n">
-        <v>6793646</v>
+        <v>6794051</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7913,10 +7908,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126166662</v>
+        <v>126158231</v>
       </c>
       <c r="B76" t="n">
-        <v>79566</v>
+        <v>57656</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,34 +7919,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432272</v>
+        <v>431597</v>
       </c>
       <c r="R76" t="n">
-        <v>6794337</v>
+        <v>6793646</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161159</v>
+        <v>126161358</v>
       </c>
       <c r="B89" t="n">
         <v>78977</v>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431724</v>
+        <v>431735</v>
       </c>
       <c r="R89" t="n">
-        <v>6793934</v>
+        <v>6794019</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126161358</v>
+        <v>126161159</v>
       </c>
       <c r="B90" t="n">
         <v>78977</v>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431735</v>
+        <v>431724</v>
       </c>
       <c r="R90" t="n">
-        <v>6794019</v>
+        <v>6793934</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126160295</v>
+        <v>126162496</v>
       </c>
       <c r="B105" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10762,39 +10762,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431734</v>
+        <v>431861</v>
       </c>
       <c r="R105" t="n">
-        <v>6793794</v>
+        <v>6794056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10853,10 +10848,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126162496</v>
+        <v>126160295</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10864,34 +10859,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431861</v>
+        <v>431734</v>
       </c>
       <c r="R106" t="n">
-        <v>6794056</v>
+        <v>6793794</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10950,53 +10950,57 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126190532</v>
+        <v>126167440</v>
       </c>
       <c r="B107" t="n">
-        <v>57653</v>
+        <v>97227</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431671</v>
+        <v>431667</v>
       </c>
       <c r="R107" t="n">
-        <v>6793831</v>
+        <v>6793982</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11028,7 +11032,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11038,7 +11042,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11047,6 +11056,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11058,64 +11068,60 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Peter Turander, Eva Löfqvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126167440</v>
+        <v>126190532</v>
       </c>
       <c r="B108" t="n">
-        <v>97227</v>
+        <v>57653</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Slätbergsbäcken, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431667</v>
+        <v>431671</v>
       </c>
       <c r="R108" t="n">
-        <v>6793982</v>
+        <v>6793831</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11147,7 +11153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11157,12 +11163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11171,7 +11172,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Peter Turander, Eva Löfqvist, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12510,53 +12510,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B121" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R121" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12588,7 +12580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12598,7 +12590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12625,45 +12617,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R122" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13077,10 +13077,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126174545</v>
+        <v>126162531</v>
       </c>
       <c r="B126" t="n">
-        <v>78736</v>
+        <v>57653</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13088,41 +13088,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431721</v>
+        <v>431906</v>
       </c>
       <c r="R126" t="n">
-        <v>6793766</v>
+        <v>6794099</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13152,40 +13145,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126162531</v>
+        <v>126174545</v>
       </c>
       <c r="B127" t="n">
-        <v>57653</v>
+        <v>78736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13193,34 +13195,41 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431906</v>
+        <v>431721</v>
       </c>
       <c r="R127" t="n">
-        <v>6794099</v>
+        <v>6793766</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13250,39 +13259,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13625,50 +13625,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126166597</v>
+        <v>126162062</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>432054</v>
+        <v>431788</v>
       </c>
       <c r="R131" t="n">
-        <v>6794331</v>
+        <v>6794108</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13700,7 +13695,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13710,7 +13705,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13719,7 +13714,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13731,17 +13725,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126190276</v>
+        <v>126165527</v>
       </c>
       <c r="B132" t="n">
-        <v>56232</v>
+        <v>78735</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13749,42 +13743,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>206004</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431609</v>
+        <v>432037</v>
       </c>
       <c r="R132" t="n">
-        <v>6793764</v>
+        <v>6794186</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13816,7 +13805,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13826,7 +13815,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13835,6 +13824,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13846,17 +13836,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126162062</v>
+        <v>126189975</v>
       </c>
       <c r="B133" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13864,34 +13854,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431788</v>
+        <v>431647</v>
       </c>
       <c r="R133" t="n">
-        <v>6794108</v>
+        <v>6794014</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13923,7 +13916,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13933,7 +13926,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13942,6 +13935,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13953,55 +13947,64 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126165527</v>
+        <v>126190225</v>
       </c>
       <c r="B134" t="n">
-        <v>78735</v>
+        <v>56848</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>432037</v>
+        <v>431908</v>
       </c>
       <c r="R134" t="n">
-        <v>6794186</v>
+        <v>6794091</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14033,7 +14036,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14043,7 +14046,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14052,7 +14055,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14071,10 +14073,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126189975</v>
+        <v>126190276</v>
       </c>
       <c r="B135" t="n">
-        <v>92724</v>
+        <v>56232</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14082,37 +14084,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>206004</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431647</v>
+        <v>431609</v>
       </c>
       <c r="R135" t="n">
-        <v>6794014</v>
+        <v>6793764</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14144,7 +14151,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14154,7 +14161,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14163,7 +14170,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14175,17 +14181,17 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126190225</v>
+        <v>126166597</v>
       </c>
       <c r="B136" t="n">
-        <v>56848</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14193,46 +14199,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431908</v>
+        <v>432054</v>
       </c>
       <c r="R136" t="n">
-        <v>6794091</v>
+        <v>6794331</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14264,7 +14263,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14274,7 +14273,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14283,6 +14282,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -16543,52 +16543,49 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126174961</v>
+        <v>126162636</v>
       </c>
       <c r="B157" t="n">
-        <v>79595</v>
+        <v>58025</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432073</v>
+        <v>431906</v>
       </c>
       <c r="R157" t="n">
-        <v>6794217</v>
+        <v>6794099</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16618,83 +16615,98 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126165393</v>
+        <v>126174659</v>
       </c>
       <c r="B158" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432012</v>
+        <v>431731</v>
       </c>
       <c r="R158" t="n">
-        <v>6794220</v>
+        <v>6793834</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16724,66 +16736,57 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126162636</v>
+        <v>126165393</v>
       </c>
       <c r="B159" t="n">
-        <v>58025</v>
+        <v>57653</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -16794,7 +16797,11 @@
       <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -16802,10 +16809,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>431906</v>
+        <v>432012</v>
       </c>
       <c r="R159" t="n">
-        <v>6794099</v>
+        <v>6794220</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16837,7 +16844,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16847,12 +16854,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16879,43 +16881,41 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126174659</v>
+        <v>126174961</v>
       </c>
       <c r="B160" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -16923,10 +16923,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>431731</v>
+        <v>432073</v>
       </c>
       <c r="R160" t="n">
-        <v>6793834</v>
+        <v>6794217</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R17" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B18" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R18" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126165139</v>
+        <v>126166842</v>
       </c>
       <c r="B30" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,34 +3402,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431949</v>
+        <v>432245</v>
       </c>
       <c r="R30" t="n">
-        <v>6794232</v>
+        <v>6794369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161265</v>
+        <v>126161538</v>
       </c>
       <c r="B31" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,34 +3504,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431735</v>
+        <v>431778</v>
       </c>
       <c r="R31" t="n">
-        <v>6794019</v>
+        <v>6794048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3553,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3585,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126166842</v>
+        <v>126162525</v>
       </c>
       <c r="B32" t="n">
-        <v>57653</v>
+        <v>79566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,39 +3601,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432245</v>
+        <v>431861</v>
       </c>
       <c r="R32" t="n">
-        <v>6794369</v>
+        <v>6794056</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126162525</v>
+        <v>126165139</v>
       </c>
       <c r="B33" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431861</v>
+        <v>431949</v>
       </c>
       <c r="R33" t="n">
-        <v>6794056</v>
+        <v>6794232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126159713</v>
+        <v>126161265</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431676</v>
+        <v>431735</v>
       </c>
       <c r="R34" t="n">
-        <v>6793755</v>
+        <v>6794019</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126162787</v>
+        <v>126159713</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3912,17 +3912,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431921</v>
+        <v>431676</v>
       </c>
       <c r="R35" t="n">
-        <v>6794053</v>
+        <v>6793755</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126159766</v>
+        <v>126162787</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4009,14 +4009,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431687</v>
+        <v>431921</v>
       </c>
       <c r="R36" t="n">
-        <v>6793778</v>
+        <v>6794053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126161051</v>
+        <v>126159766</v>
       </c>
       <c r="B37" t="n">
         <v>78977</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431757</v>
+        <v>431687</v>
       </c>
       <c r="R37" t="n">
-        <v>6793912</v>
+        <v>6793778</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,7 +4172,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161615</v>
+        <v>126161051</v>
       </c>
       <c r="B38" t="n">
         <v>78977</v>
@@ -4203,14 +4203,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431758</v>
+        <v>431757</v>
       </c>
       <c r="R38" t="n">
-        <v>6794063</v>
+        <v>6793912</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126161538</v>
+        <v>126161615</v>
       </c>
       <c r="B39" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431778</v>
+        <v>431758</v>
       </c>
       <c r="R39" t="n">
-        <v>6794048</v>
+        <v>6794063</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126164975</v>
+        <v>126161498</v>
       </c>
       <c r="B45" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,34 +4867,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431934</v>
+        <v>431776</v>
       </c>
       <c r="R45" t="n">
-        <v>6794246</v>
+        <v>6794017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4953,7 +4958,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126161498</v>
+        <v>126165020</v>
       </c>
       <c r="B46" t="n">
         <v>57653</v>
@@ -4984,19 +4989,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431776</v>
+        <v>431934</v>
       </c>
       <c r="R46" t="n">
-        <v>6794017</v>
+        <v>6794246</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126165020</v>
+        <v>126166682</v>
       </c>
       <c r="B47" t="n">
-        <v>57653</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,39 +5071,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431934</v>
+        <v>432272</v>
       </c>
       <c r="R47" t="n">
-        <v>6794246</v>
+        <v>6794337</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126166682</v>
+        <v>126164975</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432272</v>
+        <v>431934</v>
       </c>
       <c r="R48" t="n">
-        <v>6794337</v>
+        <v>6794246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126160760</v>
+        <v>126162332</v>
       </c>
       <c r="B49" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431740</v>
+        <v>431839</v>
       </c>
       <c r="R49" t="n">
-        <v>6793833</v>
+        <v>6794073</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B50" t="n">
         <v>78977</v>
@@ -5382,14 +5382,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126161213</v>
+        <v>126160760</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431756</v>
+        <v>431740</v>
       </c>
       <c r="R51" t="n">
-        <v>6793994</v>
+        <v>6793833</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126159369</v>
+        <v>126165342</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431635</v>
+        <v>431949</v>
       </c>
       <c r="R61" t="n">
-        <v>6793754</v>
+        <v>6794232</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126160807</v>
+        <v>126162164</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,34 +6546,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431738</v>
+        <v>431783</v>
       </c>
       <c r="R62" t="n">
-        <v>6793845</v>
+        <v>6794074</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6632,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126160381</v>
+        <v>126164027</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6643,34 +6643,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431734</v>
+        <v>431844</v>
       </c>
       <c r="R63" t="n">
-        <v>6793794</v>
+        <v>6794158</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126166809</v>
+        <v>126159369</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -6760,14 +6760,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432273</v>
+        <v>431635</v>
       </c>
       <c r="R64" t="n">
-        <v>6794365</v>
+        <v>6793754</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126166708</v>
+        <v>126160807</v>
       </c>
       <c r="B65" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,39 +6837,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432272</v>
+        <v>431738</v>
       </c>
       <c r="R65" t="n">
-        <v>6794337</v>
+        <v>6793845</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6896,12 +6891,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6928,10 +6923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126165342</v>
+        <v>126160381</v>
       </c>
       <c r="B66" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6939,34 +6934,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431949</v>
+        <v>431734</v>
       </c>
       <c r="R66" t="n">
-        <v>6794232</v>
+        <v>6793794</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7025,10 +7020,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126162164</v>
+        <v>126166809</v>
       </c>
       <c r="B67" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7036,21 +7031,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7060,10 +7055,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431783</v>
+        <v>432273</v>
       </c>
       <c r="R67" t="n">
-        <v>6794074</v>
+        <v>6794365</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7122,10 +7117,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126164027</v>
+        <v>126166708</v>
       </c>
       <c r="B68" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7133,34 +7128,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431844</v>
+        <v>432272</v>
       </c>
       <c r="R68" t="n">
-        <v>6794158</v>
+        <v>6794337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -11643,45 +11643,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126161529</v>
+        <v>126163646</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431705</v>
+        <v>431898</v>
       </c>
       <c r="R113" t="n">
-        <v>6794050</v>
+        <v>6794103</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11713,7 +11718,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11723,7 +11728,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11732,6 +11742,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11750,7 +11761,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126163646</v>
+        <v>126174973</v>
       </c>
       <c r="B114" t="n">
         <v>8447</v>
@@ -11782,18 +11793,22 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431898</v>
+        <v>432045</v>
       </c>
       <c r="R114" t="n">
-        <v>6794103</v>
+        <v>6794330</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11823,24 +11838,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11856,55 +11856,53 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126174973</v>
+        <v>126174681</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -11912,10 +11910,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>432045</v>
+        <v>431802</v>
       </c>
       <c r="R115" t="n">
-        <v>6794330</v>
+        <v>6794020</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11975,10 +11973,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126174681</v>
+        <v>126161529</v>
       </c>
       <c r="B116" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11986,41 +11984,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431802</v>
+        <v>431705</v>
       </c>
       <c r="R116" t="n">
-        <v>6794020</v>
+        <v>6794050</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12050,40 +12041,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126190566</v>
+        <v>126174710</v>
       </c>
       <c r="B117" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12091,42 +12091,41 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431683</v>
+        <v>431847</v>
       </c>
       <c r="R117" t="n">
-        <v>6793850</v>
+        <v>6794063</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12156,46 +12155,37 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126174710</v>
+        <v>126174513</v>
       </c>
       <c r="B118" t="n">
         <v>79595</v>
@@ -12237,10 +12227,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431847</v>
+        <v>431721</v>
       </c>
       <c r="R118" t="n">
-        <v>6794063</v>
+        <v>6793745</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12300,10 +12290,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126174513</v>
+        <v>126190566</v>
       </c>
       <c r="B119" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12311,41 +12301,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431721</v>
+        <v>431683</v>
       </c>
       <c r="R119" t="n">
-        <v>6793745</v>
+        <v>6793850</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12375,30 +12366,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -13732,46 +13732,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126190225</v>
+        <v>126189975</v>
       </c>
       <c r="B132" t="n">
-        <v>56848</v>
+        <v>92724</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -13779,10 +13770,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431908</v>
+        <v>431647</v>
       </c>
       <c r="R132" t="n">
-        <v>6794091</v>
+        <v>6794014</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13814,7 +13805,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13824,7 +13815,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13833,6 +13824,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13844,17 +13836,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126190276</v>
+        <v>126165527</v>
       </c>
       <c r="B133" t="n">
-        <v>56232</v>
+        <v>78735</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13862,42 +13854,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>206004</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431609</v>
+        <v>432037</v>
       </c>
       <c r="R133" t="n">
-        <v>6793764</v>
+        <v>6794186</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13929,7 +13916,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13939,7 +13926,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13948,6 +13935,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13959,17 +13947,17 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126166597</v>
+        <v>126190225</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>56848</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13977,39 +13965,46 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>432054</v>
+        <v>431908</v>
       </c>
       <c r="R134" t="n">
-        <v>6794331</v>
+        <v>6794091</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14041,7 +14036,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14051,7 +14046,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14060,7 +14055,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14072,17 +14066,17 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126165527</v>
+        <v>126190276</v>
       </c>
       <c r="B135" t="n">
-        <v>78735</v>
+        <v>56232</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14090,37 +14084,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>206004</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>432037</v>
+        <v>431609</v>
       </c>
       <c r="R135" t="n">
-        <v>6794186</v>
+        <v>6793764</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14152,7 +14151,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14162,7 +14161,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14171,7 +14170,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14183,55 +14181,57 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126189975</v>
+        <v>126166597</v>
       </c>
       <c r="B136" t="n">
-        <v>92724</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431647</v>
+        <v>432054</v>
       </c>
       <c r="R136" t="n">
-        <v>6794014</v>
+        <v>6794331</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14744,10 +14744,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126174633</v>
+        <v>126161782</v>
       </c>
       <c r="B141" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14755,21 +14755,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14778,14 +14778,14 @@
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431765</v>
+        <v>431721</v>
       </c>
       <c r="R141" t="n">
-        <v>6793901</v>
+        <v>6794089</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14815,9 +14815,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14833,12 +14843,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15074,10 +15084,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126161782</v>
+        <v>126174633</v>
       </c>
       <c r="B144" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15085,21 +15095,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15108,14 +15118,14 @@
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431721</v>
+        <v>431765</v>
       </c>
       <c r="R144" t="n">
-        <v>6794089</v>
+        <v>6793901</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15145,19 +15155,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15173,12 +15173,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15305,10 +15305,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126175021</v>
+        <v>126174690</v>
       </c>
       <c r="B146" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15316,21 +15316,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -15347,10 +15347,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>432130</v>
+        <v>431789</v>
       </c>
       <c r="R146" t="n">
-        <v>6794314</v>
+        <v>6794033</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15410,10 +15410,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126185018</v>
+        <v>126175021</v>
       </c>
       <c r="B147" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15421,24 +15421,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -15448,10 +15452,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431898</v>
+        <v>432130</v>
       </c>
       <c r="R147" t="n">
-        <v>6794103</v>
+        <v>6794314</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15481,19 +15485,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,44 +15503,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126165721</v>
+        <v>126188626</v>
       </c>
       <c r="B148" t="n">
-        <v>56848</v>
+        <v>57653</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15554,20 +15548,20 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>432067</v>
+        <v>431672</v>
       </c>
       <c r="R148" t="n">
-        <v>6794181</v>
+        <v>6794047</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15599,7 +15593,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15609,12 +15603,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hästmyror i stubben</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15641,53 +15635,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126165414</v>
+        <v>126185018</v>
       </c>
       <c r="B149" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>432012</v>
+        <v>431898</v>
       </c>
       <c r="R149" t="n">
-        <v>6794220</v>
+        <v>6794103</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15719,7 +15708,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15729,12 +15718,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15743,6 +15727,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15754,59 +15739,60 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126174690</v>
+        <v>126165721</v>
       </c>
       <c r="B150" t="n">
-        <v>79566</v>
+        <v>56848</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>431789</v>
+        <v>432067</v>
       </c>
       <c r="R150" t="n">
-        <v>6794033</v>
+        <v>6794181</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15836,62 +15822,76 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Barr</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126188626</v>
+        <v>126165414</v>
       </c>
       <c r="B151" t="n">
-        <v>57653</v>
+        <v>56848</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15899,20 +15899,20 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431672</v>
+        <v>432012</v>
       </c>
       <c r="R151" t="n">
-        <v>6794047</v>
+        <v>6794220</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Hästmyror i stubben</t>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16097,10 +16097,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126174924</v>
+        <v>126189054</v>
       </c>
       <c r="B153" t="n">
-        <v>79009</v>
+        <v>79595</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16108,41 +16108,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431893</v>
+        <v>431660</v>
       </c>
       <c r="R153" t="n">
-        <v>6794043</v>
+        <v>6793737</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16172,14 +16168,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16195,19 +16196,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126189054</v>
+        <v>126174574</v>
       </c>
       <c r="B154" t="n">
         <v>79595</v>
@@ -16235,20 +16236,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431660</v>
+        <v>431765</v>
       </c>
       <c r="R154" t="n">
-        <v>6793737</v>
+        <v>6793901</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16278,19 +16283,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16306,53 +16301,58 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126174574</v>
+        <v>126188337</v>
       </c>
       <c r="B155" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431765</v>
+        <v>431609</v>
       </c>
       <c r="R155" t="n">
-        <v>6793901</v>
+        <v>6793762</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16393,9 +16393,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16411,58 +16421,53 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126188337</v>
+        <v>126174924</v>
       </c>
       <c r="B156" t="n">
-        <v>98269</v>
+        <v>79009</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16470,10 +16475,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>431609</v>
+        <v>431893</v>
       </c>
       <c r="R156" t="n">
-        <v>6793762</v>
+        <v>6794043</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16503,19 +16508,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:50</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16531,22 +16531,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126174961</v>
+        <v>126165393</v>
       </c>
       <c r="B157" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16554,41 +16554,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432073</v>
+        <v>432012</v>
       </c>
       <c r="R157" t="n">
-        <v>6794217</v>
+        <v>6794220</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16618,83 +16619,93 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126165393</v>
+        <v>126174659</v>
       </c>
       <c r="B158" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432012</v>
+        <v>431731</v>
       </c>
       <c r="R158" t="n">
-        <v>6794220</v>
+        <v>6793834</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16724,88 +16735,82 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126162636</v>
+        <v>126174961</v>
       </c>
       <c r="B159" t="n">
-        <v>58025</v>
+        <v>79595</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>431906</v>
+        <v>432073</v>
       </c>
       <c r="R159" t="n">
-        <v>6794099</v>
+        <v>6794217</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16835,54 +16840,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126174659</v>
+        <v>126162636</v>
       </c>
       <c r="B160" t="n">
-        <v>8447</v>
+        <v>58025</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16890,43 +16881,38 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>431731</v>
+        <v>431906</v>
       </c>
       <c r="R160" t="n">
-        <v>6793834</v>
+        <v>6794099</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16956,30 +16942,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17101,10 +17101,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126174682</v>
+        <v>126165571</v>
       </c>
       <c r="B162" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17112,41 +17112,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>431789</v>
+        <v>432034</v>
       </c>
       <c r="R162" t="n">
-        <v>6794033</v>
+        <v>6794182</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17176,86 +17169,91 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126165703</v>
+        <v>126174682</v>
       </c>
       <c r="B163" t="n">
-        <v>92532</v>
+        <v>79595</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>432067</v>
+        <v>431789</v>
       </c>
       <c r="R163" t="n">
-        <v>6794181</v>
+        <v>6794033</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17285,24 +17283,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17318,57 +17301,68 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126165571</v>
+        <v>126165703</v>
       </c>
       <c r="B164" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>432034</v>
+        <v>432067</v>
       </c>
       <c r="R164" t="n">
-        <v>6794182</v>
+        <v>6794181</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17400,7 +17394,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17410,7 +17404,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17419,6 +17418,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126174530</v>
+        <v>126162572</v>
       </c>
       <c r="B167" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17683,41 +17683,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>431675</v>
+        <v>431906</v>
       </c>
       <c r="R167" t="n">
-        <v>6793721</v>
+        <v>6794099</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17747,9 +17743,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17765,22 +17776,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126174557</v>
+        <v>126167044</v>
       </c>
       <c r="B168" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17788,41 +17799,38 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431730</v>
+        <v>432002</v>
       </c>
       <c r="R168" t="n">
-        <v>6793838</v>
+        <v>6794336</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17852,78 +17860,89 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126162572</v>
+        <v>126188293</v>
       </c>
       <c r="B169" t="n">
-        <v>78977</v>
+        <v>5176</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>431906</v>
+        <v>431642</v>
       </c>
       <c r="R169" t="n">
-        <v>6794099</v>
+        <v>6794010</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17955,7 +17974,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -17965,12 +17984,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17991,57 +18005,59 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126188293</v>
+        <v>126174530</v>
       </c>
       <c r="B170" t="n">
-        <v>5176</v>
+        <v>79595</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>431642</v>
+        <v>431675</v>
       </c>
       <c r="R170" t="n">
-        <v>6794010</v>
+        <v>6793721</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18071,19 +18087,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18099,22 +18105,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126167044</v>
+        <v>126174557</v>
       </c>
       <c r="B171" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18122,38 +18128,41 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>432002</v>
+        <v>431730</v>
       </c>
       <c r="R171" t="n">
-        <v>6794336</v>
+        <v>6793838</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18183,39 +18192,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>18:59</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>18:59</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -20904,10 +20904,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126390468</v>
+        <v>126391611</v>
       </c>
       <c r="B198" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20915,34 +20915,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>431586</v>
+        <v>431690</v>
       </c>
       <c r="R198" t="n">
-        <v>6793937</v>
+        <v>6793903</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21011,10 +21011,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126391611</v>
+        <v>126390468</v>
       </c>
       <c r="B199" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21022,34 +21022,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>431690</v>
+        <v>431586</v>
       </c>
       <c r="R199" t="n">
-        <v>6793903</v>
+        <v>6793937</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21081,7 +21081,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B14" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R14" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R15" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78644</v>
+        <v>79566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R17" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R18" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126166842</v>
+        <v>126159713</v>
       </c>
       <c r="B30" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,42 +3402,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432245</v>
+        <v>431676</v>
       </c>
       <c r="R30" t="n">
-        <v>6794369</v>
+        <v>6793755</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3493,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161538</v>
+        <v>126165139</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431778</v>
+        <v>431949</v>
       </c>
       <c r="R31" t="n">
-        <v>6794048</v>
+        <v>6794232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126162525</v>
+        <v>126162787</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431861</v>
+        <v>431921</v>
       </c>
       <c r="R32" t="n">
-        <v>6794056</v>
+        <v>6794053</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126165139</v>
+        <v>126159766</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,34 +3693,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431949</v>
+        <v>431687</v>
       </c>
       <c r="R33" t="n">
-        <v>6794232</v>
+        <v>6793778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126159713</v>
+        <v>126161051</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3916,13 +3911,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431676</v>
+        <v>431757</v>
       </c>
       <c r="R35" t="n">
-        <v>6793755</v>
+        <v>6793912</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3946,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126162787</v>
+        <v>126161615</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431921</v>
+        <v>431758</v>
       </c>
       <c r="R36" t="n">
-        <v>6794053</v>
+        <v>6794063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126159766</v>
+        <v>126166842</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4086,34 +4081,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431687</v>
+        <v>432245</v>
       </c>
       <c r="R37" t="n">
-        <v>6793778</v>
+        <v>6794369</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161051</v>
+        <v>126161538</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431757</v>
+        <v>431778</v>
       </c>
       <c r="R38" t="n">
-        <v>6793912</v>
+        <v>6794048</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126161615</v>
+        <v>126162525</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431758</v>
+        <v>431861</v>
       </c>
       <c r="R39" t="n">
-        <v>6794063</v>
+        <v>6794056</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126156950</v>
+        <v>126166682</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,34 +4377,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431647</v>
+        <v>432272</v>
       </c>
       <c r="R40" t="n">
-        <v>6793602</v>
+        <v>6794337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126167392</v>
+        <v>126164975</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431653</v>
+        <v>431934</v>
       </c>
       <c r="R41" t="n">
-        <v>6793960</v>
+        <v>6794246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4534,11 +4534,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4565,7 +4560,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126162274</v>
+        <v>126156950</v>
       </c>
       <c r="B42" t="n">
         <v>78977</v>
@@ -4596,14 +4591,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431815</v>
+        <v>431647</v>
       </c>
       <c r="R42" t="n">
-        <v>6794067</v>
+        <v>6793602</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,7 +4657,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126162811</v>
+        <v>126167392</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -4697,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431942</v>
+        <v>431653</v>
       </c>
       <c r="R43" t="n">
-        <v>6794029</v>
+        <v>6793960</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4733,6 +4728,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126159534</v>
+        <v>126162274</v>
       </c>
       <c r="B44" t="n">
         <v>78977</v>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431657</v>
+        <v>431815</v>
       </c>
       <c r="R44" t="n">
-        <v>6793728</v>
+        <v>6794067</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126161498</v>
+        <v>126162811</v>
       </c>
       <c r="B45" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,39 +4867,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431776</v>
+        <v>431942</v>
       </c>
       <c r="R45" t="n">
-        <v>6794017</v>
+        <v>6794029</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126165020</v>
+        <v>126159534</v>
       </c>
       <c r="B46" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,39 +4964,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431934</v>
+        <v>431657</v>
       </c>
       <c r="R46" t="n">
-        <v>6794246</v>
+        <v>6793728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5050,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126166682</v>
+        <v>126161498</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>57653</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,34 +5061,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432272</v>
+        <v>431776</v>
       </c>
       <c r="R47" t="n">
-        <v>6794337</v>
+        <v>6794017</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126164975</v>
+        <v>126165020</v>
       </c>
       <c r="B48" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,24 +5163,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
@@ -5545,45 +5545,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126162207</v>
+        <v>126162045</v>
       </c>
       <c r="B52" t="n">
-        <v>79595</v>
+        <v>58025</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431783</v>
+        <v>431758</v>
       </c>
       <c r="R52" t="n">
-        <v>6794074</v>
+        <v>6794063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,50 +5846,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126162045</v>
+        <v>126162207</v>
       </c>
       <c r="B55" t="n">
-        <v>58025</v>
+        <v>79595</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431758</v>
+        <v>431783</v>
       </c>
       <c r="R55" t="n">
-        <v>6794063</v>
+        <v>6794074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126165342</v>
+        <v>126159369</v>
       </c>
       <c r="B61" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431949</v>
+        <v>431635</v>
       </c>
       <c r="R61" t="n">
-        <v>6794232</v>
+        <v>6793754</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126162164</v>
+        <v>126160807</v>
       </c>
       <c r="B62" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,34 +6546,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431783</v>
+        <v>431738</v>
       </c>
       <c r="R62" t="n">
-        <v>6794074</v>
+        <v>6793845</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6632,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126164027</v>
+        <v>126160381</v>
       </c>
       <c r="B63" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6643,34 +6643,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431844</v>
+        <v>431734</v>
       </c>
       <c r="R63" t="n">
-        <v>6794158</v>
+        <v>6793794</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126159369</v>
+        <v>126164027</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,34 +6740,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431635</v>
+        <v>431844</v>
       </c>
       <c r="R64" t="n">
-        <v>6793754</v>
+        <v>6794158</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126160807</v>
+        <v>126166809</v>
       </c>
       <c r="B65" t="n">
         <v>78977</v>
@@ -6857,14 +6857,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431738</v>
+        <v>432273</v>
       </c>
       <c r="R65" t="n">
-        <v>6793845</v>
+        <v>6794365</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6891,12 +6891,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6923,10 +6923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126160381</v>
+        <v>126166708</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,34 +6934,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431734</v>
+        <v>432272</v>
       </c>
       <c r="R66" t="n">
-        <v>6793794</v>
+        <v>6794337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7020,10 +7025,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126166809</v>
+        <v>126165342</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7031,21 +7036,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7055,10 +7060,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432273</v>
+        <v>431949</v>
       </c>
       <c r="R67" t="n">
-        <v>6794365</v>
+        <v>6794232</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7117,10 +7122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126166708</v>
+        <v>126162164</v>
       </c>
       <c r="B68" t="n">
-        <v>57653</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7128,39 +7133,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432272</v>
+        <v>431783</v>
       </c>
       <c r="R68" t="n">
-        <v>6794337</v>
+        <v>6794074</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7316,50 +7316,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126157808</v>
+        <v>126161304</v>
       </c>
       <c r="B70" t="n">
-        <v>58025</v>
+        <v>79566</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431582</v>
+        <v>431735</v>
       </c>
       <c r="R70" t="n">
-        <v>6793582</v>
+        <v>6794019</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7381,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7418,10 +7413,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126162912</v>
+        <v>126163869</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>79566</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7429,39 +7424,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431943</v>
+        <v>431844</v>
       </c>
       <c r="R71" t="n">
-        <v>6794014</v>
+        <v>6794158</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7520,10 +7510,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126161304</v>
+        <v>126162912</v>
       </c>
       <c r="B72" t="n">
-        <v>79566</v>
+        <v>57656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7531,34 +7521,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431735</v>
+        <v>431943</v>
       </c>
       <c r="R72" t="n">
-        <v>6794019</v>
+        <v>6794014</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7585,12 +7580,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7617,45 +7612,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126163869</v>
+        <v>126157808</v>
       </c>
       <c r="B73" t="n">
-        <v>79566</v>
+        <v>58025</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431844</v>
+        <v>431582</v>
       </c>
       <c r="R73" t="n">
-        <v>6794158</v>
+        <v>6793582</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126165131</v>
+        <v>126166691</v>
       </c>
       <c r="B77" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431949</v>
+        <v>432272</v>
       </c>
       <c r="R77" t="n">
-        <v>6794232</v>
+        <v>6794337</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126166691</v>
+        <v>126161557</v>
       </c>
       <c r="B78" t="n">
         <v>79595</v>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432272</v>
+        <v>431758</v>
       </c>
       <c r="R78" t="n">
-        <v>6794337</v>
+        <v>6794063</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126161557</v>
+        <v>126161478</v>
       </c>
       <c r="B79" t="n">
         <v>79595</v>
@@ -8235,14 +8235,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431758</v>
+        <v>431764</v>
       </c>
       <c r="R79" t="n">
-        <v>6794063</v>
+        <v>6794018</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126161478</v>
+        <v>126165131</v>
       </c>
       <c r="B80" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,34 +8312,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431764</v>
+        <v>431949</v>
       </c>
       <c r="R80" t="n">
-        <v>6794018</v>
+        <v>6794232</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126157967</v>
+        <v>126163857</v>
       </c>
       <c r="B81" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,34 +8409,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431581</v>
+        <v>431844</v>
       </c>
       <c r="R81" t="n">
-        <v>6793601</v>
+        <v>6794158</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8495,10 +8500,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,21 +8511,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8530,10 +8535,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R82" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8560,12 +8565,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8592,10 +8597,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126163857</v>
+        <v>126161074</v>
       </c>
       <c r="B83" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8603,39 +8608,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431844</v>
+        <v>431755</v>
       </c>
       <c r="R83" t="n">
-        <v>6794158</v>
+        <v>6793917</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8791,10 +8791,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126162862</v>
+        <v>126158198</v>
       </c>
       <c r="B85" t="n">
-        <v>79566</v>
+        <v>75072</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8802,34 +8802,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431942</v>
+        <v>431575</v>
       </c>
       <c r="R85" t="n">
-        <v>6794029</v>
+        <v>6793614</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8888,10 +8888,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126158198</v>
+        <v>126165247</v>
       </c>
       <c r="B86" t="n">
-        <v>75072</v>
+        <v>57653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8899,34 +8899,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431575</v>
+        <v>431949</v>
       </c>
       <c r="R86" t="n">
-        <v>6793614</v>
+        <v>6794232</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8985,7 +8990,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126165247</v>
+        <v>126160693</v>
       </c>
       <c r="B87" t="n">
         <v>57653</v>
@@ -9016,19 +9021,19 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431949</v>
+        <v>431740</v>
       </c>
       <c r="R87" t="n">
-        <v>6794232</v>
+        <v>6793833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9055,12 +9060,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9087,10 +9092,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126160693</v>
+        <v>126162862</v>
       </c>
       <c r="B88" t="n">
-        <v>57653</v>
+        <v>79566</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9098,39 +9103,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431740</v>
+        <v>431942</v>
       </c>
       <c r="R88" t="n">
-        <v>6793833</v>
+        <v>6794029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9674,10 +9674,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126159604</v>
+        <v>126162464</v>
       </c>
       <c r="B94" t="n">
-        <v>79566</v>
+        <v>57653</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9685,34 +9685,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431657</v>
+        <v>431861</v>
       </c>
       <c r="R94" t="n">
-        <v>6793728</v>
+        <v>6794056</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9771,10 +9776,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126163938</v>
+        <v>126159604</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9782,34 +9787,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431844</v>
+        <v>431657</v>
       </c>
       <c r="R95" t="n">
-        <v>6794158</v>
+        <v>6793728</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9868,10 +9873,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126162464</v>
+        <v>126163938</v>
       </c>
       <c r="B96" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9879,39 +9884,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431861</v>
+        <v>431844</v>
       </c>
       <c r="R96" t="n">
-        <v>6794056</v>
+        <v>6794158</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126164968</v>
+        <v>126162132</v>
       </c>
       <c r="B97" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9981,21 +9981,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431934</v>
+        <v>431783</v>
       </c>
       <c r="R97" t="n">
-        <v>6794246</v>
+        <v>6794074</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126167341</v>
+        <v>126166906</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10272,21 +10272,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431682</v>
+        <v>432177</v>
       </c>
       <c r="R100" t="n">
-        <v>6794066</v>
+        <v>6794345</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10332,11 +10332,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10363,7 +10358,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126162132</v>
+        <v>126160391</v>
       </c>
       <c r="B101" t="n">
         <v>78977</v>
@@ -10394,14 +10389,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431783</v>
+        <v>431718</v>
       </c>
       <c r="R101" t="n">
-        <v>6794074</v>
+        <v>6793795</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10460,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126166906</v>
+        <v>126164968</v>
       </c>
       <c r="B102" t="n">
-        <v>91262</v>
+        <v>79595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10471,21 +10466,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10495,10 +10490,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>432177</v>
+        <v>431934</v>
       </c>
       <c r="R102" t="n">
-        <v>6794345</v>
+        <v>6794246</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10557,7 +10552,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126160391</v>
+        <v>126167341</v>
       </c>
       <c r="B103" t="n">
         <v>78977</v>
@@ -10588,14 +10583,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431718</v>
+        <v>431682</v>
       </c>
       <c r="R103" t="n">
-        <v>6793795</v>
+        <v>6794066</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10628,6 +10623,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11190,10 +11190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126189457</v>
+        <v>126162009</v>
       </c>
       <c r="B109" t="n">
-        <v>79009</v>
+        <v>78735</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11201,21 +11201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11224,14 +11224,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431586</v>
+        <v>431754</v>
       </c>
       <c r="R109" t="n">
-        <v>6793587</v>
+        <v>6794068</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11294,17 +11294,17 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126162009</v>
+        <v>126188368</v>
       </c>
       <c r="B110" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11312,21 +11312,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11335,14 +11335,14 @@
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431754</v>
+        <v>431698</v>
       </c>
       <c r="R110" t="n">
-        <v>6794068</v>
+        <v>6793851</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11384,7 +11384,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11405,17 +11410,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126188368</v>
+        <v>126189457</v>
       </c>
       <c r="B111" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11423,21 +11428,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11450,10 +11455,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431698</v>
+        <v>431586</v>
       </c>
       <c r="R111" t="n">
-        <v>6793851</v>
+        <v>6793587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11485,7 +11490,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11495,12 +11500,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Fullt på träden</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126174681</v>
+        <v>126161529</v>
       </c>
       <c r="B115" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11879,41 +11879,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431802</v>
+        <v>431705</v>
       </c>
       <c r="R115" t="n">
-        <v>6794020</v>
+        <v>6794050</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11943,40 +11936,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126161529</v>
+        <v>126174681</v>
       </c>
       <c r="B116" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11984,34 +11986,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431705</v>
+        <v>431802</v>
       </c>
       <c r="R116" t="n">
-        <v>6794050</v>
+        <v>6794020</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12041,49 +12050,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126174710</v>
+        <v>126190566</v>
       </c>
       <c r="B117" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12091,41 +12091,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431847</v>
+        <v>431683</v>
       </c>
       <c r="R117" t="n">
-        <v>6794063</v>
+        <v>6793850</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12155,40 +12156,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126174513</v>
+        <v>126175046</v>
       </c>
       <c r="B118" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12196,21 +12206,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -12227,10 +12237,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431721</v>
+        <v>432130</v>
       </c>
       <c r="R118" t="n">
-        <v>6793745</v>
+        <v>6794314</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12290,10 +12300,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126190566</v>
+        <v>126174710</v>
       </c>
       <c r="B119" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12301,42 +12311,41 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431683</v>
+        <v>431847</v>
       </c>
       <c r="R119" t="n">
-        <v>6793850</v>
+        <v>6794063</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12366,49 +12375,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126175046</v>
+        <v>126174513</v>
       </c>
       <c r="B120" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12416,21 +12416,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>432130</v>
+        <v>431721</v>
       </c>
       <c r="R120" t="n">
-        <v>6794314</v>
+        <v>6793745</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12732,53 +12732,52 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126165489</v>
+        <v>126174983</v>
       </c>
       <c r="B123" t="n">
-        <v>56848</v>
+        <v>79595</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>432050</v>
+        <v>432144</v>
       </c>
       <c r="R123" t="n">
-        <v>6794210</v>
+        <v>6794303</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12808,44 +12807,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning, fjolårets, på stubbe</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -12972,52 +12957,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126174983</v>
+        <v>126165489</v>
       </c>
       <c r="B125" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>432144</v>
+        <v>432050</v>
       </c>
       <c r="R125" t="n">
-        <v>6794303</v>
+        <v>6794210</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13047,30 +13033,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning, fjolårets, på stubbe</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13184,50 +13184,52 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126189221</v>
+        <v>126174545</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431686</v>
+        <v>431721</v>
       </c>
       <c r="R127" t="n">
-        <v>6793927</v>
+        <v>6793766</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13257,19 +13259,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13285,64 +13277,62 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126174545</v>
+        <v>126189221</v>
       </c>
       <c r="B128" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431721</v>
+        <v>431686</v>
       </c>
       <c r="R128" t="n">
-        <v>6793766</v>
+        <v>6793927</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13372,9 +13362,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13390,12 +13390,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13732,10 +13732,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126189975</v>
+        <v>126165527</v>
       </c>
       <c r="B132" t="n">
-        <v>92724</v>
+        <v>78735</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13743,21 +13743,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13766,14 +13766,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431647</v>
+        <v>432037</v>
       </c>
       <c r="R132" t="n">
-        <v>6794014</v>
+        <v>6794186</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13836,17 +13836,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126165527</v>
+        <v>126189975</v>
       </c>
       <c r="B133" t="n">
-        <v>78735</v>
+        <v>92724</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13854,21 +13854,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13877,14 +13877,14 @@
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>432037</v>
+        <v>431647</v>
       </c>
       <c r="R133" t="n">
-        <v>6794186</v>
+        <v>6794014</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13947,34 +13947,34 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126190225</v>
+        <v>126190276</v>
       </c>
       <c r="B134" t="n">
-        <v>56848</v>
+        <v>56232</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -13982,11 +13982,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
@@ -13997,14 +13993,14 @@
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431908</v>
+        <v>431609</v>
       </c>
       <c r="R134" t="n">
-        <v>6794091</v>
+        <v>6793764</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14036,7 +14032,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14046,7 +14042,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14066,60 +14062,57 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126190276</v>
+        <v>126166597</v>
       </c>
       <c r="B135" t="n">
-        <v>56232</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431609</v>
+        <v>432054</v>
       </c>
       <c r="R135" t="n">
-        <v>6793764</v>
+        <v>6794331</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14151,7 +14144,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14161,7 +14154,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14170,6 +14163,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14181,17 +14175,17 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126166597</v>
+        <v>126190225</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>56848</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14199,39 +14193,46 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>432054</v>
+        <v>431908</v>
       </c>
       <c r="R136" t="n">
-        <v>6794331</v>
+        <v>6794091</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14263,7 +14264,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14273,7 +14274,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14282,7 +14283,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14406,10 +14406,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126188869</v>
+        <v>126188589</v>
       </c>
       <c r="B138" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14417,21 +14417,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14444,10 +14444,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431661</v>
+        <v>431672</v>
       </c>
       <c r="R138" t="n">
-        <v>6793741</v>
+        <v>6794047</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14489,7 +14489,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14517,7 +14522,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126188589</v>
+        <v>126188441</v>
       </c>
       <c r="B139" t="n">
         <v>78977</v>
@@ -14555,10 +14560,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431672</v>
+        <v>431692</v>
       </c>
       <c r="R139" t="n">
-        <v>6794047</v>
+        <v>6793928</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14590,7 +14595,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14600,12 +14605,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14633,10 +14633,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126188441</v>
+        <v>126188869</v>
       </c>
       <c r="B140" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14644,21 +14644,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431692</v>
+        <v>431661</v>
       </c>
       <c r="R140" t="n">
-        <v>6793928</v>
+        <v>6793741</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14744,48 +14744,57 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126161782</v>
+        <v>126190311</v>
       </c>
       <c r="B141" t="n">
-        <v>78736</v>
+        <v>97230</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431721</v>
+        <v>431597</v>
       </c>
       <c r="R141" t="n">
-        <v>6794089</v>
+        <v>6793607</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14817,7 +14826,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14827,7 +14836,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14855,7 +14864,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126174664</v>
+        <v>126189837</v>
       </c>
       <c r="B142" t="n">
         <v>57656</v>
@@ -14883,25 +14892,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431803</v>
+        <v>431661</v>
       </c>
       <c r="R142" t="n">
-        <v>6793998</v>
+        <v>6793926</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14931,9 +14944,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14948,19 +14976,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126189837</v>
+        <v>126174664</v>
       </c>
       <c r="B143" t="n">
         <v>57656</v>
@@ -14988,29 +15016,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431661</v>
+        <v>431803</v>
       </c>
       <c r="R143" t="n">
-        <v>6793926</v>
+        <v>6793998</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15040,24 +15064,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15072,12 +15081,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15185,57 +15194,48 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126190311</v>
+        <v>126161782</v>
       </c>
       <c r="B145" t="n">
-        <v>97230</v>
+        <v>78736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431597</v>
+        <v>431721</v>
       </c>
       <c r="R145" t="n">
-        <v>6793607</v>
+        <v>6794089</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15410,10 +15410,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126175021</v>
+        <v>126185018</v>
       </c>
       <c r="B147" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15421,28 +15421,24 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -15452,10 +15448,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>432130</v>
+        <v>431898</v>
       </c>
       <c r="R147" t="n">
-        <v>6794314</v>
+        <v>6794103</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15485,9 +15481,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15503,22 +15509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126188626</v>
+        <v>126175021</v>
       </c>
       <c r="B148" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15526,42 +15532,41 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431672</v>
+        <v>432130</v>
       </c>
       <c r="R148" t="n">
-        <v>6794047</v>
+        <v>6794314</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15591,54 +15596,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Hästmyror i stubben</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126185018</v>
+        <v>126188626</v>
       </c>
       <c r="B149" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15646,37 +15637,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431898</v>
+        <v>431672</v>
       </c>
       <c r="R149" t="n">
-        <v>6794103</v>
+        <v>6794047</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15708,7 +15704,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15718,7 +15714,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Hästmyror i stubben</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15727,7 +15728,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15746,7 +15746,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126165721</v>
+        <v>126165414</v>
       </c>
       <c r="B150" t="n">
         <v>56848</v>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>432067</v>
+        <v>432012</v>
       </c>
       <c r="R150" t="n">
-        <v>6794181</v>
+        <v>6794220</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15834,12 +15834,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Barr</t>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15859,14 +15859,14 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126165414</v>
+        <v>126165721</v>
       </c>
       <c r="B151" t="n">
         <v>56848</v>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>432012</v>
+        <v>432067</v>
       </c>
       <c r="R151" t="n">
-        <v>6794220</v>
+        <v>6794181</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15944,7 +15944,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16097,10 +16097,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126189054</v>
+        <v>126174924</v>
       </c>
       <c r="B153" t="n">
-        <v>79595</v>
+        <v>79009</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16108,37 +16108,41 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431660</v>
+        <v>431893</v>
       </c>
       <c r="R153" t="n">
-        <v>6793737</v>
+        <v>6794043</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16168,19 +16172,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>12:57</t>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16196,53 +16195,58 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126174574</v>
+        <v>126188337</v>
       </c>
       <c r="B154" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -16250,10 +16254,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431765</v>
+        <v>431609</v>
       </c>
       <c r="R154" t="n">
-        <v>6793901</v>
+        <v>6793762</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16283,9 +16287,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16301,69 +16315,60 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126188337</v>
+        <v>126189054</v>
       </c>
       <c r="B155" t="n">
-        <v>98269</v>
+        <v>79595</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431609</v>
+        <v>431660</v>
       </c>
       <c r="R155" t="n">
-        <v>6793762</v>
+        <v>6793737</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16395,7 +16400,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16405,7 +16410,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16426,17 +16431,17 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126174924</v>
+        <v>126174574</v>
       </c>
       <c r="B156" t="n">
-        <v>79009</v>
+        <v>79595</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16444,21 +16449,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -16475,10 +16480,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>431893</v>
+        <v>431765</v>
       </c>
       <c r="R156" t="n">
-        <v>6794043</v>
+        <v>6793901</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16511,11 +16516,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16543,53 +16543,54 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126165393</v>
+        <v>126174659</v>
       </c>
       <c r="B157" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432012</v>
+        <v>431731</v>
       </c>
       <c r="R157" t="n">
-        <v>6794220</v>
+        <v>6793834</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16619,93 +16620,83 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126174659</v>
+        <v>126165393</v>
       </c>
       <c r="B158" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>431731</v>
+        <v>432012</v>
       </c>
       <c r="R158" t="n">
-        <v>6793834</v>
+        <v>6794220</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16735,82 +16726,88 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126174961</v>
+        <v>126162636</v>
       </c>
       <c r="B159" t="n">
-        <v>79595</v>
+        <v>58025</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>432073</v>
+        <v>431906</v>
       </c>
       <c r="R159" t="n">
-        <v>6794217</v>
+        <v>6794099</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16840,79 +16837,96 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126162636</v>
+        <v>126174961</v>
       </c>
       <c r="B160" t="n">
-        <v>58025</v>
+        <v>79595</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>431906</v>
+        <v>432073</v>
       </c>
       <c r="R160" t="n">
-        <v>6794099</v>
+        <v>6794217</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16942,44 +16956,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17101,10 +17101,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126165571</v>
+        <v>126174682</v>
       </c>
       <c r="B162" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17112,34 +17112,41 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>432034</v>
+        <v>431789</v>
       </c>
       <c r="R162" t="n">
-        <v>6794182</v>
+        <v>6794033</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17169,91 +17176,86 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126174682</v>
+        <v>126165703</v>
       </c>
       <c r="B163" t="n">
-        <v>79595</v>
+        <v>92532</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>431789</v>
+        <v>432067</v>
       </c>
       <c r="R163" t="n">
-        <v>6794033</v>
+        <v>6794181</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17283,9 +17285,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17301,68 +17318,57 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126165703</v>
+        <v>126165571</v>
       </c>
       <c r="B164" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>432067</v>
+        <v>432034</v>
       </c>
       <c r="R164" t="n">
-        <v>6794181</v>
+        <v>6794182</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17394,7 +17400,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17404,12 +17410,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17418,7 +17419,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17430,17 +17430,17 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126192573</v>
+        <v>126189897</v>
       </c>
       <c r="B165" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17448,26 +17448,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -17475,10 +17484,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>431790</v>
+        <v>431648</v>
       </c>
       <c r="R165" t="n">
-        <v>6794069</v>
+        <v>6793779</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17510,7 +17519,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17520,7 +17529,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17529,7 +17543,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17541,17 +17554,17 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126189897</v>
+        <v>126192573</v>
       </c>
       <c r="B166" t="n">
-        <v>57656</v>
+        <v>79595</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17559,35 +17572,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17595,10 +17599,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431648</v>
+        <v>431790</v>
       </c>
       <c r="R166" t="n">
-        <v>6793779</v>
+        <v>6794069</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17630,7 +17634,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17640,12 +17644,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Hack efter tretåig hackspett i tallåga.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17654,6 +17653,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17665,17 +17665,17 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126162572</v>
+        <v>126167044</v>
       </c>
       <c r="B167" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17683,26 +17683,27 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -17710,10 +17711,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>431906</v>
+        <v>432002</v>
       </c>
       <c r="R167" t="n">
-        <v>6794099</v>
+        <v>6794336</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17745,7 +17746,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17755,12 +17756,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17769,7 +17765,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17781,56 +17776,57 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126167044</v>
+        <v>126188293</v>
       </c>
       <c r="B168" t="n">
-        <v>57653</v>
+        <v>5176</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>432002</v>
+        <v>431642</v>
       </c>
       <c r="R168" t="n">
-        <v>6794336</v>
+        <v>6794010</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17862,7 +17858,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17872,7 +17868,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17881,6 +17877,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17892,57 +17889,59 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126188293</v>
+        <v>126174530</v>
       </c>
       <c r="B169" t="n">
-        <v>5176</v>
+        <v>79595</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>431642</v>
+        <v>431675</v>
       </c>
       <c r="R169" t="n">
-        <v>6794010</v>
+        <v>6793721</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17972,19 +17971,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18000,19 +17989,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126174530</v>
+        <v>126174557</v>
       </c>
       <c r="B170" t="n">
         <v>79595</v>
@@ -18054,10 +18043,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>431675</v>
+        <v>431730</v>
       </c>
       <c r="R170" t="n">
-        <v>6793721</v>
+        <v>6793838</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18117,10 +18106,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126174557</v>
+        <v>126162572</v>
       </c>
       <c r="B171" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18128,41 +18117,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>431730</v>
+        <v>431906</v>
       </c>
       <c r="R171" t="n">
-        <v>6793838</v>
+        <v>6794099</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18192,9 +18177,24 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18210,12 +18210,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -19834,7 +19834,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126390231</v>
+        <v>126392771</v>
       </c>
       <c r="B188" t="n">
         <v>78977</v>
@@ -19865,14 +19865,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>431576</v>
+        <v>431749</v>
       </c>
       <c r="R188" t="n">
-        <v>6793904</v>
+        <v>6794238</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19904,7 +19904,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19941,7 +19941,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126390354</v>
+        <v>126390231</v>
       </c>
       <c r="B189" t="n">
         <v>78977</v>
@@ -19972,14 +19972,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>431564</v>
+        <v>431576</v>
       </c>
       <c r="R189" t="n">
-        <v>6793938</v>
+        <v>6793904</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20048,7 +20048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126392771</v>
+        <v>126390354</v>
       </c>
       <c r="B190" t="n">
         <v>78977</v>
@@ -20079,14 +20079,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Skarpmyrarna, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>431749</v>
+        <v>431564</v>
       </c>
       <c r="R190" t="n">
-        <v>6794238</v>
+        <v>6793938</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20690,10 +20690,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126392284</v>
+        <v>126391910</v>
       </c>
       <c r="B196" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20701,21 +20701,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20725,10 +20725,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>431729</v>
+        <v>431709</v>
       </c>
       <c r="R196" t="n">
-        <v>6794249</v>
+        <v>6794201</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20797,10 +20797,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126391910</v>
+        <v>126392284</v>
       </c>
       <c r="B197" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20808,21 +20808,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>431709</v>
+        <v>431729</v>
       </c>
       <c r="R197" t="n">
-        <v>6794201</v>
+        <v>6794249</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126159713</v>
+        <v>126166842</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,37 +3402,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431676</v>
+        <v>432245</v>
       </c>
       <c r="R30" t="n">
-        <v>6793755</v>
+        <v>6794369</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3488,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126165139</v>
+        <v>126161538</v>
       </c>
       <c r="B31" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431949</v>
+        <v>431778</v>
       </c>
       <c r="R31" t="n">
-        <v>6794232</v>
+        <v>6794048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126162787</v>
+        <v>126162525</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431921</v>
+        <v>431861</v>
       </c>
       <c r="R32" t="n">
-        <v>6794053</v>
+        <v>6794056</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3682,7 +3687,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126159766</v>
+        <v>126159713</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -3717,13 +3722,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431687</v>
+        <v>431676</v>
       </c>
       <c r="R33" t="n">
-        <v>6793778</v>
+        <v>6793755</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126161265</v>
+        <v>126165139</v>
       </c>
       <c r="B34" t="n">
         <v>79595</v>
@@ -3810,14 +3815,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431735</v>
+        <v>431949</v>
       </c>
       <c r="R34" t="n">
-        <v>6794019</v>
+        <v>6794232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3844,12 +3849,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3876,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126161051</v>
+        <v>126162787</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3907,14 +3912,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431757</v>
+        <v>431921</v>
       </c>
       <c r="R35" t="n">
-        <v>6793912</v>
+        <v>6794053</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3941,12 +3946,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3973,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126161615</v>
+        <v>126159766</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4004,14 +4009,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431758</v>
+        <v>431687</v>
       </c>
       <c r="R36" t="n">
-        <v>6794063</v>
+        <v>6793778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126166842</v>
+        <v>126161265</v>
       </c>
       <c r="B37" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4081,39 +4086,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432245</v>
+        <v>431735</v>
       </c>
       <c r="R37" t="n">
-        <v>6794369</v>
+        <v>6794019</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161538</v>
+        <v>126161051</v>
       </c>
       <c r="B38" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431778</v>
+        <v>431757</v>
       </c>
       <c r="R38" t="n">
-        <v>6794048</v>
+        <v>6793912</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126162525</v>
+        <v>126161615</v>
       </c>
       <c r="B39" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431861</v>
+        <v>431758</v>
       </c>
       <c r="R39" t="n">
-        <v>6794056</v>
+        <v>6794063</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126159852</v>
+        <v>126162912</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7230,34 +7230,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431733</v>
+        <v>431943</v>
       </c>
       <c r="R69" t="n">
-        <v>6793772</v>
+        <v>6794014</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7316,7 +7321,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126161304</v>
+        <v>126163869</v>
       </c>
       <c r="B70" t="n">
         <v>79566</v>
@@ -7347,14 +7352,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431735</v>
+        <v>431844</v>
       </c>
       <c r="R70" t="n">
-        <v>6794019</v>
+        <v>6794158</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7381,12 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7413,10 +7418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126163869</v>
+        <v>126159852</v>
       </c>
       <c r="B71" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7424,34 +7429,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431844</v>
+        <v>431733</v>
       </c>
       <c r="R71" t="n">
-        <v>6794158</v>
+        <v>6793772</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7510,10 +7515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126162912</v>
+        <v>126161304</v>
       </c>
       <c r="B72" t="n">
-        <v>57656</v>
+        <v>79566</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7521,39 +7526,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431943</v>
+        <v>431735</v>
       </c>
       <c r="R72" t="n">
-        <v>6794014</v>
+        <v>6794019</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8010,10 +8010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126166691</v>
+        <v>126165131</v>
       </c>
       <c r="B77" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432272</v>
+        <v>431949</v>
       </c>
       <c r="R77" t="n">
-        <v>6794337</v>
+        <v>6794232</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126161557</v>
+        <v>126166691</v>
       </c>
       <c r="B78" t="n">
         <v>79595</v>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431758</v>
+        <v>432272</v>
       </c>
       <c r="R78" t="n">
-        <v>6794063</v>
+        <v>6794337</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126161478</v>
+        <v>126161557</v>
       </c>
       <c r="B79" t="n">
         <v>79595</v>
@@ -8235,14 +8235,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431764</v>
+        <v>431758</v>
       </c>
       <c r="R79" t="n">
-        <v>6794018</v>
+        <v>6794063</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126165131</v>
+        <v>126161478</v>
       </c>
       <c r="B80" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,34 +8312,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431949</v>
+        <v>431764</v>
       </c>
       <c r="R80" t="n">
-        <v>6794232</v>
+        <v>6794018</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126163857</v>
+        <v>126157967</v>
       </c>
       <c r="B81" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,39 +8409,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431844</v>
+        <v>431581</v>
       </c>
       <c r="R81" t="n">
-        <v>6794158</v>
+        <v>6793601</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8500,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126157967</v>
+        <v>126163857</v>
       </c>
       <c r="B82" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8511,34 +8506,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431581</v>
+        <v>431844</v>
       </c>
       <c r="R82" t="n">
-        <v>6793601</v>
+        <v>6794158</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11643,50 +11643,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126163646</v>
+        <v>126161529</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431898</v>
+        <v>431705</v>
       </c>
       <c r="R113" t="n">
-        <v>6794103</v>
+        <v>6794050</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11718,7 +11713,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11728,12 +11723,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11742,7 +11732,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11761,43 +11750,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126174973</v>
+        <v>126174681</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79566</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -11805,10 +11792,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>432045</v>
+        <v>431802</v>
       </c>
       <c r="R114" t="n">
-        <v>6794330</v>
+        <v>6794020</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11868,45 +11855,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126161529</v>
+        <v>126163646</v>
       </c>
       <c r="B115" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431705</v>
+        <v>431898</v>
       </c>
       <c r="R115" t="n">
-        <v>6794050</v>
+        <v>6794103</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,7 +11930,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11948,7 +11940,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11957,6 +11954,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -11975,41 +11973,43 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126174681</v>
+        <v>126174973</v>
       </c>
       <c r="B116" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12017,10 +12017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431802</v>
+        <v>432045</v>
       </c>
       <c r="R116" t="n">
-        <v>6794020</v>
+        <v>6794330</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12510,53 +12510,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B121" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R121" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12588,7 +12580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12598,7 +12590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12625,45 +12617,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R122" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13625,10 +13625,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126162062</v>
+        <v>126189975</v>
       </c>
       <c r="B131" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13636,34 +13636,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431788</v>
+        <v>431647</v>
       </c>
       <c r="R131" t="n">
-        <v>6794108</v>
+        <v>6794014</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13695,7 +13698,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13705,7 +13708,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13714,6 +13717,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13725,55 +13729,64 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126165527</v>
+        <v>126190225</v>
       </c>
       <c r="B132" t="n">
-        <v>78735</v>
+        <v>56848</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>432037</v>
+        <v>431908</v>
       </c>
       <c r="R132" t="n">
-        <v>6794186</v>
+        <v>6794091</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13805,7 +13818,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13815,7 +13828,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13824,7 +13837,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13843,10 +13855,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126189975</v>
+        <v>126190276</v>
       </c>
       <c r="B133" t="n">
-        <v>92724</v>
+        <v>56232</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13854,37 +13866,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2079</v>
+        <v>206004</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431647</v>
+        <v>431609</v>
       </c>
       <c r="R133" t="n">
-        <v>6794014</v>
+        <v>6793764</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13916,7 +13933,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13926,7 +13943,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13935,7 +13952,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13947,60 +13963,57 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126190276</v>
+        <v>126166597</v>
       </c>
       <c r="B134" t="n">
-        <v>56232</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431609</v>
+        <v>432054</v>
       </c>
       <c r="R134" t="n">
-        <v>6793764</v>
+        <v>6794331</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14032,7 +14045,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14042,7 +14055,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14051,6 +14064,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14062,57 +14076,52 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126166597</v>
+        <v>126162062</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>432054</v>
+        <v>431788</v>
       </c>
       <c r="R135" t="n">
-        <v>6794331</v>
+        <v>6794108</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14144,7 +14153,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14154,7 +14163,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14163,7 +14172,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14175,64 +14183,55 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126190225</v>
+        <v>126165527</v>
       </c>
       <c r="B136" t="n">
-        <v>56848</v>
+        <v>78735</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431908</v>
+        <v>432037</v>
       </c>
       <c r="R136" t="n">
-        <v>6794091</v>
+        <v>6794186</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14264,7 +14263,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14274,7 +14273,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14283,6 +14282,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14744,57 +14744,48 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126190311</v>
+        <v>126174633</v>
       </c>
       <c r="B141" t="n">
-        <v>97230</v>
+        <v>79566</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431597</v>
+        <v>431765</v>
       </c>
       <c r="R141" t="n">
-        <v>6793607</v>
+        <v>6793901</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14824,19 +14815,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14852,22 +14833,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126189837</v>
+        <v>126161782</v>
       </c>
       <c r="B142" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14875,46 +14856,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431661</v>
+        <v>431721</v>
       </c>
       <c r="R142" t="n">
-        <v>6793926</v>
+        <v>6794089</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14946,7 +14918,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -14956,12 +14928,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14970,6 +14937,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14981,60 +14949,64 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126174664</v>
+        <v>126190311</v>
       </c>
       <c r="B143" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431803</v>
+        <v>431597</v>
       </c>
       <c r="R143" t="n">
-        <v>6793998</v>
+        <v>6793607</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15064,39 +15036,50 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126174633</v>
+        <v>126189837</v>
       </c>
       <c r="B144" t="n">
-        <v>79566</v>
+        <v>57656</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15104,37 +15087,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431765</v>
+        <v>431661</v>
       </c>
       <c r="R144" t="n">
-        <v>6793901</v>
+        <v>6793926</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15164,40 +15156,54 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126161782</v>
+        <v>126174664</v>
       </c>
       <c r="B145" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15205,37 +15211,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431721</v>
+        <v>431803</v>
       </c>
       <c r="R145" t="n">
-        <v>6794089</v>
+        <v>6793998</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15265,50 +15276,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126174690</v>
+        <v>126185018</v>
       </c>
       <c r="B146" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15316,28 +15316,24 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
@@ -15347,10 +15343,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431789</v>
+        <v>431898</v>
       </c>
       <c r="R146" t="n">
-        <v>6794033</v>
+        <v>6794103</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15380,9 +15376,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15398,22 +15404,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126185018</v>
+        <v>126175021</v>
       </c>
       <c r="B147" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15421,24 +15427,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -15448,10 +15458,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431898</v>
+        <v>432130</v>
       </c>
       <c r="R147" t="n">
-        <v>6794103</v>
+        <v>6794314</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15481,19 +15491,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,22 +15509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126175021</v>
+        <v>126188626</v>
       </c>
       <c r="B148" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15532,41 +15532,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>432130</v>
+        <v>431672</v>
       </c>
       <c r="R148" t="n">
-        <v>6794314</v>
+        <v>6794047</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15596,62 +15597,76 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Hästmyror i stubben</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126188626</v>
+        <v>126165414</v>
       </c>
       <c r="B149" t="n">
-        <v>57653</v>
+        <v>56848</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15659,20 +15674,20 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431672</v>
+        <v>432012</v>
       </c>
       <c r="R149" t="n">
-        <v>6794047</v>
+        <v>6794220</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15704,7 +15719,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15714,12 +15729,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Hästmyror i stubben</t>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15739,14 +15754,14 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126165414</v>
+        <v>126165721</v>
       </c>
       <c r="B150" t="n">
         <v>56848</v>
@@ -15789,10 +15804,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>432012</v>
+        <v>432067</v>
       </c>
       <c r="R150" t="n">
-        <v>6794220</v>
+        <v>6794181</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15824,7 +15839,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15834,12 +15849,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+          <t>Barr</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15859,60 +15874,59 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126165721</v>
+        <v>126174690</v>
       </c>
       <c r="B151" t="n">
-        <v>56848</v>
+        <v>79566</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>432067</v>
+        <v>431789</v>
       </c>
       <c r="R151" t="n">
-        <v>6794181</v>
+        <v>6794033</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15942,44 +15956,30 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Barr</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16097,10 +16097,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126174924</v>
+        <v>126189054</v>
       </c>
       <c r="B153" t="n">
-        <v>79009</v>
+        <v>79595</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16108,41 +16108,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431893</v>
+        <v>431660</v>
       </c>
       <c r="R153" t="n">
-        <v>6794043</v>
+        <v>6793737</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16172,14 +16168,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16195,58 +16196,53 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126188337</v>
+        <v>126174574</v>
       </c>
       <c r="B154" t="n">
-        <v>98269</v>
+        <v>79595</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -16254,10 +16250,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431609</v>
+        <v>431765</v>
       </c>
       <c r="R154" t="n">
-        <v>6793762</v>
+        <v>6793901</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16287,19 +16283,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16315,22 +16301,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126189054</v>
+        <v>126174924</v>
       </c>
       <c r="B155" t="n">
-        <v>79595</v>
+        <v>79009</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16338,37 +16324,41 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431660</v>
+        <v>431893</v>
       </c>
       <c r="R155" t="n">
-        <v>6793737</v>
+        <v>6794043</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16398,19 +16388,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:57</t>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16426,53 +16411,58 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126174574</v>
+        <v>126188337</v>
       </c>
       <c r="B156" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16480,10 +16470,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>431765</v>
+        <v>431609</v>
       </c>
       <c r="R156" t="n">
-        <v>6793901</v>
+        <v>6793762</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16513,9 +16503,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16531,12 +16531,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17437,10 +17437,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126189897</v>
+        <v>126192573</v>
       </c>
       <c r="B165" t="n">
-        <v>57656</v>
+        <v>79595</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17448,35 +17448,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -17484,10 +17475,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>431648</v>
+        <v>431790</v>
       </c>
       <c r="R165" t="n">
-        <v>6793779</v>
+        <v>6794069</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17519,7 +17510,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17529,12 +17520,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Hack efter tretåig hackspett i tallåga.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17543,6 +17529,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17554,17 +17541,17 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126192573</v>
+        <v>126189897</v>
       </c>
       <c r="B166" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17572,26 +17559,35 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17599,10 +17595,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431790</v>
+        <v>431648</v>
       </c>
       <c r="R166" t="n">
-        <v>6794069</v>
+        <v>6793779</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17634,7 +17630,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17644,7 +17640,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Hack efter tretåig hackspett i tallåga.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17653,7 +17654,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022251</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022241</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022243</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022253</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022256</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126022260</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126022264</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126022240</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126022236</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126022254</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126022257</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126022238</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022246</v>
+        <v>126022267</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431785</v>
+        <v>431663</v>
       </c>
       <c r="R14" t="n">
-        <v>6793548</v>
+        <v>6793516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022267</v>
+        <v>126022232</v>
       </c>
       <c r="B15" t="n">
-        <v>78644</v>
+        <v>79569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431663</v>
+        <v>431615</v>
       </c>
       <c r="R15" t="n">
-        <v>6793516</v>
+        <v>6793508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R16" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R17" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B18" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R18" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>126022247</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126022255</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126022237</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126022262</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126022245</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126022250</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126022242</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126022248</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126022263</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>126022252</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>126022239</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126166842</v>
+        <v>126161538</v>
       </c>
       <c r="B30" t="n">
-        <v>57653</v>
+        <v>78739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,39 +3402,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432245</v>
+        <v>431778</v>
       </c>
       <c r="R30" t="n">
-        <v>6794369</v>
+        <v>6794048</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126161538</v>
+        <v>126162525</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431778</v>
+        <v>431861</v>
       </c>
       <c r="R31" t="n">
-        <v>6794048</v>
+        <v>6794056</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126162525</v>
+        <v>126166842</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>57654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,34 +3596,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431861</v>
+        <v>432245</v>
       </c>
       <c r="R32" t="n">
-        <v>6794056</v>
+        <v>6794369</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126159713</v>
+        <v>126161615</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3718,17 +3718,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431676</v>
+        <v>431758</v>
       </c>
       <c r="R33" t="n">
-        <v>6793755</v>
+        <v>6794063</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126165139</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126162787</v>
+        <v>126161265</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,34 +3892,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431921</v>
+        <v>431735</v>
       </c>
       <c r="R35" t="n">
-        <v>6794053</v>
+        <v>6794019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3946,12 +3946,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126159766</v>
+        <v>126159713</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431687</v>
+        <v>431676</v>
       </c>
       <c r="R36" t="n">
-        <v>6793778</v>
+        <v>6793755</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126161265</v>
+        <v>126159766</v>
       </c>
       <c r="B37" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431735</v>
+        <v>431687</v>
       </c>
       <c r="R37" t="n">
-        <v>6794019</v>
+        <v>6793778</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4175,7 +4175,7 @@
         <v>126161051</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126161615</v>
+        <v>126162787</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431758</v>
+        <v>431921</v>
       </c>
       <c r="R39" t="n">
-        <v>6794063</v>
+        <v>6794053</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126166682</v>
+        <v>126167392</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432272</v>
+        <v>431653</v>
       </c>
       <c r="R40" t="n">
-        <v>6794337</v>
+        <v>6793960</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4437,6 +4437,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4463,10 +4468,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126164975</v>
+        <v>126162274</v>
       </c>
       <c r="B41" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4474,21 +4479,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4503,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431934</v>
+        <v>431815</v>
       </c>
       <c r="R41" t="n">
-        <v>6794246</v>
+        <v>6794067</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4560,10 +4565,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126156950</v>
+        <v>126162811</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4591,14 +4596,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431647</v>
+        <v>431942</v>
       </c>
       <c r="R42" t="n">
-        <v>6793602</v>
+        <v>6794029</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,10 +4662,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126167392</v>
+        <v>126156950</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4688,14 +4693,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431653</v>
+        <v>431647</v>
       </c>
       <c r="R43" t="n">
-        <v>6793960</v>
+        <v>6793602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126162274</v>
+        <v>126159534</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431815</v>
+        <v>431657</v>
       </c>
       <c r="R44" t="n">
-        <v>6794067</v>
+        <v>6793728</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126162811</v>
+        <v>126161498</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,34 +4867,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431942</v>
+        <v>431776</v>
       </c>
       <c r="R45" t="n">
-        <v>6794029</v>
+        <v>6794017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4953,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126159534</v>
+        <v>126165020</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4964,34 +4969,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431657</v>
+        <v>431934</v>
       </c>
       <c r="R46" t="n">
-        <v>6793728</v>
+        <v>6794246</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5050,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126161498</v>
+        <v>126164975</v>
       </c>
       <c r="B47" t="n">
-        <v>57653</v>
+        <v>79569</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5061,39 +5071,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431776</v>
+        <v>431934</v>
       </c>
       <c r="R47" t="n">
-        <v>6794017</v>
+        <v>6794246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5152,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126165020</v>
+        <v>126166682</v>
       </c>
       <c r="B48" t="n">
-        <v>57653</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,39 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431934</v>
+        <v>432272</v>
       </c>
       <c r="R48" t="n">
-        <v>6794246</v>
+        <v>6794337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5285,14 +5285,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R49" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126161213</v>
+        <v>126162332</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5382,14 +5382,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431756</v>
+        <v>431839</v>
       </c>
       <c r="R50" t="n">
-        <v>6793994</v>
+        <v>6794073</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5451,7 +5451,7 @@
         <v>126160760</v>
       </c>
       <c r="B51" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5545,50 +5545,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126162045</v>
+        <v>126160189</v>
       </c>
       <c r="B52" t="n">
-        <v>58025</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431758</v>
+        <v>431763</v>
       </c>
       <c r="R52" t="n">
-        <v>6794063</v>
+        <v>6793789</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5647,10 +5642,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126157004</v>
+        <v>126157375</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5749,10 +5744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126160189</v>
+        <v>126162207</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,34 +5755,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431763</v>
+        <v>431783</v>
       </c>
       <c r="R54" t="n">
-        <v>6793789</v>
+        <v>6794074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,45 +5841,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126162207</v>
+        <v>126162045</v>
       </c>
       <c r="B55" t="n">
-        <v>79595</v>
+        <v>58027</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431783</v>
+        <v>431758</v>
       </c>
       <c r="R55" t="n">
-        <v>6794074</v>
+        <v>6794063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126166910</v>
+        <v>126162541</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432177</v>
+        <v>431861</v>
       </c>
       <c r="R56" t="n">
-        <v>6794345</v>
+        <v>6794056</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126162541</v>
+        <v>126165216</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431861</v>
+        <v>431949</v>
       </c>
       <c r="R57" t="n">
-        <v>6794056</v>
+        <v>6794232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126167237</v>
+        <v>126166910</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432161</v>
+        <v>432177</v>
       </c>
       <c r="R58" t="n">
-        <v>6794303</v>
+        <v>6794345</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6208,11 +6208,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6239,10 +6234,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126165216</v>
+        <v>126167107</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6274,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431949</v>
+        <v>432161</v>
       </c>
       <c r="R59" t="n">
-        <v>6794232</v>
+        <v>6794303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6310,6 +6305,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6339,7 +6339,7 @@
         <v>126162778</v>
       </c>
       <c r="B60" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126159369</v>
+        <v>126166809</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,14 +6469,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431635</v>
+        <v>432273</v>
       </c>
       <c r="R61" t="n">
-        <v>6793754</v>
+        <v>6794365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126160807</v>
+        <v>126164027</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,34 +6546,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431738</v>
+        <v>431844</v>
       </c>
       <c r="R62" t="n">
-        <v>6793845</v>
+        <v>6794158</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6632,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126160381</v>
+        <v>126160807</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431734</v>
+        <v>431738</v>
       </c>
       <c r="R63" t="n">
-        <v>6793794</v>
+        <v>6793845</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6697,12 +6697,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6729,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126164027</v>
+        <v>126160381</v>
       </c>
       <c r="B64" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,34 +6740,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431844</v>
+        <v>431734</v>
       </c>
       <c r="R64" t="n">
-        <v>6794158</v>
+        <v>6793794</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126166809</v>
+        <v>126159369</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,14 +6857,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432273</v>
+        <v>431635</v>
       </c>
       <c r="R65" t="n">
-        <v>6794365</v>
+        <v>6793754</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6926,7 +6926,7 @@
         <v>126166708</v>
       </c>
       <c r="B66" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126165342</v>
       </c>
       <c r="B67" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>126162164</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126162912</v>
+        <v>126159852</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7230,39 +7230,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431943</v>
+        <v>431733</v>
       </c>
       <c r="R69" t="n">
-        <v>6794014</v>
+        <v>6793772</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126163869</v>
+        <v>126162912</v>
       </c>
       <c r="B70" t="n">
-        <v>79566</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,34 +7327,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431844</v>
+        <v>431943</v>
       </c>
       <c r="R70" t="n">
-        <v>6794158</v>
+        <v>6794014</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,45 +7418,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126159852</v>
+        <v>126157808</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>58027</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431733</v>
+        <v>431582</v>
       </c>
       <c r="R71" t="n">
-        <v>6793772</v>
+        <v>6793582</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7518,7 +7523,7 @@
         <v>126161304</v>
       </c>
       <c r="B72" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7612,50 +7617,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126157808</v>
+        <v>126163869</v>
       </c>
       <c r="B73" t="n">
-        <v>58025</v>
+        <v>79569</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431582</v>
+        <v>431844</v>
       </c>
       <c r="R73" t="n">
-        <v>6793582</v>
+        <v>6794158</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
         <v>126162596</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>126158231</v>
       </c>
       <c r="B75" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>126166662</v>
       </c>
       <c r="B76" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126165131</v>
+        <v>126166691</v>
       </c>
       <c r="B77" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431949</v>
+        <v>432272</v>
       </c>
       <c r="R77" t="n">
-        <v>6794232</v>
+        <v>6794337</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126166691</v>
+        <v>126161478</v>
       </c>
       <c r="B78" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8138,14 +8138,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432272</v>
+        <v>431764</v>
       </c>
       <c r="R78" t="n">
-        <v>6794337</v>
+        <v>6794018</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>126161557</v>
       </c>
       <c r="B79" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126161478</v>
+        <v>126165131</v>
       </c>
       <c r="B80" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,34 +8312,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431764</v>
+        <v>431949</v>
       </c>
       <c r="R80" t="n">
-        <v>6794018</v>
+        <v>6794232</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126157967</v>
+        <v>126161074</v>
       </c>
       <c r="B81" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,21 +8409,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431581</v>
+        <v>431755</v>
       </c>
       <c r="R81" t="n">
-        <v>6793601</v>
+        <v>6793917</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8495,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126163857</v>
+        <v>126157967</v>
       </c>
       <c r="B82" t="n">
-        <v>57653</v>
+        <v>79598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,39 +8506,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431844</v>
+        <v>431581</v>
       </c>
       <c r="R82" t="n">
-        <v>6794158</v>
+        <v>6793601</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8597,10 +8592,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126161074</v>
+        <v>126163857</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8608,34 +8603,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431755</v>
+        <v>431844</v>
       </c>
       <c r="R83" t="n">
-        <v>6793917</v>
+        <v>6794158</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8794,7 +8794,7 @@
         <v>126158198</v>
       </c>
       <c r="B85" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>126165247</v>
       </c>
       <c r="B86" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>126160693</v>
       </c>
       <c r="B87" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>126162862</v>
       </c>
       <c r="B88" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9189,10 +9189,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161358</v>
+        <v>126161159</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431735</v>
+        <v>431724</v>
       </c>
       <c r="R89" t="n">
-        <v>6794019</v>
+        <v>6793934</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126161159</v>
+        <v>126161358</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431724</v>
+        <v>431735</v>
       </c>
       <c r="R90" t="n">
-        <v>6793934</v>
+        <v>6794019</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9386,7 +9386,7 @@
         <v>126162110</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>126160792</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>126160826</v>
       </c>
       <c r="B93" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126162464</v>
+        <v>126163938</v>
       </c>
       <c r="B94" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9685,39 +9685,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431861</v>
+        <v>431844</v>
       </c>
       <c r="R94" t="n">
-        <v>6794056</v>
+        <v>6794158</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9779,7 +9774,7 @@
         <v>126159604</v>
       </c>
       <c r="B95" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9873,10 +9868,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126163938</v>
+        <v>126162464</v>
       </c>
       <c r="B96" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9884,34 +9879,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431844</v>
+        <v>431861</v>
       </c>
       <c r="R96" t="n">
-        <v>6794158</v>
+        <v>6794056</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126162132</v>
+        <v>126166906</v>
       </c>
       <c r="B97" t="n">
-        <v>78977</v>
+        <v>91265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9981,21 +9981,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431783</v>
+        <v>432177</v>
       </c>
       <c r="R97" t="n">
-        <v>6794074</v>
+        <v>6794345</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10067,10 +10067,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126160368</v>
+        <v>126162132</v>
       </c>
       <c r="B98" t="n">
-        <v>75072</v>
+        <v>78980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10078,34 +10078,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431734</v>
+        <v>431783</v>
       </c>
       <c r="R98" t="n">
-        <v>6793794</v>
+        <v>6794074</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10167,7 +10167,7 @@
         <v>126160965</v>
       </c>
       <c r="B99" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126166906</v>
+        <v>126160391</v>
       </c>
       <c r="B100" t="n">
-        <v>91262</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10272,34 +10272,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>432177</v>
+        <v>431718</v>
       </c>
       <c r="R100" t="n">
-        <v>6794345</v>
+        <v>6793795</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10358,10 +10358,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126160391</v>
+        <v>126164968</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10369,34 +10369,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431718</v>
+        <v>431934</v>
       </c>
       <c r="R101" t="n">
-        <v>6793795</v>
+        <v>6794246</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126164968</v>
+        <v>126160368</v>
       </c>
       <c r="B102" t="n">
-        <v>79595</v>
+        <v>75075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,34 +10466,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431934</v>
+        <v>431734</v>
       </c>
       <c r="R102" t="n">
-        <v>6794246</v>
+        <v>6793794</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10555,7 +10555,7 @@
         <v>126167341</v>
       </c>
       <c r="B103" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>126161563</v>
       </c>
       <c r="B104" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10751,10 +10751,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126160295</v>
+        <v>126162496</v>
       </c>
       <c r="B105" t="n">
-        <v>57653</v>
+        <v>79598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10762,39 +10762,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431734</v>
+        <v>431861</v>
       </c>
       <c r="R105" t="n">
-        <v>6793794</v>
+        <v>6794056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10853,10 +10848,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126162496</v>
+        <v>126160295</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>57654</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10864,34 +10859,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431861</v>
+        <v>431734</v>
       </c>
       <c r="R106" t="n">
-        <v>6794056</v>
+        <v>6793794</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10953,7 +10953,7 @@
         <v>126190532</v>
       </c>
       <c r="B107" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>126167440</v>
       </c>
       <c r="B108" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126162009</v>
+        <v>126189457</v>
       </c>
       <c r="B109" t="n">
-        <v>78735</v>
+        <v>79012</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11201,21 +11201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11224,14 +11224,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431754</v>
+        <v>431586</v>
       </c>
       <c r="R109" t="n">
-        <v>6794068</v>
+        <v>6793587</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11304,7 +11304,7 @@
         <v>126188368</v>
       </c>
       <c r="B110" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126189457</v>
+        <v>126162009</v>
       </c>
       <c r="B111" t="n">
-        <v>79009</v>
+        <v>78738</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11428,21 +11428,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11451,14 +11451,14 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431586</v>
+        <v>431754</v>
       </c>
       <c r="R111" t="n">
-        <v>6793587</v>
+        <v>6794068</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11531,7 +11531,7 @@
         <v>126190428</v>
       </c>
       <c r="B112" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11643,45 +11643,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126161529</v>
+        <v>126163646</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431705</v>
+        <v>431898</v>
       </c>
       <c r="R113" t="n">
-        <v>6794050</v>
+        <v>6794103</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11713,7 +11718,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11723,7 +11728,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11732,6 +11742,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11750,41 +11761,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126174681</v>
+        <v>126174973</v>
       </c>
       <c r="B114" t="n">
-        <v>79566</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -11792,10 +11805,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431802</v>
+        <v>432045</v>
       </c>
       <c r="R114" t="n">
-        <v>6794020</v>
+        <v>6794330</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11855,50 +11868,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126163646</v>
+        <v>126161529</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431898</v>
+        <v>431705</v>
       </c>
       <c r="R115" t="n">
-        <v>6794103</v>
+        <v>6794050</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11930,7 +11938,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -11940,12 +11948,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11954,7 +11957,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -11973,43 +11975,41 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126174973</v>
+        <v>126174681</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12017,10 +12017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>432045</v>
+        <v>431802</v>
       </c>
       <c r="R116" t="n">
-        <v>6794330</v>
+        <v>6794020</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12080,10 +12080,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126190566</v>
+        <v>126174513</v>
       </c>
       <c r="B117" t="n">
-        <v>57653</v>
+        <v>79598</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12091,42 +12091,41 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431683</v>
+        <v>431721</v>
       </c>
       <c r="R117" t="n">
-        <v>6793850</v>
+        <v>6793745</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12156,49 +12155,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126175046</v>
+        <v>126174710</v>
       </c>
       <c r="B118" t="n">
-        <v>79566</v>
+        <v>79598</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12206,21 +12196,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -12237,10 +12227,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>432130</v>
+        <v>431847</v>
       </c>
       <c r="R118" t="n">
-        <v>6794314</v>
+        <v>6794063</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12300,10 +12290,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126174710</v>
+        <v>126190566</v>
       </c>
       <c r="B119" t="n">
-        <v>79595</v>
+        <v>57654</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12311,41 +12301,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431847</v>
+        <v>431683</v>
       </c>
       <c r="R119" t="n">
-        <v>6794063</v>
+        <v>6793850</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12375,40 +12366,49 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126174513</v>
+        <v>126175046</v>
       </c>
       <c r="B120" t="n">
-        <v>79595</v>
+        <v>79569</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12416,21 +12416,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431721</v>
+        <v>432130</v>
       </c>
       <c r="R120" t="n">
-        <v>6793745</v>
+        <v>6794314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12510,45 +12510,53 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126166304</v>
+        <v>126190620</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>432104</v>
+        <v>432093</v>
       </c>
       <c r="R121" t="n">
-        <v>6794293</v>
+        <v>6794181</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12580,7 +12588,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12590,7 +12598,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12617,53 +12625,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126190620</v>
+        <v>126166304</v>
       </c>
       <c r="B122" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>432093</v>
+        <v>432104</v>
       </c>
       <c r="R122" t="n">
-        <v>6794181</v>
+        <v>6794293</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12735,7 +12735,7 @@
         <v>126174983</v>
       </c>
       <c r="B123" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126165849</v>
+        <v>126165489</v>
       </c>
       <c r="B124" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -12880,10 +12880,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>432071</v>
+        <v>432050</v>
       </c>
       <c r="R124" t="n">
-        <v>6794181</v>
+        <v>6794210</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -12925,12 +12925,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Hona? ev med kycklingar</t>
+          <t>Blåbärsspillning, fjolårets, på stubbe</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12950,17 +12950,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126165489</v>
+        <v>126165849</v>
       </c>
       <c r="B125" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -13000,10 +13000,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>432050</v>
+        <v>432071</v>
       </c>
       <c r="R125" t="n">
-        <v>6794210</v>
+        <v>6794181</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13045,12 +13045,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Blåbärsspillning, fjolårets, på stubbe</t>
+          <t>Hona? ev med kycklingar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13080,7 +13080,7 @@
         <v>126162531</v>
       </c>
       <c r="B126" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13184,52 +13184,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126174545</v>
+        <v>126189221</v>
       </c>
       <c r="B127" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431721</v>
+        <v>431686</v>
       </c>
       <c r="R127" t="n">
-        <v>6793766</v>
+        <v>6793927</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13259,9 +13257,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13277,62 +13285,64 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126189221</v>
+        <v>126174545</v>
       </c>
       <c r="B128" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431686</v>
+        <v>431721</v>
       </c>
       <c r="R128" t="n">
-        <v>6793927</v>
+        <v>6793766</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13362,19 +13372,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13390,22 +13390,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126188380</v>
+        <v>126167010</v>
       </c>
       <c r="B129" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13431,19 +13431,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>431700</v>
+        <v>432026</v>
       </c>
       <c r="R129" t="n">
-        <v>6793865</v>
+        <v>6794333</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13475,7 +13472,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13485,12 +13482,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Massor</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13499,7 +13491,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13518,10 +13509,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126167010</v>
+        <v>126188380</v>
       </c>
       <c r="B130" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13547,16 +13538,19 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>432026</v>
+        <v>431700</v>
       </c>
       <c r="R130" t="n">
-        <v>6794333</v>
+        <v>6793865</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13588,7 +13582,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13598,7 +13592,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13607,6 +13606,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13628,7 +13628,7 @@
         <v>126189975</v>
       </c>
       <c r="B131" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13736,57 +13736,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126190225</v>
+        <v>126162062</v>
       </c>
       <c r="B132" t="n">
-        <v>56848</v>
+        <v>78980</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431908</v>
+        <v>431788</v>
       </c>
       <c r="R132" t="n">
-        <v>6794091</v>
+        <v>6794108</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13818,7 +13806,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13828,7 +13816,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13855,10 +13843,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126190276</v>
+        <v>126165527</v>
       </c>
       <c r="B133" t="n">
-        <v>56232</v>
+        <v>78738</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13866,42 +13854,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>206004</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431609</v>
+        <v>432037</v>
       </c>
       <c r="R133" t="n">
-        <v>6793764</v>
+        <v>6794186</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13933,7 +13916,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13943,7 +13926,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13952,6 +13935,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13963,7 +13947,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14083,45 +14067,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126162062</v>
+        <v>126190225</v>
       </c>
       <c r="B135" t="n">
-        <v>78977</v>
+        <v>56849</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431788</v>
+        <v>431908</v>
       </c>
       <c r="R135" t="n">
-        <v>6794108</v>
+        <v>6794091</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14153,7 +14149,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14163,7 +14159,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14190,10 +14186,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126165527</v>
+        <v>126190276</v>
       </c>
       <c r="B136" t="n">
-        <v>78735</v>
+        <v>56233</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14201,37 +14197,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>206004</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>432037</v>
+        <v>431609</v>
       </c>
       <c r="R136" t="n">
-        <v>6794186</v>
+        <v>6793764</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14263,7 +14264,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14273,7 +14274,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14282,7 +14283,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14294,17 +14294,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126174674</v>
+        <v>126188869</v>
       </c>
       <c r="B137" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14312,41 +14312,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431802</v>
+        <v>431661</v>
       </c>
       <c r="R137" t="n">
-        <v>6794020</v>
+        <v>6793741</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14376,9 +14372,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14394,22 +14400,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126188589</v>
+        <v>126174674</v>
       </c>
       <c r="B138" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14417,37 +14423,41 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431672</v>
+        <v>431802</v>
       </c>
       <c r="R138" t="n">
-        <v>6794047</v>
+        <v>6794020</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14477,24 +14487,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14510,22 +14505,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126188441</v>
+        <v>126188589</v>
       </c>
       <c r="B139" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14560,10 +14555,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431692</v>
+        <v>431672</v>
       </c>
       <c r="R139" t="n">
-        <v>6793928</v>
+        <v>6794047</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14595,7 +14590,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14605,7 +14600,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14633,10 +14633,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126188869</v>
+        <v>126188441</v>
       </c>
       <c r="B140" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14644,21 +14644,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431661</v>
+        <v>431692</v>
       </c>
       <c r="R140" t="n">
-        <v>6793741</v>
+        <v>6793928</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14744,48 +14744,57 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126174633</v>
+        <v>126190311</v>
       </c>
       <c r="B141" t="n">
-        <v>79566</v>
+        <v>97239</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431765</v>
+        <v>431597</v>
       </c>
       <c r="R141" t="n">
-        <v>6793901</v>
+        <v>6793607</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14815,9 +14824,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14833,22 +14852,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126161782</v>
+        <v>126174633</v>
       </c>
       <c r="B142" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14856,21 +14875,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14879,14 +14898,14 @@
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431721</v>
+        <v>431765</v>
       </c>
       <c r="R142" t="n">
-        <v>6794089</v>
+        <v>6793901</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14916,19 +14935,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14944,69 +14953,60 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126190311</v>
+        <v>126161782</v>
       </c>
       <c r="B143" t="n">
-        <v>97230</v>
+        <v>78739</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431597</v>
+        <v>431721</v>
       </c>
       <c r="R143" t="n">
-        <v>6793607</v>
+        <v>6794089</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15079,7 +15079,7 @@
         <v>126189837</v>
       </c>
       <c r="B144" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15203,7 +15203,7 @@
         <v>126174664</v>
       </c>
       <c r="B145" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>126185018</v>
       </c>
       <c r="B146" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>126175021</v>
       </c>
       <c r="B147" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>126188626</v>
       </c>
       <c r="B148" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>126165414</v>
       </c>
       <c r="B149" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -15764,7 +15764,7 @@
         <v>126165721</v>
       </c>
       <c r="B150" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>126174690</v>
       </c>
       <c r="B151" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>126190467</v>
       </c>
       <c r="B152" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16097,10 +16097,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126189054</v>
+        <v>126174924</v>
       </c>
       <c r="B153" t="n">
-        <v>79595</v>
+        <v>79012</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16108,37 +16108,41 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>431660</v>
+        <v>431893</v>
       </c>
       <c r="R153" t="n">
-        <v>6793737</v>
+        <v>6794043</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16168,19 +16172,14 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>12:57</t>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ett obs ex på gran</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16196,12 +16195,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16211,7 +16210,7 @@
         <v>126174574</v>
       </c>
       <c r="B154" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16313,10 +16312,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126174924</v>
+        <v>126189054</v>
       </c>
       <c r="B155" t="n">
-        <v>79009</v>
+        <v>79598</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16324,41 +16323,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431893</v>
+        <v>431660</v>
       </c>
       <c r="R155" t="n">
-        <v>6794043</v>
+        <v>6793737</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16388,14 +16383,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ett obs ex på gran</t>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16411,12 +16411,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -16426,7 +16426,7 @@
         <v>126188337</v>
       </c>
       <c r="B156" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16543,43 +16543,41 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126174659</v>
+        <v>126174961</v>
       </c>
       <c r="B157" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -16587,10 +16585,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>431731</v>
+        <v>432073</v>
       </c>
       <c r="R157" t="n">
-        <v>6793834</v>
+        <v>6794217</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16653,7 +16651,7 @@
         <v>126165393</v>
       </c>
       <c r="B158" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16768,7 +16766,7 @@
         <v>126162636</v>
       </c>
       <c r="B159" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16881,41 +16879,43 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126174961</v>
+        <v>126174659</v>
       </c>
       <c r="B160" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -16923,10 +16923,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>432073</v>
+        <v>431731</v>
       </c>
       <c r="R160" t="n">
-        <v>6794217</v>
+        <v>6793834</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16989,7 +16989,7 @@
         <v>126166368</v>
       </c>
       <c r="B161" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>126174682</v>
       </c>
       <c r="B162" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>126165703</v>
       </c>
       <c r="B163" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17333,7 +17333,7 @@
         <v>126165571</v>
       </c>
       <c r="B164" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>126192573</v>
       </c>
       <c r="B165" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>126189897</v>
       </c>
       <c r="B166" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17672,10 +17672,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126167044</v>
+        <v>126162572</v>
       </c>
       <c r="B167" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17683,27 +17683,26 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -17711,10 +17710,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>432002</v>
+        <v>431906</v>
       </c>
       <c r="R167" t="n">
-        <v>6794336</v>
+        <v>6794099</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17746,7 +17745,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17756,7 +17755,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På 6 tallar inom en radie av 5m</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17765,6 +17769,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17776,57 +17781,59 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126188293</v>
+        <v>126174530</v>
       </c>
       <c r="B168" t="n">
-        <v>5176</v>
+        <v>79598</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431642</v>
+        <v>431675</v>
       </c>
       <c r="R168" t="n">
-        <v>6794010</v>
+        <v>6793721</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17856,19 +17863,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17884,22 +17881,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126174530</v>
+        <v>126174557</v>
       </c>
       <c r="B169" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17938,10 +17935,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>431675</v>
+        <v>431730</v>
       </c>
       <c r="R169" t="n">
-        <v>6793721</v>
+        <v>6793838</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18001,10 +17998,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126174557</v>
+        <v>126167044</v>
       </c>
       <c r="B170" t="n">
-        <v>79595</v>
+        <v>57654</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18012,41 +18009,38 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>431730</v>
+        <v>432002</v>
       </c>
       <c r="R170" t="n">
-        <v>6793838</v>
+        <v>6794336</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18076,78 +18070,89 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126162572</v>
+        <v>126188293</v>
       </c>
       <c r="B171" t="n">
-        <v>78977</v>
+        <v>5176</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>431906</v>
+        <v>431642</v>
       </c>
       <c r="R171" t="n">
-        <v>6794099</v>
+        <v>6794010</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18179,7 +18184,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18189,12 +18194,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>På 6 tallar inom en radie av 5m</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Håkan Thenander, Peter Turander, Jakob Bowers, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18225,7 +18225,7 @@
         <v>126165882</v>
       </c>
       <c r="B172" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>126165872</v>
       </c>
       <c r="B174" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>126166244</v>
       </c>
       <c r="B175" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18610,10 +18610,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126166337</v>
+        <v>126166521</v>
       </c>
       <c r="B176" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>126165950</v>
       </c>
       <c r="B177" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>126166104</v>
       </c>
       <c r="B178" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18906,10 +18906,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126163588</v>
+        <v>126163407</v>
       </c>
       <c r="B179" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18917,21 +18917,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18977,6 +18977,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Hackhål/bohål på stam</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19003,10 +19008,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126163407</v>
+        <v>126163588</v>
       </c>
       <c r="B180" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19014,21 +19019,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19074,11 +19079,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Hackhål/bohål på stam</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19108,7 +19108,7 @@
         <v>126165579</v>
       </c>
       <c r="B181" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>126390164</v>
       </c>
       <c r="B183" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>126391418</v>
       </c>
       <c r="B184" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>126390323</v>
       </c>
       <c r="B185" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>126392236</v>
       </c>
       <c r="B186" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>126392797</v>
       </c>
       <c r="B187" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>126392771</v>
       </c>
       <c r="B188" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>126390231</v>
       </c>
       <c r="B189" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>126390354</v>
       </c>
       <c r="B190" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>126391208</v>
       </c>
       <c r="B191" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>126391435</v>
       </c>
       <c r="B192" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>126392605</v>
       </c>
       <c r="B193" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>126391199</v>
       </c>
       <c r="B194" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>126391926</v>
       </c>
       <c r="B195" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>126391910</v>
       </c>
       <c r="B196" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>126392284</v>
       </c>
       <c r="B197" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>126391611</v>
       </c>
       <c r="B198" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>126390468</v>
       </c>
       <c r="B199" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>126390506</v>
       </c>
       <c r="B200" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>126391130</v>
       </c>
       <c r="B201" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -3585,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126166842</v>
+        <v>126161615</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,39 +3596,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432245</v>
+        <v>431758</v>
       </c>
       <c r="R32" t="n">
-        <v>6794369</v>
+        <v>6794063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126161615</v>
+        <v>126165139</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431758</v>
+        <v>431949</v>
       </c>
       <c r="R33" t="n">
-        <v>6794063</v>
+        <v>6794232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,7 +3779,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126165139</v>
+        <v>126161265</v>
       </c>
       <c r="B34" t="n">
         <v>79598</v>
@@ -3815,14 +3810,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431949</v>
+        <v>431735</v>
       </c>
       <c r="R34" t="n">
-        <v>6794232</v>
+        <v>6794019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3849,12 +3844,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3881,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126161265</v>
+        <v>126159713</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,13 +3911,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431735</v>
+        <v>431676</v>
       </c>
       <c r="R35" t="n">
-        <v>6794019</v>
+        <v>6793755</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3946,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3978,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126159713</v>
+        <v>126159766</v>
       </c>
       <c r="B36" t="n">
         <v>78980</v>
@@ -4013,13 +4008,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431676</v>
+        <v>431687</v>
       </c>
       <c r="R36" t="n">
-        <v>6793755</v>
+        <v>6793778</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4075,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126159766</v>
+        <v>126161051</v>
       </c>
       <c r="B37" t="n">
         <v>78980</v>
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431687</v>
+        <v>431757</v>
       </c>
       <c r="R37" t="n">
-        <v>6793778</v>
+        <v>6793912</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4140,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4172,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126161051</v>
+        <v>126162787</v>
       </c>
       <c r="B38" t="n">
         <v>78980</v>
@@ -4203,14 +4198,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431757</v>
+        <v>431921</v>
       </c>
       <c r="R38" t="n">
-        <v>6793912</v>
+        <v>6794053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4237,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126162787</v>
+        <v>126166842</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,34 +4275,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431921</v>
+        <v>432245</v>
       </c>
       <c r="R39" t="n">
-        <v>6794053</v>
+        <v>6794369</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126167392</v>
+        <v>126164975</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431653</v>
+        <v>431934</v>
       </c>
       <c r="R40" t="n">
-        <v>6793960</v>
+        <v>6794246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4437,11 +4437,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4468,10 +4463,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126162274</v>
+        <v>126166682</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,21 +4474,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431815</v>
+        <v>432272</v>
       </c>
       <c r="R41" t="n">
-        <v>6794067</v>
+        <v>6794337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,7 +4560,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126162811</v>
+        <v>126167392</v>
       </c>
       <c r="B42" t="n">
         <v>78980</v>
@@ -4600,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431942</v>
+        <v>431653</v>
       </c>
       <c r="R42" t="n">
-        <v>6794029</v>
+        <v>6793960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126156950</v>
+        <v>126162274</v>
       </c>
       <c r="B43" t="n">
         <v>78980</v>
@@ -4693,14 +4693,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431647</v>
+        <v>431815</v>
       </c>
       <c r="R43" t="n">
-        <v>6793602</v>
+        <v>6794067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126159534</v>
+        <v>126162811</v>
       </c>
       <c r="B44" t="n">
         <v>78980</v>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431657</v>
+        <v>431942</v>
       </c>
       <c r="R44" t="n">
-        <v>6793728</v>
+        <v>6794029</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126161498</v>
+        <v>126156950</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,39 +4867,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431776</v>
+        <v>431647</v>
       </c>
       <c r="R45" t="n">
-        <v>6794017</v>
+        <v>6793602</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126165020</v>
+        <v>126159534</v>
       </c>
       <c r="B46" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,39 +4964,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431934</v>
+        <v>431657</v>
       </c>
       <c r="R46" t="n">
-        <v>6794246</v>
+        <v>6793728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5050,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126164975</v>
+        <v>126161498</v>
       </c>
       <c r="B47" t="n">
-        <v>79569</v>
+        <v>57654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,34 +5061,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431934</v>
+        <v>431776</v>
       </c>
       <c r="R47" t="n">
-        <v>6794246</v>
+        <v>6794017</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126166682</v>
+        <v>126165020</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>57654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5163,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432272</v>
+        <v>431934</v>
       </c>
       <c r="R48" t="n">
-        <v>6794337</v>
+        <v>6794246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7219,45 +7219,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126159852</v>
+        <v>126157808</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431733</v>
+        <v>431582</v>
       </c>
       <c r="R69" t="n">
-        <v>6793772</v>
+        <v>6793582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7316,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126162912</v>
+        <v>126161304</v>
       </c>
       <c r="B70" t="n">
-        <v>57657</v>
+        <v>79569</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7327,39 +7332,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431943</v>
+        <v>431735</v>
       </c>
       <c r="R70" t="n">
-        <v>6794014</v>
+        <v>6794019</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7418,50 +7418,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126157808</v>
+        <v>126163869</v>
       </c>
       <c r="B71" t="n">
-        <v>58027</v>
+        <v>79569</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431582</v>
+        <v>431844</v>
       </c>
       <c r="R71" t="n">
-        <v>6793582</v>
+        <v>6794158</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7520,10 +7515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126161304</v>
+        <v>126159852</v>
       </c>
       <c r="B72" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7531,21 +7526,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7555,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431735</v>
+        <v>431733</v>
       </c>
       <c r="R72" t="n">
-        <v>6794019</v>
+        <v>6793772</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7585,12 +7580,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7617,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126163869</v>
+        <v>126162912</v>
       </c>
       <c r="B73" t="n">
-        <v>79569</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7628,34 +7623,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431844</v>
+        <v>431943</v>
       </c>
       <c r="R73" t="n">
-        <v>6794158</v>
+        <v>6794014</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126166691</v>
+        <v>126165131</v>
       </c>
       <c r="B77" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432272</v>
+        <v>431949</v>
       </c>
       <c r="R77" t="n">
-        <v>6794337</v>
+        <v>6794232</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126161478</v>
+        <v>126166691</v>
       </c>
       <c r="B78" t="n">
         <v>79598</v>
@@ -8138,14 +8138,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431764</v>
+        <v>432272</v>
       </c>
       <c r="R78" t="n">
-        <v>6794018</v>
+        <v>6794337</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126161557</v>
+        <v>126161478</v>
       </c>
       <c r="B79" t="n">
         <v>79598</v>
@@ -8235,14 +8235,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431758</v>
+        <v>431764</v>
       </c>
       <c r="R79" t="n">
-        <v>6794063</v>
+        <v>6794018</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126165131</v>
+        <v>126161557</v>
       </c>
       <c r="B80" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,21 +8312,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431949</v>
+        <v>431758</v>
       </c>
       <c r="R80" t="n">
-        <v>6794232</v>
+        <v>6794063</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -13077,45 +13077,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126162531</v>
+        <v>126189221</v>
       </c>
       <c r="B126" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431906</v>
+        <v>431686</v>
       </c>
       <c r="R126" t="n">
-        <v>6794099</v>
+        <v>6793927</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13147,7 +13152,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13157,7 +13162,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13166,6 +13171,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13184,50 +13190,52 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126189221</v>
+        <v>126174545</v>
       </c>
       <c r="B127" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431686</v>
+        <v>431721</v>
       </c>
       <c r="R127" t="n">
-        <v>6793927</v>
+        <v>6793766</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13257,19 +13265,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13285,22 +13283,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126174545</v>
+        <v>126162531</v>
       </c>
       <c r="B128" t="n">
-        <v>78739</v>
+        <v>57654</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13308,41 +13306,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431721</v>
+        <v>431906</v>
       </c>
       <c r="R128" t="n">
-        <v>6793766</v>
+        <v>6794099</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13372,30 +13363,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13625,10 +13625,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126189975</v>
+        <v>126190276</v>
       </c>
       <c r="B131" t="n">
-        <v>92727</v>
+        <v>56233</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13636,37 +13636,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2079</v>
+        <v>206004</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431647</v>
+        <v>431609</v>
       </c>
       <c r="R131" t="n">
-        <v>6794014</v>
+        <v>6793764</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13698,7 +13703,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13708,7 +13713,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13717,7 +13722,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13729,17 +13733,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126162062</v>
+        <v>126189975</v>
       </c>
       <c r="B132" t="n">
-        <v>78980</v>
+        <v>92727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13747,34 +13751,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431788</v>
+        <v>431647</v>
       </c>
       <c r="R132" t="n">
-        <v>6794108</v>
+        <v>6794014</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13806,7 +13813,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13816,7 +13823,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13825,6 +13832,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13836,17 +13844,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126165527</v>
+        <v>126162062</v>
       </c>
       <c r="B133" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13854,37 +13862,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>432037</v>
+        <v>431788</v>
       </c>
       <c r="R133" t="n">
-        <v>6794186</v>
+        <v>6794108</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13916,7 +13921,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13926,7 +13931,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13935,7 +13940,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13954,39 +13958,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126166597</v>
+        <v>126165527</v>
       </c>
       <c r="B134" t="n">
-        <v>8447</v>
+        <v>78738</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -13994,10 +13996,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>432054</v>
+        <v>432037</v>
       </c>
       <c r="R134" t="n">
-        <v>6794331</v>
+        <v>6794186</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14029,7 +14031,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14039,7 +14041,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14060,17 +14062,17 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126190225</v>
+        <v>126166597</v>
       </c>
       <c r="B135" t="n">
-        <v>56849</v>
+        <v>8447</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14078,46 +14080,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431908</v>
+        <v>432054</v>
       </c>
       <c r="R135" t="n">
-        <v>6794091</v>
+        <v>6794331</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14149,7 +14144,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14159,7 +14154,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14168,6 +14163,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14179,34 +14175,34 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126190276</v>
+        <v>126190225</v>
       </c>
       <c r="B136" t="n">
-        <v>56233</v>
+        <v>56849</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14214,7 +14210,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
@@ -14225,14 +14225,14 @@
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431609</v>
+        <v>431908</v>
       </c>
       <c r="R136" t="n">
-        <v>6793764</v>
+        <v>6794091</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14294,17 +14294,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126188869</v>
+        <v>126188589</v>
       </c>
       <c r="B137" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14312,21 +14312,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431661</v>
+        <v>431672</v>
       </c>
       <c r="R137" t="n">
-        <v>6793741</v>
+        <v>6794047</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14384,7 +14384,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14412,10 +14417,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126174674</v>
+        <v>126188441</v>
       </c>
       <c r="B138" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14423,41 +14428,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431802</v>
+        <v>431692</v>
       </c>
       <c r="R138" t="n">
-        <v>6794020</v>
+        <v>6793928</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14487,9 +14488,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14505,22 +14516,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126188589</v>
+        <v>126188869</v>
       </c>
       <c r="B139" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14528,21 +14539,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14555,10 +14566,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431672</v>
+        <v>431661</v>
       </c>
       <c r="R139" t="n">
-        <v>6794047</v>
+        <v>6793741</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14590,7 +14601,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14600,12 +14611,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14633,10 +14639,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126188441</v>
+        <v>126174674</v>
       </c>
       <c r="B140" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14644,37 +14650,41 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431692</v>
+        <v>431802</v>
       </c>
       <c r="R140" t="n">
-        <v>6793928</v>
+        <v>6794020</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14704,19 +14714,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14732,69 +14732,60 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126190311</v>
+        <v>126174633</v>
       </c>
       <c r="B141" t="n">
-        <v>97239</v>
+        <v>79569</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431597</v>
+        <v>431765</v>
       </c>
       <c r="R141" t="n">
-        <v>6793607</v>
+        <v>6793901</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14824,19 +14815,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14852,22 +14833,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126174633</v>
+        <v>126161782</v>
       </c>
       <c r="B142" t="n">
-        <v>79569</v>
+        <v>78739</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14875,21 +14856,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14898,14 +14879,14 @@
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431765</v>
+        <v>431721</v>
       </c>
       <c r="R142" t="n">
-        <v>6793901</v>
+        <v>6794089</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14935,9 +14916,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14953,60 +14944,69 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126161782</v>
+        <v>126190311</v>
       </c>
       <c r="B143" t="n">
-        <v>78739</v>
+        <v>97239</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431721</v>
+        <v>431597</v>
       </c>
       <c r="R143" t="n">
-        <v>6794089</v>
+        <v>6793607</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16648,27 +16648,27 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126165393</v>
+        <v>126162636</v>
       </c>
       <c r="B158" t="n">
-        <v>57654</v>
+        <v>58027</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -16679,11 +16679,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -16691,10 +16687,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432012</v>
+        <v>431906</v>
       </c>
       <c r="R158" t="n">
-        <v>6794220</v>
+        <v>6794099</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16726,7 +16722,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16736,7 +16732,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16763,10 +16764,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126162636</v>
+        <v>126174659</v>
       </c>
       <c r="B159" t="n">
-        <v>58027</v>
+        <v>8447</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16774,38 +16775,43 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>431906</v>
+        <v>431731</v>
       </c>
       <c r="R159" t="n">
-        <v>6794099</v>
+        <v>6793834</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16835,98 +16841,83 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>miljöbild</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126174659</v>
+        <v>126165393</v>
       </c>
       <c r="B160" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>431731</v>
+        <v>432012</v>
       </c>
       <c r="R160" t="n">
-        <v>6793834</v>
+        <v>6794220</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16956,30 +16947,39 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17206,56 +17206,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126165703</v>
+        <v>126165571</v>
       </c>
       <c r="B163" t="n">
-        <v>92535</v>
+        <v>78739</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>432067</v>
+        <v>432034</v>
       </c>
       <c r="R163" t="n">
-        <v>6794181</v>
+        <v>6794182</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17287,7 +17276,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17297,12 +17286,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,7 +17295,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17323,52 +17306,63 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126165571</v>
+        <v>126165703</v>
       </c>
       <c r="B164" t="n">
-        <v>78739</v>
+        <v>92535</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>432034</v>
+        <v>432067</v>
       </c>
       <c r="R164" t="n">
-        <v>6794182</v>
+        <v>6794181</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17400,7 +17394,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17410,7 +17404,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17419,6 +17418,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>

--- a/artfynd/A 25649-2025 artfynd.xlsx
+++ b/artfynd/A 25649-2025 artfynd.xlsx
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022232</v>
+        <v>126022246</v>
       </c>
       <c r="B15" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431615</v>
+        <v>431785</v>
       </c>
       <c r="R15" t="n">
-        <v>6793508</v>
+        <v>6793548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022246</v>
+        <v>126022232</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431785</v>
+        <v>431615</v>
       </c>
       <c r="R16" t="n">
-        <v>6793548</v>
+        <v>6793508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022235</v>
+        <v>126022265</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431773</v>
+        <v>431775</v>
       </c>
       <c r="R17" t="n">
-        <v>6793515</v>
+        <v>6793521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022265</v>
+        <v>126022235</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431775</v>
+        <v>431773</v>
       </c>
       <c r="R18" t="n">
-        <v>6793521</v>
+        <v>6793515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126161538</v>
+        <v>126159713</v>
       </c>
       <c r="B30" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,37 +3402,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431778</v>
+        <v>431676</v>
       </c>
       <c r="R30" t="n">
-        <v>6794048</v>
+        <v>6793755</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126162525</v>
+        <v>126165139</v>
       </c>
       <c r="B31" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431861</v>
+        <v>431949</v>
       </c>
       <c r="R31" t="n">
-        <v>6794056</v>
+        <v>6794232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126161615</v>
+        <v>126162787</v>
       </c>
       <c r="B32" t="n">
         <v>78980</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431758</v>
+        <v>431921</v>
       </c>
       <c r="R32" t="n">
-        <v>6794063</v>
+        <v>6794053</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126165139</v>
+        <v>126159766</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,34 +3693,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431949</v>
+        <v>431687</v>
       </c>
       <c r="R33" t="n">
-        <v>6794232</v>
+        <v>6793778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126159713</v>
+        <v>126161051</v>
       </c>
       <c r="B35" t="n">
         <v>78980</v>
@@ -3911,13 +3911,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431676</v>
+        <v>431757</v>
       </c>
       <c r="R35" t="n">
-        <v>6793755</v>
+        <v>6793912</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126159766</v>
+        <v>126161615</v>
       </c>
       <c r="B36" t="n">
         <v>78980</v>
@@ -4004,14 +4004,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431687</v>
+        <v>431758</v>
       </c>
       <c r="R36" t="n">
-        <v>6793778</v>
+        <v>6794063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126161051</v>
+        <v>126166842</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4081,34 +4081,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431757</v>
+        <v>432245</v>
       </c>
       <c r="R37" t="n">
-        <v>6793912</v>
+        <v>6794369</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4135,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4167,10 +4172,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126162787</v>
+        <v>126161538</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4178,21 +4183,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4202,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431921</v>
+        <v>431778</v>
       </c>
       <c r="R38" t="n">
-        <v>6794053</v>
+        <v>6794048</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126166842</v>
+        <v>126162525</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>79569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4275,39 +4280,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432245</v>
+        <v>431861</v>
       </c>
       <c r="R39" t="n">
-        <v>6794369</v>
+        <v>6794056</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126164975</v>
+        <v>126156950</v>
       </c>
       <c r="B40" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,34 +4377,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431934</v>
+        <v>431647</v>
       </c>
       <c r="R40" t="n">
-        <v>6794246</v>
+        <v>6793602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126166682</v>
+        <v>126167392</v>
       </c>
       <c r="B41" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432272</v>
+        <v>431653</v>
       </c>
       <c r="R41" t="n">
-        <v>6794337</v>
+        <v>6793960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4534,6 +4534,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4560,7 +4565,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126167392</v>
+        <v>126162274</v>
       </c>
       <c r="B42" t="n">
         <v>78980</v>
@@ -4595,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431653</v>
+        <v>431815</v>
       </c>
       <c r="R42" t="n">
-        <v>6793960</v>
+        <v>6794067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4631,11 +4636,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126162274</v>
+        <v>126162811</v>
       </c>
       <c r="B43" t="n">
         <v>78980</v>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431815</v>
+        <v>431942</v>
       </c>
       <c r="R43" t="n">
-        <v>6794067</v>
+        <v>6794029</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126162811</v>
+        <v>126159534</v>
       </c>
       <c r="B44" t="n">
         <v>78980</v>
@@ -4790,14 +4790,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431942</v>
+        <v>431657</v>
       </c>
       <c r="R44" t="n">
-        <v>6794029</v>
+        <v>6793728</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126156950</v>
+        <v>126161498</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4867,34 +4867,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431647</v>
+        <v>431776</v>
       </c>
       <c r="R45" t="n">
-        <v>6793602</v>
+        <v>6794017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4953,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126159534</v>
+        <v>126165020</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4964,34 +4969,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431657</v>
+        <v>431934</v>
       </c>
       <c r="R46" t="n">
-        <v>6793728</v>
+        <v>6794246</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5050,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126161498</v>
+        <v>126164975</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>79569</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5061,39 +5071,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431776</v>
+        <v>431934</v>
       </c>
       <c r="R47" t="n">
-        <v>6794017</v>
+        <v>6794246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5152,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126165020</v>
+        <v>126166682</v>
       </c>
       <c r="B48" t="n">
-        <v>57654</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,39 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431934</v>
+        <v>432272</v>
       </c>
       <c r="R48" t="n">
-        <v>6794246</v>
+        <v>6794337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126161213</v>
+        <v>126162332</v>
       </c>
       <c r="B49" t="n">
         <v>78980</v>
@@ -5285,14 +5285,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431756</v>
+        <v>431839</v>
       </c>
       <c r="R49" t="n">
-        <v>6793994</v>
+        <v>6794073</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126162332</v>
+        <v>126161213</v>
       </c>
       <c r="B50" t="n">
         <v>78980</v>
@@ -5382,14 +5382,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431839</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6794073</v>
+        <v>6793994</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5545,45 +5545,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126160189</v>
+        <v>126162045</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431763</v>
+        <v>431758</v>
       </c>
       <c r="R52" t="n">
-        <v>6793789</v>
+        <v>6794063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,7 +5647,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126157375</v>
+        <v>126157004</v>
       </c>
       <c r="B53" t="n">
         <v>78980</v>
@@ -5717,7 +5722,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 60 meter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5744,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126162207</v>
+        <v>126160189</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5755,34 +5760,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431783</v>
+        <v>431763</v>
       </c>
       <c r="R54" t="n">
-        <v>6794074</v>
+        <v>6793789</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5841,50 +5846,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126162045</v>
+        <v>126162207</v>
       </c>
       <c r="B55" t="n">
-        <v>58027</v>
+        <v>79598</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431758</v>
+        <v>431783</v>
       </c>
       <c r="R55" t="n">
-        <v>6794063</v>
+        <v>6794074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126162541</v>
+        <v>126166910</v>
       </c>
       <c r="B56" t="n">
         <v>78980</v>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431861</v>
+        <v>432177</v>
       </c>
       <c r="R56" t="n">
-        <v>6794056</v>
+        <v>6794345</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126165216</v>
+        <v>126162541</v>
       </c>
       <c r="B57" t="n">
         <v>78980</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431949</v>
+        <v>431861</v>
       </c>
       <c r="R57" t="n">
-        <v>6794232</v>
+        <v>6794056</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126166910</v>
+        <v>126167237</v>
       </c>
       <c r="B58" t="n">
         <v>78980</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432177</v>
+        <v>432161</v>
       </c>
       <c r="R58" t="n">
-        <v>6794345</v>
+        <v>6794303</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6208,6 +6208,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6234,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126167107</v>
+        <v>126165216</v>
       </c>
       <c r="B59" t="n">
         <v>78980</v>
@@ -6269,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432161</v>
+        <v>431949</v>
       </c>
       <c r="R59" t="n">
-        <v>6794303</v>
+        <v>6794232</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6305,11 +6310,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 60 meter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126166809</v>
+        <v>126166708</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432273</v>
+        <v>432272</v>
       </c>
       <c r="R61" t="n">
-        <v>6794365</v>
+        <v>6794337</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6535,10 +6540,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126164027</v>
+        <v>126159369</v>
       </c>
       <c r="B62" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,34 +6551,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431844</v>
+        <v>431635</v>
       </c>
       <c r="R62" t="n">
-        <v>6794158</v>
+        <v>6793754</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6826,10 +6831,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126159369</v>
+        <v>126164027</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,34 +6842,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431635</v>
+        <v>431844</v>
       </c>
       <c r="R65" t="n">
-        <v>6793754</v>
+        <v>6794158</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6923,10 +6928,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126166708</v>
+        <v>126166809</v>
       </c>
       <c r="B66" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,39 +6939,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432272</v>
+        <v>432273</v>
       </c>
       <c r="R66" t="n">
-        <v>6794337</v>
+        <v>6794365</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7219,50 +7219,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126157808</v>
+        <v>126161304</v>
       </c>
       <c r="B69" t="n">
-        <v>58027</v>
+        <v>79569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431582</v>
+        <v>431735</v>
       </c>
       <c r="R69" t="n">
-        <v>6793582</v>
+        <v>6794019</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7284,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,7 +7316,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126161304</v>
+        <v>126163869</v>
       </c>
       <c r="B70" t="n">
         <v>79569</v>
@@ -7352,14 +7347,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431735</v>
+        <v>431844</v>
       </c>
       <c r="R70" t="n">
-        <v>6794019</v>
+        <v>6794158</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7381,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7418,10 +7413,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126163869</v>
+        <v>126162912</v>
       </c>
       <c r="B71" t="n">
-        <v>79569</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7429,34 +7424,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431844</v>
+        <v>431943</v>
       </c>
       <c r="R71" t="n">
-        <v>6794158</v>
+        <v>6794014</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,27 +7612,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126162912</v>
+        <v>126157808</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7643,19 +7643,19 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431943</v>
+        <v>431582</v>
       </c>
       <c r="R73" t="n">
-        <v>6794014</v>
+        <v>6793582</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126165131</v>
+        <v>126166691</v>
       </c>
       <c r="B77" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431949</v>
+        <v>432272</v>
       </c>
       <c r="R77" t="n">
-        <v>6794232</v>
+        <v>6794337</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126166691</v>
+        <v>126161557</v>
       </c>
       <c r="B78" t="n">
         <v>79598</v>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432272</v>
+        <v>431758</v>
       </c>
       <c r="R78" t="n">
-        <v>6794337</v>
+        <v>6794063</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126161557</v>
+        <v>126165131</v>
       </c>
       <c r="B80" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8312,21 +8312,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431758</v>
+        <v>431949</v>
       </c>
       <c r="R80" t="n">
-        <v>6794063</v>
+        <v>6794232</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126161074</v>
+        <v>126157967</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8409,21 +8409,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431755</v>
+        <v>431581</v>
       </c>
       <c r="R81" t="n">
-        <v>6793917</v>
+        <v>6793601</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8495,10 +8495,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126157967</v>
+        <v>126161074</v>
       </c>
       <c r="B82" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8506,21 +8506,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431581</v>
+        <v>431755</v>
       </c>
       <c r="R82" t="n">
-        <v>6793601</v>
+        <v>6793917</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8560,12 +8560,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8791,10 +8791,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126158198</v>
+        <v>126162862</v>
       </c>
       <c r="B85" t="n">
-        <v>75075</v>
+        <v>79569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8802,34 +8802,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431575</v>
+        <v>431942</v>
       </c>
       <c r="R85" t="n">
-        <v>6793614</v>
+        <v>6794029</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8888,10 +8888,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126165247</v>
+        <v>126158198</v>
       </c>
       <c r="B86" t="n">
-        <v>57654</v>
+        <v>75075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8899,39 +8899,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431949</v>
+        <v>431575</v>
       </c>
       <c r="R86" t="n">
-        <v>6794232</v>
+        <v>6793614</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8990,7 +8985,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126160693</v>
+        <v>126165247</v>
       </c>
       <c r="B87" t="n">
         <v>57654</v>
@@ -9021,19 +9016,19 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431740</v>
+        <v>431949</v>
       </c>
       <c r="R87" t="n">
-        <v>6793833</v>
+        <v>6794232</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9060,12 +9055,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9092,10 +9087,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126162862</v>
+        <v>126160693</v>
       </c>
       <c r="B88" t="n">
-        <v>79569</v>
+        <v>57654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9103,34 +9098,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431942</v>
+        <v>431740</v>
       </c>
       <c r="R88" t="n">
-        <v>6794029</v>
+        <v>6793833</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9189,7 +9189,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126161159</v>
+        <v>126161358</v>
       </c>
       <c r="B89" t="n">
         <v>78980</v>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431724</v>
+        <v>431735</v>
       </c>
       <c r="R89" t="n">
-        <v>6793934</v>
+        <v>6794019</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126161358</v>
+        <v>126161159</v>
       </c>
       <c r="B90" t="n">
         <v>78980</v>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431735</v>
+        <v>431724</v>
       </c>
       <c r="R90" t="n">
-        <v>6794019</v>
+        <v>6793934</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9771,10 +9771,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126159604</v>
+        <v>126162464</v>
       </c>
       <c r="B95" t="n">
-        <v>79569</v>
+        <v>57654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9782,34 +9782,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431657</v>
+        <v>431861</v>
       </c>
       <c r="R95" t="n">
-        <v>6793728</v>
+        <v>6794056</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9868,10 +9873,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126162464</v>
+        <v>126159604</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>79569</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9879,39 +9884,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431861</v>
+        <v>431657</v>
       </c>
       <c r="R96" t="n">
-        <v>6794056</v>
+        <v>6793728</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10067,10 +10067,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126162132</v>
+        <v>126164968</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10078,21 +10078,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431783</v>
+        <v>431934</v>
       </c>
       <c r="R98" t="n">
-        <v>6794074</v>
+        <v>6794246</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10164,10 +10164,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126160965</v>
+        <v>126167341</v>
       </c>
       <c r="B99" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10175,34 +10175,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431763</v>
+        <v>431682</v>
       </c>
       <c r="R99" t="n">
-        <v>6793869</v>
+        <v>6794066</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10229,12 +10229,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10261,7 +10266,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126160391</v>
+        <v>126162132</v>
       </c>
       <c r="B100" t="n">
         <v>78980</v>
@@ -10292,14 +10297,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431718</v>
+        <v>431783</v>
       </c>
       <c r="R100" t="n">
-        <v>6793795</v>
+        <v>6794074</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10358,10 +10363,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126164968</v>
+        <v>126160368</v>
       </c>
       <c r="B101" t="n">
-        <v>79598</v>
+        <v>75075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10369,34 +10374,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431934</v>
+        <v>431734</v>
       </c>
       <c r="R101" t="n">
-        <v>6794246</v>
+        <v>6793794</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10455,10 +10460,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126160368</v>
+        <v>126160965</v>
       </c>
       <c r="B102" t="n">
-        <v>75075</v>
+        <v>79598</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10466,21 +10471,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10490,10 +10495,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431734</v>
+        <v>431763</v>
       </c>
       <c r="R102" t="n">
-        <v>6793794</v>
+        <v>6793869</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10520,12 +10525,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10552,7 +10557,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126167341</v>
+        <v>126160391</v>
       </c>
       <c r="B103" t="n">
         <v>78980</v>
@@ -10583,14 +10588,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Slätbergsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431682</v>
+        <v>431718</v>
       </c>
       <c r="R103" t="n">
-        <v>6794066</v>
+        <v>6793795</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10623,11 +10628,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11301,10 +11301,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126188368</v>
+        <v>126190428</v>
       </c>
       <c r="B110" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11312,26 +11312,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11339,10 +11344,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431698</v>
+        <v>431652</v>
       </c>
       <c r="R110" t="n">
-        <v>6793851</v>
+        <v>6793771</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11374,7 +11379,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11384,12 +11389,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Fullt på träden</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11398,7 +11398,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11528,10 +11527,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126190428</v>
+        <v>126188368</v>
       </c>
       <c r="B112" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11539,31 +11538,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11571,10 +11565,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431652</v>
+        <v>431698</v>
       </c>
       <c r="R112" t="n">
-        <v>6793771</v>
+        <v>6793851</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11606,7 +11600,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11616,7 +11610,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Fullt på träden</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11625,6 +11624,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12080,7 +12080,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126174513</v>
+        <v>126174710</v>
       </c>
       <c r="B117" t="n">
         <v>79598</v>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431721</v>
+        <v>431847</v>
       </c>
       <c r="R117" t="n">
-        <v>6793745</v>
+        <v>6794063</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12185,7 +12185,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126174710</v>
+        <v>126174513</v>
       </c>
       <c r="B118" t="n">
         <v>79598</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431847</v>
+        <v>431721</v>
       </c>
       <c r="R118" t="n">
-        <v>6794063</v>
+        <v>6793745</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13077,50 +13077,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126189221</v>
+        <v>126162531</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431686</v>
+        <v>431906</v>
       </c>
       <c r="R126" t="n">
-        <v>6793927</v>
+        <v>6794099</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13152,7 +13147,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13162,7 +13157,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13171,7 +13166,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13295,45 +13289,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126162531</v>
+        <v>126189221</v>
       </c>
       <c r="B128" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431906</v>
+        <v>431686</v>
       </c>
       <c r="R128" t="n">
-        <v>6794099</v>
+        <v>6793927</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13365,7 +13364,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13375,7 +13374,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13384,6 +13383,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13402,7 +13402,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126167010</v>
+        <v>126188380</v>
       </c>
       <c r="B129" t="n">
         <v>78980</v>
@@ -13431,16 +13431,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>432026</v>
+        <v>431700</v>
       </c>
       <c r="R129" t="n">
-        <v>6794333</v>
+        <v>6793865</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13472,7 +13475,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13482,7 +13485,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13491,6 +13499,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13509,7 +13518,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126188380</v>
+        <v>126167010</v>
       </c>
       <c r="B130" t="n">
         <v>78980</v>
@@ -13538,19 +13547,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431700</v>
+        <v>432026</v>
       </c>
       <c r="R130" t="n">
-        <v>6793865</v>
+        <v>6794333</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13582,7 +13588,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13592,12 +13598,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Massor</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13606,7 +13607,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13625,10 +13625,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126190276</v>
+        <v>126162062</v>
       </c>
       <c r="B131" t="n">
-        <v>56233</v>
+        <v>78980</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13636,42 +13636,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Baruersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431609</v>
+        <v>431788</v>
       </c>
       <c r="R131" t="n">
-        <v>6793764</v>
+        <v>6794108</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13703,7 +13695,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13713,7 +13705,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13733,17 +13725,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126189975</v>
+        <v>126165527</v>
       </c>
       <c r="B132" t="n">
-        <v>92727</v>
+        <v>78738</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13751,21 +13743,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13774,14 +13766,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431647</v>
+        <v>432037</v>
       </c>
       <c r="R132" t="n">
-        <v>6794014</v>
+        <v>6794186</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13813,7 +13805,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13823,7 +13815,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13844,52 +13836,64 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126162062</v>
+        <v>126190225</v>
       </c>
       <c r="B133" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431788</v>
+        <v>431908</v>
       </c>
       <c r="R133" t="n">
-        <v>6794108</v>
+        <v>6794091</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13921,7 +13925,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13931,7 +13935,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13958,37 +13962,39 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126165527</v>
+        <v>126166597</v>
       </c>
       <c r="B134" t="n">
-        <v>78738</v>
+        <v>8447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -13996,10 +14002,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>432037</v>
+        <v>432054</v>
       </c>
       <c r="R134" t="n">
-        <v>6794186</v>
+        <v>6794331</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14031,7 +14037,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14041,7 +14047,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14062,57 +14068,60 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126166597</v>
+        <v>126190276</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>56233</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baruersberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>432054</v>
+        <v>431609</v>
       </c>
       <c r="R135" t="n">
-        <v>6794331</v>
+        <v>6793764</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14144,7 +14153,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14154,7 +14163,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14163,7 +14172,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14175,53 +14183,44 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld, Eva Löfqvist, Peter Turander, Jakob Bowers, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126190225</v>
+        <v>126189975</v>
       </c>
       <c r="B136" t="n">
-        <v>56849</v>
+        <v>92727</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14229,10 +14228,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431908</v>
+        <v>431647</v>
       </c>
       <c r="R136" t="n">
-        <v>6794091</v>
+        <v>6794014</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14264,7 +14263,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14274,7 +14273,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14283,6 +14282,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14294,17 +14294,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Jakob Bowers, Eva Löfqvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126188589</v>
+        <v>126174674</v>
       </c>
       <c r="B137" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14312,37 +14312,41 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431672</v>
+        <v>431802</v>
       </c>
       <c r="R137" t="n">
-        <v>6794047</v>
+        <v>6794020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14372,24 +14376,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14405,19 +14394,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126188441</v>
+        <v>126188589</v>
       </c>
       <c r="B138" t="n">
         <v>78980</v>
@@ -14455,10 +14444,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431692</v>
+        <v>431672</v>
       </c>
       <c r="R138" t="n">
-        <v>6793928</v>
+        <v>6794047</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14490,7 +14479,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14500,7 +14489,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>6 tallar med garnlav på inom kort avstånd</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14528,10 +14522,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126188869</v>
+        <v>126188441</v>
       </c>
       <c r="B139" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14539,21 +14533,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14566,10 +14560,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431661</v>
+        <v>431692</v>
       </c>
       <c r="R139" t="n">
-        <v>6793741</v>
+        <v>6793928</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14601,7 +14595,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14611,7 +14605,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14639,10 +14633,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126174674</v>
+        <v>126188869</v>
       </c>
       <c r="B140" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14650,41 +14644,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431802</v>
+        <v>431661</v>
       </c>
       <c r="R140" t="n">
-        <v>6794020</v>
+        <v>6793741</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14714,9 +14704,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14732,60 +14732,69 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126174633</v>
+        <v>126190311</v>
       </c>
       <c r="B141" t="n">
-        <v>79569</v>
+        <v>97239</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431765</v>
+        <v>431597</v>
       </c>
       <c r="R141" t="n">
-        <v>6793901</v>
+        <v>6793607</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14815,9 +14824,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14833,22 +14852,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126161782</v>
+        <v>126174664</v>
       </c>
       <c r="B142" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14856,37 +14875,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431721</v>
+        <v>431803</v>
       </c>
       <c r="R142" t="n">
-        <v>6794089</v>
+        <v>6793998</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14916,86 +14940,75 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126190311</v>
+        <v>126189837</v>
       </c>
       <c r="B143" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15003,10 +15016,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431597</v>
+        <v>431661</v>
       </c>
       <c r="R143" t="n">
-        <v>6793607</v>
+        <v>6793926</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15038,7 +15051,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15048,7 +15061,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15057,7 +15075,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15069,17 +15086,17 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126189837</v>
+        <v>126174633</v>
       </c>
       <c r="B144" t="n">
-        <v>57657</v>
+        <v>79569</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15087,46 +15104,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431661</v>
+        <v>431765</v>
       </c>
       <c r="R144" t="n">
-        <v>6793926</v>
+        <v>6793901</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15156,54 +15164,40 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>UPPSKATTNINGSVIS 10 RADER MED RINGHACK</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist, Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126174664</v>
+        <v>126161782</v>
       </c>
       <c r="B145" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15211,42 +15205,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431803</v>
+        <v>431721</v>
       </c>
       <c r="R145" t="n">
-        <v>6793998</v>
+        <v>6794089</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15276,39 +15265,50 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126185018</v>
+        <v>126174690</v>
       </c>
       <c r="B146" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15316,24 +15316,28 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
@@ -15343,10 +15347,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431898</v>
+        <v>431789</v>
       </c>
       <c r="R146" t="n">
-        <v>6794103</v>
+        <v>6794033</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15376,19 +15380,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15404,22 +15398,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126175021</v>
+        <v>126185018</v>
       </c>
       <c r="B147" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15427,28 +15421,24 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -15458,10 +15448,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>432130</v>
+        <v>431898</v>
       </c>
       <c r="R147" t="n">
-        <v>6794314</v>
+        <v>6794103</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15491,9 +15481,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,22 +15509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126188626</v>
+        <v>126175021</v>
       </c>
       <c r="B148" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15532,42 +15532,41 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431672</v>
+        <v>432130</v>
       </c>
       <c r="R148" t="n">
-        <v>6794047</v>
+        <v>6794314</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15597,76 +15596,62 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Hästmyror i stubben</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126165414</v>
+        <v>126188626</v>
       </c>
       <c r="B149" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15674,20 +15659,20 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Baursberg, Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>432012</v>
+        <v>431672</v>
       </c>
       <c r="R149" t="n">
-        <v>6794220</v>
+        <v>6794047</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15719,7 +15704,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15729,12 +15714,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+          <t>Hästmyror i stubben</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15754,7 +15739,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Peter Turander, Jakob Bowers, Håkan Thenander, Eva Löfqvist</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -15881,52 +15866,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126174690</v>
+        <v>126165414</v>
       </c>
       <c r="B151" t="n">
-        <v>79569</v>
+        <v>56849</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>431789</v>
+        <v>432012</v>
       </c>
       <c r="R151" t="n">
-        <v>6794033</v>
+        <v>6794220</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15956,30 +15942,44 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Hanne? Grova, kanske hundra, utspridda under tall</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld, Eva Löfqvist, Håkan Thenander, Jakob Bowers, Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16207,7 +16207,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126174574</v>
+        <v>126189054</v>
       </c>
       <c r="B154" t="n">
         <v>79598</v>
@@ -16235,24 +16235,20 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Bauersberg, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>431765</v>
+        <v>431660</v>
       </c>
       <c r="R154" t="n">
-        <v>6793901</v>
+        <v>6793737</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16282,9 +16278,19 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16300,19 +16306,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126189054</v>
+        <v>126174574</v>
       </c>
       <c r="B155" t="n">
         <v>79598</v>
@@ -16340,20 +16346,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bauersberg, Dlr</t>
+          <t>Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>431660</v>
+        <v>431765</v>
       </c>
       <c r="R155" t="n">
-        <v>6793737</v>
+        <v>6793901</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16383,19 +16393,9 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16411,12 +16411,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -16543,52 +16543,49 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126174961</v>
+        <v>126162636</v>
       </c>
       <c r="B157" t="n">
-        <v>79598</v>
+        <v>58027</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baursberg, Dlr</t>
+          <t>Baursberg, Baursberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432073</v>
+        <v>431906</v>
       </c>
       <c r="R157" t="n">
-        <v>6794217</v>
+        <v>6794099</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16618,79 +16615,96 @@
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126162636</v>
+        <v>126174961</v>
       </c>
       <c r="B158" t="n">
-        <v>58027</v>
+        <v>79598</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="in